--- a/data/Geller_et_al_2009_WIYN_single_lined_orbits.xlsx
+++ b/data/Geller_et_al_2009_WIYN_single_lined_orbits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kpenev/projects/git/CircularizationDissipationConstraints/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B30B43C-4C22-6547-A067-4181393BD126}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C927BCED-A3D8-0F4F-BDA9-383459EECE3D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10880" yWindow="2820" windowWidth="40320" windowHeight="25980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -571,7 +571,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -771,6 +771,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF00F4FF"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -950,7 +956,6 @@
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -959,6 +964,7 @@
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16"/>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -967,8 +973,8 @@
     <xf numFmtId="11" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1739,7 +1745,7 @@
       <c r="C80" s="1"/>
     </row>
     <row r="81" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A81" s="14" t="s">
+      <c r="A81" s="13" t="s">
         <v>116</v>
       </c>
       <c r="B81" t="s">
@@ -2026,86 +2032,86 @@
         <v>97</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="8" t="s">
+    <row r="90" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C90" s="9" t="s">
+      <c r="C90" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D90" s="10">
+      <c r="D90" s="9">
         <v>5362</v>
       </c>
-      <c r="E90" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F90" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G90" s="11">
+      <c r="E90" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G90" s="10">
         <v>6.1894400000000003</v>
       </c>
-      <c r="H90" s="11">
+      <c r="H90" s="10">
         <v>1.9000000000000001E-4</v>
       </c>
-      <c r="I90" s="11">
+      <c r="I90" s="10">
         <v>178.9</v>
       </c>
-      <c r="J90" s="11">
+      <c r="J90" s="10">
         <v>-28.2</v>
       </c>
-      <c r="K90" s="11">
+      <c r="K90" s="10">
         <v>0.3</v>
       </c>
-      <c r="L90" s="11">
+      <c r="L90" s="10">
         <v>49</v>
       </c>
-      <c r="M90" s="11">
+      <c r="M90" s="10">
         <v>0.5</v>
       </c>
-      <c r="N90" s="11">
+      <c r="N90" s="10">
         <v>2.7E-2</v>
       </c>
-      <c r="O90" s="11">
+      <c r="O90" s="10">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="P90" s="11">
+      <c r="P90" s="10">
         <v>183</v>
       </c>
-      <c r="Q90" s="11">
+      <c r="Q90" s="10">
         <v>20</v>
       </c>
-      <c r="R90" s="11">
+      <c r="R90" s="10">
         <v>51035.3</v>
       </c>
-      <c r="S90" s="11">
+      <c r="S90" s="10">
         <v>0.4</v>
       </c>
-      <c r="T90" s="11">
+      <c r="T90" s="10">
         <v>4.17</v>
       </c>
-      <c r="U90" s="11">
+      <c r="U90" s="10">
         <v>0.04</v>
       </c>
-      <c r="V90" s="12">
+      <c r="V90" s="11">
         <v>7.5200000000000003E-2</v>
       </c>
-      <c r="W90" s="12">
+      <c r="W90" s="11">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="X90" s="11">
+      <c r="X90" s="10">
         <v>1.51</v>
       </c>
-      <c r="Y90" s="11">
+      <c r="Y90" s="10">
         <v>29</v>
       </c>
-      <c r="Z90" s="11" t="s">
+      <c r="Z90" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AA90" s="11" t="s">
+      <c r="AA90" s="10" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2269,91 +2275,91 @@
         <v>97</v>
       </c>
     </row>
-    <row r="93" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="8" t="s">
+    <row r="93" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C93" s="9" t="s">
+      <c r="C93" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D93" s="10">
+      <c r="D93" s="9">
         <v>5733</v>
       </c>
-      <c r="E93" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F93" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G93" s="11">
+      <c r="E93" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G93" s="10">
         <v>8.7040000000000006</v>
       </c>
-      <c r="H93" s="11">
+      <c r="H93" s="10">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="I93" s="11">
+      <c r="I93" s="10">
         <v>356.8</v>
       </c>
-      <c r="J93" s="11">
+      <c r="J93" s="10">
         <v>-33</v>
       </c>
-      <c r="K93" s="11">
+      <c r="K93" s="10">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L93" s="11">
+      <c r="L93" s="10">
         <v>60</v>
       </c>
-      <c r="M93" s="11">
+      <c r="M93" s="10">
         <v>5</v>
       </c>
-      <c r="N93" s="11">
+      <c r="N93" s="10">
         <v>0.5</v>
       </c>
-      <c r="O93" s="11">
+      <c r="O93" s="10">
         <v>0.05</v>
       </c>
-      <c r="P93" s="11">
+      <c r="P93" s="10">
         <v>120</v>
       </c>
-      <c r="Q93" s="11">
+      <c r="Q93" s="10">
         <v>7</v>
       </c>
-      <c r="R93" s="11">
+      <c r="R93" s="10">
         <v>51606.69</v>
       </c>
-      <c r="S93" s="11">
+      <c r="S93" s="10">
         <v>0.1</v>
       </c>
-      <c r="T93" s="11">
+      <c r="T93" s="10">
         <v>6.2</v>
       </c>
-      <c r="U93" s="11">
+      <c r="U93" s="10">
         <v>0.6</v>
       </c>
-      <c r="V93" s="12">
+      <c r="V93" s="11">
         <v>0.13</v>
       </c>
-      <c r="W93" s="12">
+      <c r="W93" s="11">
         <v>0.03</v>
       </c>
-      <c r="X93" s="11">
+      <c r="X93" s="10">
         <v>5.49</v>
       </c>
-      <c r="Y93" s="11">
+      <c r="Y93" s="10">
         <v>11</v>
       </c>
-      <c r="Z93" s="11" t="s">
+      <c r="Z93" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AA93" s="11" t="s">
+      <c r="AA93" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A94" s="14" t="s">
+      <c r="A94" s="13" t="s">
         <v>113</v>
       </c>
       <c r="B94" s="5" t="s">
@@ -2436,7 +2442,7 @@
       </c>
     </row>
     <row r="95" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A95" s="14" t="s">
+      <c r="A95" s="13" t="s">
         <v>113</v>
       </c>
       <c r="B95" s="5" t="s">
@@ -2519,7 +2525,7 @@
       </c>
     </row>
     <row r="96" spans="1:27" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="14" t="s">
+      <c r="A96" s="13" t="s">
         <v>113</v>
       </c>
       <c r="B96" s="24" t="s">
@@ -2685,7 +2691,7 @@
       </c>
     </row>
     <row r="98" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A98" s="14" t="s">
+      <c r="A98" s="13" t="s">
         <v>113</v>
       </c>
       <c r="B98" s="5" t="s">
@@ -2768,7 +2774,7 @@
       </c>
     </row>
     <row r="99" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A99" s="14" t="s">
+      <c r="A99" s="13" t="s">
         <v>113</v>
       </c>
       <c r="B99" s="5" t="s">
@@ -2850,91 +2856,91 @@
         <v>97</v>
       </c>
     </row>
-    <row r="100" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="15" t="s">
+    <row r="100" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B100" s="13" t="s">
+      <c r="B100" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C100" s="9" t="s">
+      <c r="C100" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D100" s="10">
+      <c r="D100" s="9">
         <v>8775</v>
       </c>
-      <c r="E100" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F100" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G100" s="11">
+      <c r="E100" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G100" s="10">
         <v>14.57</v>
       </c>
-      <c r="H100" s="11">
+      <c r="H100" s="10">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I100" s="11">
+      <c r="I100" s="10">
         <v>50.8</v>
       </c>
-      <c r="J100" s="11">
+      <c r="J100" s="10">
         <v>-23.18</v>
       </c>
-      <c r="K100" s="11">
+      <c r="K100" s="10">
         <v>0.22</v>
       </c>
-      <c r="L100" s="11">
+      <c r="L100" s="10">
         <v>8.8000000000000007</v>
       </c>
-      <c r="M100" s="11">
+      <c r="M100" s="10">
         <v>0.3</v>
       </c>
-      <c r="N100" s="11">
+      <c r="N100" s="10">
         <v>0.2</v>
       </c>
-      <c r="O100" s="11">
+      <c r="O100" s="10">
         <v>0.04</v>
       </c>
-      <c r="P100" s="11">
+      <c r="P100" s="10">
         <v>74</v>
       </c>
-      <c r="Q100" s="11">
+      <c r="Q100" s="10">
         <v>9</v>
       </c>
-      <c r="R100" s="11">
+      <c r="R100" s="10">
         <v>50890.400000000001</v>
       </c>
-      <c r="S100" s="11">
+      <c r="S100" s="10">
         <v>0.3</v>
       </c>
-      <c r="T100" s="11">
+      <c r="T100" s="10">
         <v>1.72</v>
       </c>
-      <c r="U100" s="11">
+      <c r="U100" s="10">
         <v>0.06</v>
       </c>
-      <c r="V100" s="12">
+      <c r="V100" s="11">
         <v>9.6000000000000002E-4</v>
       </c>
-      <c r="W100" s="12">
+      <c r="W100" s="11">
         <v>1E-4</v>
       </c>
-      <c r="X100" s="11">
+      <c r="X100" s="10">
         <v>0.9</v>
       </c>
-      <c r="Y100" s="11">
+      <c r="Y100" s="10">
         <v>19</v>
       </c>
-      <c r="Z100" s="11" t="s">
+      <c r="Z100" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AA100" s="11" t="s">
+      <c r="AA100" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A101" s="14" t="s">
+      <c r="A101" s="13" t="s">
         <v>113</v>
       </c>
       <c r="B101" s="5" t="s">
@@ -3017,10 +3023,10 @@
       </c>
     </row>
     <row r="102" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A102" s="14" t="s">
+      <c r="A102" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="5" t="s">
         <v>112</v>
       </c>
       <c r="C102" s="1" t="s">
@@ -3100,10 +3106,10 @@
       </c>
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A103" s="14" t="s">
+      <c r="A103" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B103" s="5" t="s">
         <v>112</v>
       </c>
       <c r="C103" s="1" t="s">
@@ -3183,7 +3189,7 @@
       </c>
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B104" s="7" t="s">
+      <c r="B104" s="5" t="s">
         <v>112</v>
       </c>
       <c r="C104" s="1" t="s">
@@ -3263,7 +3269,7 @@
       </c>
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B105" s="7" t="s">
+      <c r="B105" s="5" t="s">
         <v>112</v>
       </c>
       <c r="C105" s="1" t="s">
@@ -3419,157 +3425,157 @@
         <v>97</v>
       </c>
     </row>
-    <row r="107" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C107" s="9" t="s">
+    <row r="107" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C107" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D107" s="11">
+      <c r="D107" s="10">
         <v>5110</v>
       </c>
-      <c r="E107" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F107" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G107" s="11">
+      <c r="E107" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G107" s="10">
         <v>21.360199999999999</v>
       </c>
-      <c r="H107" s="11">
+      <c r="H107" s="10">
         <v>1.9E-3</v>
       </c>
-      <c r="I107" s="11">
+      <c r="I107" s="10">
         <v>163.19999999999999</v>
       </c>
-      <c r="J107" s="11">
+      <c r="J107" s="10">
         <v>-38</v>
       </c>
-      <c r="K107" s="11">
+      <c r="K107" s="10">
         <v>0.7</v>
       </c>
-      <c r="L107" s="11">
+      <c r="L107" s="10">
         <v>37.799999999999997</v>
       </c>
-      <c r="M107" s="11">
+      <c r="M107" s="10">
         <v>0.9</v>
       </c>
-      <c r="N107" s="11">
+      <c r="N107" s="10">
         <v>0.1</v>
       </c>
-      <c r="O107" s="11">
+      <c r="O107" s="10">
         <v>0.03</v>
       </c>
-      <c r="P107" s="11">
+      <c r="P107" s="10">
         <v>195</v>
       </c>
-      <c r="Q107" s="11">
+      <c r="Q107" s="10">
         <v>16</v>
       </c>
-      <c r="R107" s="11">
+      <c r="R107" s="10">
         <v>51197.2</v>
       </c>
-      <c r="S107" s="11">
+      <c r="S107" s="10">
         <v>0.9</v>
       </c>
-      <c r="T107" s="11">
+      <c r="T107" s="10">
         <v>11.1</v>
       </c>
-      <c r="U107" s="11">
+      <c r="U107" s="10">
         <v>0.3</v>
       </c>
-      <c r="V107" s="12">
+      <c r="V107" s="11">
         <v>0.11799999999999999</v>
       </c>
-      <c r="W107" s="12">
+      <c r="W107" s="11">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="X107" s="11">
+      <c r="X107" s="10">
         <v>3.07</v>
       </c>
-      <c r="Y107" s="11">
+      <c r="Y107" s="10">
         <v>22</v>
       </c>
-      <c r="Z107" s="11" t="s">
+      <c r="Z107" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AA107" s="11" t="s">
+      <c r="AA107" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="108" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C108" s="9" t="s">
+    <row r="108" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C108" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D108" s="11">
+      <c r="D108" s="10">
         <v>736</v>
       </c>
-      <c r="E108" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F108" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G108" s="11">
+      <c r="E108" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F108" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G108" s="10">
         <v>24.004000000000001</v>
       </c>
-      <c r="H108" s="11">
+      <c r="H108" s="10">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="I108" s="11">
+      <c r="I108" s="10">
         <v>50.8</v>
       </c>
-      <c r="J108" s="11">
+      <c r="J108" s="10">
         <v>-50.5</v>
       </c>
-      <c r="K108" s="11">
+      <c r="K108" s="10">
         <v>0.11</v>
       </c>
-      <c r="L108" s="11">
+      <c r="L108" s="10">
         <v>7.21</v>
       </c>
-      <c r="M108" s="11">
+      <c r="M108" s="10">
         <v>0.16</v>
       </c>
-      <c r="N108" s="11">
+      <c r="N108" s="10">
         <v>0.21</v>
       </c>
-      <c r="O108" s="11">
+      <c r="O108" s="10">
         <v>1.9E-2</v>
       </c>
-      <c r="P108" s="11">
+      <c r="P108" s="10">
         <v>240</v>
       </c>
-      <c r="Q108" s="11">
+      <c r="Q108" s="10">
         <v>6</v>
       </c>
-      <c r="R108" s="11">
+      <c r="R108" s="10">
         <v>52039.8</v>
       </c>
-      <c r="S108" s="11">
+      <c r="S108" s="10">
         <v>0.4</v>
       </c>
-      <c r="T108" s="11">
+      <c r="T108" s="10">
         <v>2.33</v>
       </c>
-      <c r="U108" s="11">
+      <c r="U108" s="10">
         <v>0.05</v>
       </c>
-      <c r="V108" s="12">
+      <c r="V108" s="11">
         <v>8.7000000000000001E-4</v>
       </c>
-      <c r="W108" s="12">
+      <c r="W108" s="11">
         <v>6.0000000000000002E-5</v>
       </c>
-      <c r="X108" s="11">
+      <c r="X108" s="10">
         <v>0.42</v>
       </c>
-      <c r="Y108" s="11">
+      <c r="Y108" s="10">
         <v>17</v>
       </c>
-      <c r="Z108" s="11" t="s">
+      <c r="Z108" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AA108" s="11" t="s">
+      <c r="AA108" s="10" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3654,7 +3660,7 @@
       </c>
     </row>
     <row r="110" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B110" s="25" t="s">
+      <c r="B110" s="15" t="s">
         <v>112</v>
       </c>
       <c r="C110" s="1" t="s">

--- a/data/Geller_et_al_2009_WIYN_single_lined_orbits.xlsx
+++ b/data/Geller_et_al_2009_WIYN_single_lined_orbits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kpenev/projects/git/CircularizationDissipationConstraints/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C927BCED-A3D8-0F4F-BDA9-383459EECE3D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E090225-8288-5A46-AEC1-CF1F46CC1FFD}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10880" yWindow="2820" windowWidth="40320" windowHeight="25980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="128">
   <si>
     <t>#</t>
   </si>
@@ -395,13 +395,22 @@
   </si>
   <si>
     <t>Sufficient samples accumulated on the given cluster</t>
+  </si>
+  <si>
+    <t>CRASHED</t>
+  </si>
+  <si>
+    <t>bold purple</t>
+  </si>
+  <si>
+    <t>Stellar mass distributions go out of range too often</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -566,6 +575,24 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF00C8D2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u val="double"/>
+      <sz val="22"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFD261CE"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -783,8 +810,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FF000000"/>
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -963,7 +990,6 @@
     <xf numFmtId="11" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16"/>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -974,7 +1000,8 @@
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1341,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA171"/>
+  <dimension ref="A1:AA172"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -1739,7 +1766,7 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" s="16" t="s">
+      <c r="A80" s="15" t="s">
         <v>115</v>
       </c>
       <c r="C80" s="1"/>
@@ -1754,7 +1781,7 @@
       <c r="C81" s="1"/>
     </row>
     <row r="82" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A82" s="17" t="s">
+      <c r="A82" s="16" t="s">
         <v>116</v>
       </c>
       <c r="B82" t="s">
@@ -1772,7 +1799,7 @@
       <c r="C83" s="1"/>
     </row>
     <row r="84" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A84" s="24" t="s">
+      <c r="A84" s="23" t="s">
         <v>116</v>
       </c>
       <c r="B84" t="s">
@@ -1781,7 +1808,7 @@
       <c r="C84" s="1"/>
     </row>
     <row r="85" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A85" s="19" t="s">
+      <c r="A85" s="18" t="s">
         <v>123</v>
       </c>
       <c r="B85" t="s">
@@ -1790,483 +1817,415 @@
       <c r="C85" s="1"/>
     </row>
     <row r="86" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A86" s="18" t="s">
+      <c r="A86" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B86" t="s">
+        <v>127</v>
+      </c>
+      <c r="C86" s="1"/>
+    </row>
+    <row r="87" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A87" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B87" t="s">
         <v>120</v>
       </c>
-      <c r="C86" s="1"/>
-    </row>
-    <row r="87" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="1"/>
+    </row>
+    <row r="88" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C88" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G87" s="3" t="s">
+      <c r="D88" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G88" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H87" s="3" t="s">
+      <c r="H88" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="I87" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J87" s="3" t="s">
+      <c r="I88" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J88" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="K87" s="3" t="s">
+      <c r="K88" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="L87" s="3" t="s">
+      <c r="L88" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="M87" s="3" t="s">
+      <c r="M88" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="N87" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="O87" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="P87" s="3" t="s">
+      <c r="N88" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="P88" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="Q87" s="3" t="s">
+      <c r="Q88" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="R87" s="3" t="s">
+      <c r="R88" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="S87" s="3" t="s">
+      <c r="S88" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="T87" s="3" t="s">
+      <c r="T88" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="U87" s="3" t="s">
+      <c r="U88" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="V87" s="3" t="s">
+      <c r="V88" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="W87" s="3" t="s">
+      <c r="W88" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="X87" s="3" t="s">
+      <c r="X88" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="Y87" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z87" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="88" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="3" t="s">
+      <c r="Y88" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z88" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B89" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C89" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D89" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="E89" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F88" s="3" t="s">
+      <c r="F89" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G88" s="3" t="s">
+      <c r="G89" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H88" s="3" t="s">
+      <c r="H89" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I88" s="3" t="s">
+      <c r="I89" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J88" s="3" t="s">
+      <c r="J89" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K88" s="3" t="s">
+      <c r="K89" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="L88" s="3" t="s">
+      <c r="L89" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="M88" s="3" t="s">
+      <c r="M89" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="N88" s="3" t="s">
+      <c r="N89" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="O88" s="3" t="s">
+      <c r="O89" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="P88" s="3" t="s">
+      <c r="P89" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q88" s="3" t="s">
+      <c r="Q89" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="R88" s="3" t="s">
+      <c r="R89" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="S88" s="3" t="s">
+      <c r="S89" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="T88" s="3" t="s">
+      <c r="T89" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="U88" s="3" t="s">
+      <c r="U89" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="V88" s="3" t="s">
+      <c r="V89" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="W88" s="3" t="s">
+      <c r="W89" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="X88" s="3" t="s">
+      <c r="X89" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="Y88" s="3" t="s">
+      <c r="Y89" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="Z88" s="3" t="s">
+      <c r="Z89" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="AA88" s="3" t="s">
+      <c r="AA89" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="C89" s="1" t="s">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="C90" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D89">
+      <c r="D90">
         <v>5052</v>
       </c>
-      <c r="E89" t="s">
-        <v>98</v>
-      </c>
-      <c r="F89" t="s">
-        <v>98</v>
-      </c>
-      <c r="G89">
+      <c r="E90" t="s">
+        <v>98</v>
+      </c>
+      <c r="F90" t="s">
+        <v>98</v>
+      </c>
+      <c r="G90">
         <v>3.8473099999999998</v>
       </c>
-      <c r="H89">
+      <c r="H90">
         <v>6.9999999999999994E-5</v>
       </c>
-      <c r="I89">
+      <c r="I90">
         <v>923</v>
       </c>
-      <c r="J89">
+      <c r="J90">
         <v>-42.71</v>
       </c>
-      <c r="K89">
+      <c r="K90">
         <v>0.19</v>
       </c>
-      <c r="L89">
+      <c r="L90">
         <v>8.8000000000000007</v>
       </c>
-      <c r="M89">
+      <c r="M90">
         <v>0.3</v>
       </c>
-      <c r="N89">
+      <c r="N90">
         <v>0.05</v>
       </c>
-      <c r="O89">
+      <c r="O90">
         <v>0.03</v>
       </c>
-      <c r="P89">
+      <c r="P90">
         <v>260</v>
       </c>
-      <c r="Q89">
+      <c r="Q90">
         <v>50</v>
       </c>
-      <c r="R89">
+      <c r="R90">
         <v>51570.2</v>
       </c>
-      <c r="S89">
+      <c r="S90">
         <v>0.5</v>
       </c>
-      <c r="T89">
+      <c r="T90">
         <v>0.46800000000000003</v>
       </c>
-      <c r="U89">
+      <c r="U90">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="V89" s="2">
+      <c r="V90" s="2">
         <v>2.7999999999999998E-4</v>
       </c>
-      <c r="W89" s="2">
+      <c r="W90" s="2">
         <v>3.0000000000000001E-5</v>
       </c>
-      <c r="X89">
+      <c r="X90">
         <v>1.01</v>
       </c>
-      <c r="Y89">
+      <c r="Y90">
         <v>29</v>
       </c>
-      <c r="Z89" t="s">
+      <c r="Z90" t="s">
         <v>96</v>
       </c>
-      <c r="AA89" t="s">
+      <c r="AA90" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="7" t="s">
+    <row r="91" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B90" s="7" t="s">
+      <c r="B91" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C91" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D91" s="9">
         <v>5362</v>
       </c>
-      <c r="E90" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F90" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="G90" s="10">
+      <c r="E91" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G91" s="10">
         <v>6.1894400000000003</v>
       </c>
-      <c r="H90" s="10">
+      <c r="H91" s="10">
         <v>1.9000000000000001E-4</v>
       </c>
-      <c r="I90" s="10">
+      <c r="I91" s="10">
         <v>178.9</v>
       </c>
-      <c r="J90" s="10">
+      <c r="J91" s="10">
         <v>-28.2</v>
       </c>
-      <c r="K90" s="10">
+      <c r="K91" s="10">
         <v>0.3</v>
       </c>
-      <c r="L90" s="10">
+      <c r="L91" s="10">
         <v>49</v>
       </c>
-      <c r="M90" s="10">
+      <c r="M91" s="10">
         <v>0.5</v>
       </c>
-      <c r="N90" s="10">
+      <c r="N91" s="10">
         <v>2.7E-2</v>
       </c>
-      <c r="O90" s="10">
+      <c r="O91" s="10">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="P90" s="10">
+      <c r="P91" s="10">
         <v>183</v>
       </c>
-      <c r="Q90" s="10">
+      <c r="Q91" s="10">
         <v>20</v>
       </c>
-      <c r="R90" s="10">
+      <c r="R91" s="10">
         <v>51035.3</v>
       </c>
-      <c r="S90" s="10">
+      <c r="S91" s="10">
         <v>0.4</v>
       </c>
-      <c r="T90" s="10">
+      <c r="T91" s="10">
         <v>4.17</v>
       </c>
-      <c r="U90" s="10">
+      <c r="U91" s="10">
         <v>0.04</v>
       </c>
-      <c r="V90" s="11">
+      <c r="V91" s="11">
         <v>7.5200000000000003E-2</v>
       </c>
-      <c r="W90" s="11">
+      <c r="W91" s="11">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="X90" s="10">
+      <c r="X91" s="10">
         <v>1.51</v>
       </c>
-      <c r="Y90" s="10">
+      <c r="Y91" s="10">
         <v>29</v>
       </c>
-      <c r="Z90" s="10" t="s">
+      <c r="Z91" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AA90" s="10" t="s">
+      <c r="AA91" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A91" s="5" t="s">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A92" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B92" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D91" s="6">
-        <v>4618</v>
-      </c>
-      <c r="E91" t="s">
-        <v>98</v>
-      </c>
-      <c r="F91" t="s">
-        <v>98</v>
-      </c>
-      <c r="G91">
-        <v>8.0729000000000006</v>
-      </c>
-      <c r="H91">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="I91">
-        <v>104.4</v>
-      </c>
-      <c r="J91">
-        <v>-42.4</v>
-      </c>
-      <c r="K91">
-        <v>0.3</v>
-      </c>
-      <c r="L91">
-        <v>55.1</v>
-      </c>
-      <c r="M91">
-        <v>0.4</v>
-      </c>
-      <c r="N91">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="O91">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="P91">
-        <v>306</v>
-      </c>
-      <c r="Q91">
-        <v>24</v>
-      </c>
-      <c r="R91">
-        <v>50819.5</v>
-      </c>
-      <c r="S91">
-        <v>0.5</v>
-      </c>
-      <c r="T91">
-        <v>6.12</v>
-      </c>
-      <c r="U91">
-        <v>0.04</v>
-      </c>
-      <c r="V91" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="W91" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="X91">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="Y91">
-        <v>21</v>
-      </c>
-      <c r="Z91" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA91" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>104</v>
       </c>
       <c r="D92" s="6">
-        <v>5015</v>
+        <v>4618</v>
       </c>
       <c r="E92" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="F92" t="s">
         <v>98</v>
       </c>
       <c r="G92">
-        <v>8.3291000000000004</v>
+        <v>8.0729000000000006</v>
       </c>
       <c r="H92">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="I92" t="s">
-        <v>107</v>
+      <c r="I92">
+        <v>104.4</v>
       </c>
       <c r="J92">
-        <v>-37.200000000000003</v>
+        <v>-42.4</v>
       </c>
       <c r="K92">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="L92">
-        <v>45.6</v>
+        <v>55.1</v>
       </c>
       <c r="M92">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="N92">
-        <v>8.0000000000000002E-3</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="O92">
-        <v>1.6E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="P92">
-        <v>70</v>
+        <v>306</v>
       </c>
       <c r="Q92">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="R92">
-        <v>51875</v>
+        <v>50819.5</v>
       </c>
       <c r="S92">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="T92">
-        <v>5.22</v>
+        <v>6.12</v>
       </c>
       <c r="U92">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="V92" s="2">
-        <v>8.2000000000000003E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="W92" s="2">
-        <v>4.0000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="X92">
-        <v>2.5499999999999998</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="Y92">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z92" t="s">
         <v>96</v>
@@ -2275,174 +2234,168 @@
         <v>97</v>
       </c>
     </row>
-    <row r="93" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="7" t="s">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="C93" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D93" s="6">
+        <v>5015</v>
+      </c>
+      <c r="E93" t="s">
+        <v>108</v>
+      </c>
+      <c r="F93" t="s">
+        <v>98</v>
+      </c>
+      <c r="G93">
+        <v>8.3291000000000004</v>
+      </c>
+      <c r="H93">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="I93" t="s">
+        <v>107</v>
+      </c>
+      <c r="J93">
+        <v>-37.200000000000003</v>
+      </c>
+      <c r="K93">
+        <v>0.6</v>
+      </c>
+      <c r="L93">
+        <v>45.6</v>
+      </c>
+      <c r="M93">
+        <v>0.7</v>
+      </c>
+      <c r="N93">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="O93">
+        <v>1.6E-2</v>
+      </c>
+      <c r="P93">
+        <v>70</v>
+      </c>
+      <c r="Q93">
+        <v>150</v>
+      </c>
+      <c r="R93">
+        <v>51875</v>
+      </c>
+      <c r="S93">
+        <v>4</v>
+      </c>
+      <c r="T93">
+        <v>5.22</v>
+      </c>
+      <c r="U93">
+        <v>0.08</v>
+      </c>
+      <c r="V93" s="2">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="W93" s="2">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="X93">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="Y93">
+        <v>22</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA93" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B94" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C94" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D93" s="9">
+      <c r="D94" s="9">
         <v>5733</v>
       </c>
-      <c r="E93" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F93" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="G93" s="10">
+      <c r="E94" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G94" s="10">
         <v>8.7040000000000006</v>
       </c>
-      <c r="H93" s="10">
+      <c r="H94" s="10">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="I93" s="10">
+      <c r="I94" s="10">
         <v>356.8</v>
       </c>
-      <c r="J93" s="10">
+      <c r="J94" s="10">
         <v>-33</v>
       </c>
-      <c r="K93" s="10">
+      <c r="K94" s="10">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L93" s="10">
+      <c r="L94" s="10">
         <v>60</v>
       </c>
-      <c r="M93" s="10">
+      <c r="M94" s="10">
         <v>5</v>
       </c>
-      <c r="N93" s="10">
+      <c r="N94" s="10">
         <v>0.5</v>
       </c>
-      <c r="O93" s="10">
+      <c r="O94" s="10">
         <v>0.05</v>
       </c>
-      <c r="P93" s="10">
+      <c r="P94" s="10">
         <v>120</v>
       </c>
-      <c r="Q93" s="10">
+      <c r="Q94" s="10">
         <v>7</v>
       </c>
-      <c r="R93" s="10">
+      <c r="R94" s="10">
         <v>51606.69</v>
       </c>
-      <c r="S93" s="10">
+      <c r="S94" s="10">
         <v>0.1</v>
       </c>
-      <c r="T93" s="10">
+      <c r="T94" s="10">
         <v>6.2</v>
       </c>
-      <c r="U93" s="10">
+      <c r="U94" s="10">
         <v>0.6</v>
       </c>
-      <c r="V93" s="11">
+      <c r="V94" s="11">
         <v>0.13</v>
       </c>
-      <c r="W93" s="11">
+      <c r="W94" s="11">
         <v>0.03</v>
       </c>
-      <c r="X93" s="10">
+      <c r="X94" s="10">
         <v>5.49</v>
       </c>
-      <c r="Y93" s="10">
+      <c r="Y94" s="10">
         <v>11</v>
       </c>
-      <c r="Z93" s="10" t="s">
+      <c r="Z94" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AA93" s="10" t="s">
+      <c r="AA94" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A94" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D94" s="6">
-        <v>6171</v>
-      </c>
-      <c r="E94" t="s">
-        <v>98</v>
-      </c>
-      <c r="F94" t="s">
-        <v>98</v>
-      </c>
-      <c r="G94">
-        <v>8.8276000000000003</v>
-      </c>
-      <c r="H94">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="I94">
-        <v>125.4</v>
-      </c>
-      <c r="J94">
-        <v>-41.9</v>
-      </c>
-      <c r="K94">
-        <v>0.3</v>
-      </c>
-      <c r="L94">
-        <v>35.9</v>
-      </c>
-      <c r="M94">
-        <v>0.4</v>
-      </c>
-      <c r="N94">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="O94">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="P94">
-        <v>33</v>
-      </c>
-      <c r="Q94">
-        <v>24</v>
-      </c>
-      <c r="R94">
-        <v>54189.8</v>
-      </c>
-      <c r="S94">
-        <v>0.6</v>
-      </c>
-      <c r="T94">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="U94">
-        <v>0.05</v>
-      </c>
-      <c r="V94" s="2">
-        <v>4.24E-2</v>
-      </c>
-      <c r="W94" s="2">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="X94">
-        <v>0.97</v>
-      </c>
-      <c r="Y94">
-        <v>14</v>
-      </c>
-      <c r="Z94" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA94" t="s">
-        <v>97</v>
-      </c>
-    </row>
     <row r="95" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A95" s="13" t="s">
+      <c r="A95" s="16" t="s">
         <v>113</v>
       </c>
       <c r="B95" s="5" t="s">
@@ -2452,7 +2405,7 @@
         <v>104</v>
       </c>
       <c r="D95" s="6">
-        <v>5463</v>
+        <v>6171</v>
       </c>
       <c r="E95" t="s">
         <v>98</v>
@@ -2461,61 +2414,61 @@
         <v>98</v>
       </c>
       <c r="G95">
-        <v>9.4648000000000003</v>
+        <v>8.8276000000000003</v>
       </c>
       <c r="H95">
-        <v>1E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="I95">
-        <v>129.4</v>
+        <v>125.4</v>
       </c>
       <c r="J95">
-        <v>-41.81</v>
+        <v>-41.9</v>
       </c>
       <c r="K95">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="L95">
-        <v>6.24</v>
+        <v>35.9</v>
       </c>
       <c r="M95">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="N95">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="O95">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="P95">
+        <v>33</v>
+      </c>
+      <c r="Q95">
+        <v>24</v>
+      </c>
+      <c r="R95">
+        <v>54189.8</v>
+      </c>
+      <c r="S95">
+        <v>0.6</v>
+      </c>
+      <c r="T95">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="U95">
         <v>0.05</v>
       </c>
-      <c r="O95">
-        <v>0.03</v>
-      </c>
-      <c r="P95">
-        <v>320</v>
-      </c>
-      <c r="Q95">
-        <v>30</v>
-      </c>
-      <c r="R95">
-        <v>50976.5</v>
-      </c>
-      <c r="S95">
-        <v>0.9</v>
-      </c>
-      <c r="T95">
-        <v>0.81</v>
-      </c>
-      <c r="U95">
-        <v>0.03</v>
-      </c>
       <c r="V95" s="2">
-        <v>2.3800000000000001E-4</v>
+        <v>4.24E-2</v>
       </c>
       <c r="W95" s="2">
-        <v>2.5000000000000001E-5</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="X95">
-        <v>0.59</v>
+        <v>0.97</v>
       </c>
       <c r="Y95">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="Z95" t="s">
         <v>96</v>
@@ -2524,18 +2477,18 @@
         <v>97</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="13" t="s">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A96" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B96" s="24" t="s">
+      <c r="B96" s="5" t="s">
         <v>112</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>104</v>
       </c>
       <c r="D96" s="6">
-        <v>5601</v>
+        <v>5463</v>
       </c>
       <c r="E96" t="s">
         <v>98</v>
@@ -2544,61 +2497,61 @@
         <v>98</v>
       </c>
       <c r="G96">
-        <v>10.014200000000001</v>
+        <v>9.4648000000000003</v>
       </c>
       <c r="H96">
-        <v>1.1999999999999999E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="I96">
-        <v>132.6</v>
+        <v>129.4</v>
       </c>
       <c r="J96">
-        <v>-41.19</v>
+        <v>-41.81</v>
       </c>
       <c r="K96">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="L96">
-        <v>5.67</v>
+        <v>6.24</v>
       </c>
       <c r="M96">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="N96">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="O96">
         <v>0.03</v>
       </c>
       <c r="P96">
-        <v>58</v>
+        <v>320</v>
       </c>
       <c r="Q96">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="R96">
-        <v>51162.9</v>
+        <v>50976.5</v>
       </c>
       <c r="S96">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="T96">
-        <v>0.77900000000000003</v>
+        <v>0.81</v>
       </c>
       <c r="U96">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="V96" s="2">
-        <v>1.8699999999999999E-4</v>
+        <v>2.3800000000000001E-4</v>
       </c>
       <c r="W96" s="2">
-        <v>1.4E-5</v>
+        <v>2.5000000000000001E-5</v>
       </c>
       <c r="X96">
-        <v>0.56999999999999995</v>
+        <v>0.59</v>
       </c>
       <c r="Y96">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="Z96" t="s">
         <v>96</v>
@@ -2607,174 +2560,174 @@
         <v>97</v>
       </c>
     </row>
-    <row r="97" spans="1:27" s="19" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="22" t="s">
-        <v>114</v>
+    <row r="97" spans="1:27" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="16" t="s">
+        <v>113</v>
       </c>
       <c r="B97" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="C97" s="20" t="s">
+      <c r="C97" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D97" s="19">
+      <c r="D97" s="6">
+        <v>5601</v>
+      </c>
+      <c r="E97" t="s">
+        <v>98</v>
+      </c>
+      <c r="F97" t="s">
+        <v>98</v>
+      </c>
+      <c r="G97">
+        <v>10.014200000000001</v>
+      </c>
+      <c r="H97">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="I97">
+        <v>132.6</v>
+      </c>
+      <c r="J97">
+        <v>-41.19</v>
+      </c>
+      <c r="K97">
+        <v>0.1</v>
+      </c>
+      <c r="L97">
+        <v>5.67</v>
+      </c>
+      <c r="M97">
+        <v>0.1</v>
+      </c>
+      <c r="N97">
+        <v>0.09</v>
+      </c>
+      <c r="O97">
+        <v>0.03</v>
+      </c>
+      <c r="P97">
+        <v>58</v>
+      </c>
+      <c r="Q97">
+        <v>16</v>
+      </c>
+      <c r="R97">
+        <v>51162.9</v>
+      </c>
+      <c r="S97">
+        <v>0.4</v>
+      </c>
+      <c r="T97">
+        <v>0.77900000000000003</v>
+      </c>
+      <c r="U97">
+        <v>0.02</v>
+      </c>
+      <c r="V97" s="2">
+        <v>1.8699999999999999E-4</v>
+      </c>
+      <c r="W97" s="2">
+        <v>1.4E-5</v>
+      </c>
+      <c r="X97">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="Y97">
+        <v>47</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA97" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:27" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B98" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C98" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D98" s="18">
         <v>4904</v>
       </c>
-      <c r="E97" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="F97" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="G97" s="19">
+      <c r="E98" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F98" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="G98" s="18">
         <v>10.185</v>
       </c>
-      <c r="H97" s="19">
+      <c r="H98" s="18">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I97" s="19">
+      <c r="I98" s="18">
         <v>100.5</v>
       </c>
-      <c r="J97" s="19">
+      <c r="J98" s="18">
         <v>-42.7</v>
       </c>
-      <c r="K97" s="19">
+      <c r="K98" s="18">
         <v>0.3</v>
       </c>
-      <c r="L97" s="19">
+      <c r="L98" s="18">
         <v>11.2</v>
       </c>
-      <c r="M97" s="19">
+      <c r="M98" s="18">
         <v>0.5</v>
       </c>
-      <c r="N97" s="19">
+      <c r="N98" s="18">
         <v>0.37</v>
       </c>
-      <c r="O97" s="19">
+      <c r="O98" s="18">
         <v>0.04</v>
       </c>
-      <c r="P97" s="19">
+      <c r="P98" s="18">
         <v>253</v>
       </c>
-      <c r="Q97" s="19">
+      <c r="Q98" s="18">
         <v>7</v>
       </c>
-      <c r="R97" s="19">
+      <c r="R98" s="18">
         <v>50894.6</v>
       </c>
-      <c r="S97" s="19">
+      <c r="S98" s="18">
         <v>0.16</v>
       </c>
-      <c r="T97" s="19">
+      <c r="T98" s="18">
         <v>1.45</v>
       </c>
-      <c r="U97" s="19">
+      <c r="U98" s="18">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="V97" s="21">
+      <c r="V98" s="20">
         <v>1.1800000000000001E-3</v>
       </c>
-      <c r="W97" s="21">
+      <c r="W98" s="20">
         <v>1.6000000000000001E-4</v>
       </c>
-      <c r="X97" s="19">
+      <c r="X98" s="18">
         <v>1.26</v>
       </c>
-      <c r="Y97" s="19">
+      <c r="Y98" s="18">
         <v>28</v>
       </c>
-      <c r="Z97" s="19" t="s">
+      <c r="Z98" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="AA97" s="19" t="s">
+      <c r="AA98" s="18" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A98" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D98" s="6">
-        <v>4289</v>
-      </c>
-      <c r="E98" t="s">
-        <v>98</v>
-      </c>
-      <c r="F98" t="s">
-        <v>98</v>
-      </c>
-      <c r="G98">
-        <v>11.4877</v>
-      </c>
-      <c r="H98">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="I98">
-        <v>116.2</v>
-      </c>
-      <c r="J98">
-        <v>-42.62</v>
-      </c>
-      <c r="K98">
-        <v>0.23</v>
-      </c>
-      <c r="L98">
-        <v>40.799999999999997</v>
-      </c>
-      <c r="M98">
-        <v>0.3</v>
-      </c>
-      <c r="N98">
-        <v>1.2E-2</v>
-      </c>
-      <c r="O98">
-        <v>0.01</v>
-      </c>
-      <c r="P98">
-        <v>200</v>
-      </c>
-      <c r="Q98">
-        <v>50</v>
-      </c>
-      <c r="R98">
-        <v>50744.5</v>
-      </c>
-      <c r="S98">
-        <v>1.7</v>
-      </c>
-      <c r="T98">
-        <v>6.44</v>
-      </c>
-      <c r="U98">
-        <v>0.05</v>
-      </c>
-      <c r="V98" s="2">
-        <v>8.0699999999999994E-2</v>
-      </c>
-      <c r="W98" s="2">
-        <v>2E-3</v>
-      </c>
-      <c r="X98">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="Y98">
-        <v>25</v>
-      </c>
-      <c r="Z98" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA98" t="s">
-        <v>97</v>
-      </c>
-    </row>
     <row r="99" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A99" s="13" t="s">
+      <c r="A99" s="16" t="s">
         <v>113</v>
       </c>
       <c r="B99" s="5" t="s">
@@ -2784,7 +2737,7 @@
         <v>104</v>
       </c>
       <c r="D99" s="6">
-        <v>5738</v>
+        <v>4289</v>
       </c>
       <c r="E99" t="s">
         <v>98</v>
@@ -2793,61 +2746,61 @@
         <v>98</v>
       </c>
       <c r="G99">
-        <v>13.049200000000001</v>
+        <v>11.4877</v>
       </c>
       <c r="H99">
-        <v>8.0000000000000004E-4</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="I99">
-        <v>272.3</v>
+        <v>116.2</v>
       </c>
       <c r="J99">
-        <v>-42.33</v>
+        <v>-42.62</v>
       </c>
       <c r="K99">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="L99">
-        <v>5.92</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="M99">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N99">
-        <v>0.02</v>
+        <v>1.2E-2</v>
       </c>
       <c r="O99">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="P99">
         <v>200</v>
       </c>
       <c r="Q99">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="R99">
-        <v>51403</v>
+        <v>50744.5</v>
       </c>
       <c r="S99">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="T99">
-        <v>1.06</v>
+        <v>6.44</v>
       </c>
       <c r="U99">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="V99" s="2">
-        <v>2.7999999999999998E-4</v>
+        <v>8.0699999999999994E-2</v>
       </c>
       <c r="W99" s="2">
-        <v>3.0000000000000001E-5</v>
+        <v>2E-3</v>
       </c>
       <c r="X99">
-        <v>0.74</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="Y99">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Z99" t="s">
         <v>96</v>
@@ -2856,174 +2809,174 @@
         <v>97</v>
       </c>
     </row>
-    <row r="100" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="14" t="s">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A100" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="B100" s="12" t="s">
+      <c r="B100" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="C100" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D100" s="6">
+        <v>5738</v>
+      </c>
+      <c r="E100" t="s">
+        <v>98</v>
+      </c>
+      <c r="F100" t="s">
+        <v>98</v>
+      </c>
+      <c r="G100">
+        <v>13.049200000000001</v>
+      </c>
+      <c r="H100">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="I100">
+        <v>272.3</v>
+      </c>
+      <c r="J100">
+        <v>-42.33</v>
+      </c>
+      <c r="K100">
+        <v>0.15</v>
+      </c>
+      <c r="L100">
+        <v>5.92</v>
+      </c>
+      <c r="M100">
+        <v>0.2</v>
+      </c>
+      <c r="N100">
+        <v>0.02</v>
+      </c>
+      <c r="O100">
+        <v>0.04</v>
+      </c>
+      <c r="P100">
+        <v>200</v>
+      </c>
+      <c r="Q100">
+        <v>80</v>
+      </c>
+      <c r="R100">
+        <v>51403</v>
+      </c>
+      <c r="S100">
+        <v>3</v>
+      </c>
+      <c r="T100">
+        <v>1.06</v>
+      </c>
+      <c r="U100">
+        <v>0.04</v>
+      </c>
+      <c r="V100" s="2">
+        <v>2.7999999999999998E-4</v>
+      </c>
+      <c r="W100" s="2">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="X100">
+        <v>0.74</v>
+      </c>
+      <c r="Y100">
+        <v>29</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA100" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C101" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D100" s="9">
+      <c r="D101" s="9">
         <v>8775</v>
       </c>
-      <c r="E100" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F100" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="G100" s="10">
+      <c r="E101" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G101" s="10">
         <v>14.57</v>
       </c>
-      <c r="H100" s="10">
+      <c r="H101" s="10">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I100" s="10">
+      <c r="I101" s="10">
         <v>50.8</v>
       </c>
-      <c r="J100" s="10">
+      <c r="J101" s="10">
         <v>-23.18</v>
       </c>
-      <c r="K100" s="10">
+      <c r="K101" s="10">
         <v>0.22</v>
       </c>
-      <c r="L100" s="10">
+      <c r="L101" s="10">
         <v>8.8000000000000007</v>
       </c>
-      <c r="M100" s="10">
+      <c r="M101" s="10">
         <v>0.3</v>
       </c>
-      <c r="N100" s="10">
+      <c r="N101" s="10">
         <v>0.2</v>
       </c>
-      <c r="O100" s="10">
+      <c r="O101" s="10">
         <v>0.04</v>
       </c>
-      <c r="P100" s="10">
+      <c r="P101" s="10">
         <v>74</v>
       </c>
-      <c r="Q100" s="10">
+      <c r="Q101" s="10">
         <v>9</v>
       </c>
-      <c r="R100" s="10">
+      <c r="R101" s="10">
         <v>50890.400000000001</v>
       </c>
-      <c r="S100" s="10">
+      <c r="S101" s="10">
         <v>0.3</v>
       </c>
-      <c r="T100" s="10">
+      <c r="T101" s="10">
         <v>1.72</v>
       </c>
-      <c r="U100" s="10">
+      <c r="U101" s="10">
         <v>0.06</v>
       </c>
-      <c r="V100" s="11">
+      <c r="V101" s="11">
         <v>9.6000000000000002E-4</v>
       </c>
-      <c r="W100" s="11">
+      <c r="W101" s="11">
         <v>1E-4</v>
       </c>
-      <c r="X100" s="10">
+      <c r="X101" s="10">
         <v>0.9</v>
       </c>
-      <c r="Y100" s="10">
+      <c r="Y101" s="10">
         <v>19</v>
       </c>
-      <c r="Z100" s="10" t="s">
+      <c r="Z101" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AA100" s="10" t="s">
+      <c r="AA101" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A101" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D101" s="6">
-        <v>6292</v>
-      </c>
-      <c r="E101" t="s">
-        <v>98</v>
-      </c>
-      <c r="F101" t="s">
-        <v>98</v>
-      </c>
-      <c r="G101">
-        <v>14.598800000000001</v>
-      </c>
-      <c r="H101">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="I101">
-        <v>70.099999999999994</v>
-      </c>
-      <c r="J101">
-        <v>-43.31</v>
-      </c>
-      <c r="K101">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="L101">
-        <v>30.99</v>
-      </c>
-      <c r="M101">
-        <v>0.19</v>
-      </c>
-      <c r="N101">
-        <v>1.2E-2</v>
-      </c>
-      <c r="O101">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="P101">
-        <v>20</v>
-      </c>
-      <c r="Q101">
-        <v>30</v>
-      </c>
-      <c r="R101">
-        <v>50859.9</v>
-      </c>
-      <c r="S101">
-        <v>1.3</v>
-      </c>
-      <c r="T101">
-        <v>6.22</v>
-      </c>
-      <c r="U101">
-        <v>0.04</v>
-      </c>
-      <c r="V101" s="2">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="W101" s="2">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="X101">
-        <v>0.62</v>
-      </c>
-      <c r="Y101">
-        <v>21</v>
-      </c>
-      <c r="Z101" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA101" t="s">
-        <v>97</v>
-      </c>
-    </row>
     <row r="102" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A102" s="13" t="s">
+      <c r="A102" s="5" t="s">
         <v>113</v>
       </c>
       <c r="B102" s="5" t="s">
@@ -3032,8 +2985,8 @@
       <c r="C102" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D102">
-        <v>4965</v>
+      <c r="D102" s="6">
+        <v>6292</v>
       </c>
       <c r="E102" t="s">
         <v>98</v>
@@ -3042,61 +2995,61 @@
         <v>98</v>
       </c>
       <c r="G102">
-        <v>14.9222</v>
+        <v>14.598800000000001</v>
       </c>
       <c r="H102">
-        <v>5.0000000000000001E-4</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="I102">
-        <v>257.3</v>
+        <v>70.099999999999994</v>
       </c>
       <c r="J102">
-        <v>-43.11</v>
+        <v>-43.31</v>
       </c>
       <c r="K102">
-        <v>0.17</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="L102">
-        <v>17.38</v>
+        <v>30.99</v>
       </c>
       <c r="M102">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="N102">
-        <v>0.01</v>
+        <v>1.2E-2</v>
       </c>
       <c r="O102">
-        <v>1.4E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="P102">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="Q102">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="R102">
-        <v>52346</v>
+        <v>50859.9</v>
       </c>
       <c r="S102">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="T102">
-        <v>3.57</v>
+        <v>6.22</v>
       </c>
       <c r="U102">
         <v>0.04</v>
       </c>
       <c r="V102" s="2">
-        <v>8.0999999999999996E-3</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="W102" s="2">
-        <v>2.9999999999999997E-4</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>0.62</v>
       </c>
       <c r="Y102">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="Z102" t="s">
         <v>96</v>
@@ -3106,7 +3059,7 @@
       </c>
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A103" s="13" t="s">
+      <c r="A103" s="5" t="s">
         <v>113</v>
       </c>
       <c r="B103" s="5" t="s">
@@ -3116,7 +3069,7 @@
         <v>104</v>
       </c>
       <c r="D103">
-        <v>5797</v>
+        <v>4965</v>
       </c>
       <c r="E103" t="s">
         <v>98</v>
@@ -3125,61 +3078,61 @@
         <v>98</v>
       </c>
       <c r="G103">
-        <v>14.990600000000001</v>
+        <v>14.9222</v>
       </c>
       <c r="H103">
-        <v>8.9999999999999998E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="I103">
-        <v>98.8</v>
+        <v>257.3</v>
       </c>
       <c r="J103">
-        <v>-42.67</v>
+        <v>-43.11</v>
       </c>
       <c r="K103">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="L103">
-        <v>19.53</v>
+        <v>17.38</v>
       </c>
       <c r="M103">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="N103">
-        <v>2.3E-2</v>
+        <v>0.01</v>
       </c>
       <c r="O103">
-        <v>1.0999999999999999E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="P103">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="Q103">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="R103">
-        <v>52033.9</v>
+        <v>52346</v>
       </c>
       <c r="S103">
-        <v>1.1000000000000001</v>
+        <v>3</v>
       </c>
       <c r="T103">
-        <v>4.0199999999999996</v>
+        <v>3.57</v>
       </c>
       <c r="U103">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="V103" s="2">
-        <v>1.1599999999999999E-2</v>
+        <v>8.0999999999999996E-3</v>
       </c>
       <c r="W103" s="2">
-        <v>4.0000000000000002E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="X103">
-        <v>0.69</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="Z103" t="s">
         <v>96</v>
@@ -3189,6 +3142,9 @@
       </c>
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A104" s="5" t="s">
+        <v>113</v>
+      </c>
       <c r="B104" s="5" t="s">
         <v>112</v>
       </c>
@@ -3196,7 +3152,7 @@
         <v>104</v>
       </c>
       <c r="D104">
-        <v>5647</v>
+        <v>5797</v>
       </c>
       <c r="E104" t="s">
         <v>98</v>
@@ -3205,61 +3161,61 @@
         <v>98</v>
       </c>
       <c r="G104">
-        <v>15.5528</v>
+        <v>14.990600000000001</v>
       </c>
       <c r="H104">
-        <v>1.1000000000000001E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="I104">
-        <v>57.3</v>
+        <v>98.8</v>
       </c>
       <c r="J104">
-        <v>-43.5</v>
+        <v>-42.67</v>
       </c>
       <c r="K104">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="L104">
-        <v>45.5</v>
+        <v>19.53</v>
       </c>
       <c r="M104">
-        <v>0.7</v>
+        <v>0.23</v>
       </c>
       <c r="N104">
-        <v>0.28499999999999998</v>
+        <v>2.3E-2</v>
       </c>
       <c r="O104">
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="P104">
-        <v>55</v>
+        <v>260</v>
       </c>
       <c r="Q104">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="R104">
-        <v>54123.82</v>
+        <v>52033.9</v>
       </c>
       <c r="S104">
-        <v>0.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="T104">
-        <v>9.32</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="U104">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="V104" s="2">
-        <v>0.13300000000000001</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="W104" s="2">
-        <v>6.0000000000000001E-3</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="X104">
-        <v>1.17</v>
+        <v>0.69</v>
       </c>
       <c r="Y104">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="Z104" t="s">
         <v>96</v>
@@ -3276,7 +3232,7 @@
         <v>104</v>
       </c>
       <c r="D105">
-        <v>880</v>
+        <v>5647</v>
       </c>
       <c r="E105" t="s">
         <v>98</v>
@@ -3285,61 +3241,61 @@
         <v>98</v>
       </c>
       <c r="G105">
-        <v>20.292000000000002</v>
+        <v>15.5528</v>
       </c>
       <c r="H105">
-        <v>4.0000000000000001E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="I105">
-        <v>42.1</v>
+        <v>57.3</v>
       </c>
       <c r="J105">
-        <v>-41.71</v>
+        <v>-43.5</v>
       </c>
       <c r="K105">
-        <v>0.24</v>
+        <v>0.6</v>
       </c>
       <c r="L105">
-        <v>15.4</v>
+        <v>45.5</v>
       </c>
       <c r="M105">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="N105">
-        <v>0.21299999999999999</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="O105">
-        <v>1.6E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="P105">
-        <v>238</v>
+        <v>55</v>
       </c>
       <c r="Q105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R105">
-        <v>50715.29</v>
+        <v>54123.82</v>
       </c>
       <c r="S105">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
       <c r="T105">
-        <v>4.21</v>
+        <v>9.32</v>
       </c>
       <c r="U105">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="V105" s="2">
-        <v>7.1999999999999998E-3</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="W105" s="2">
-        <v>4.0000000000000002E-4</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="X105">
-        <v>0.77</v>
+        <v>1.17</v>
       </c>
       <c r="Y105">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="Z105" t="s">
         <v>96</v>
@@ -3348,157 +3304,160 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:27" s="19" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C106" s="20" t="s">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B106" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D106" s="19">
+      <c r="D106">
+        <v>880</v>
+      </c>
+      <c r="E106" t="s">
+        <v>98</v>
+      </c>
+      <c r="F106" t="s">
+        <v>98</v>
+      </c>
+      <c r="G106">
+        <v>20.292000000000002</v>
+      </c>
+      <c r="H106">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="I106">
+        <v>42.1</v>
+      </c>
+      <c r="J106">
+        <v>-41.71</v>
+      </c>
+      <c r="K106">
+        <v>0.24</v>
+      </c>
+      <c r="L106">
+        <v>15.4</v>
+      </c>
+      <c r="M106">
+        <v>0.3</v>
+      </c>
+      <c r="N106">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="O106">
+        <v>1.6E-2</v>
+      </c>
+      <c r="P106">
+        <v>238</v>
+      </c>
+      <c r="Q106">
+        <v>4</v>
+      </c>
+      <c r="R106">
+        <v>50715.29</v>
+      </c>
+      <c r="S106">
+        <v>0.21</v>
+      </c>
+      <c r="T106">
+        <v>4.21</v>
+      </c>
+      <c r="U106">
+        <v>0.08</v>
+      </c>
+      <c r="V106" s="2">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="W106" s="2">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="X106">
+        <v>0.77</v>
+      </c>
+      <c r="Y106">
+        <v>31</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA106" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="107" spans="1:27" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C107" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D107" s="18">
         <v>4710</v>
       </c>
-      <c r="E106" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="F106" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="G106" s="19">
+      <c r="E107" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F107" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="G107" s="18">
         <v>21.340699999999998</v>
       </c>
-      <c r="H106" s="19">
+      <c r="H107" s="18">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="I106" s="19">
+      <c r="I107" s="18">
         <v>203.7</v>
       </c>
-      <c r="J106" s="19">
+      <c r="J107" s="18">
         <v>-45.7</v>
       </c>
-      <c r="K106" s="19">
+      <c r="K107" s="18">
         <v>0.3</v>
       </c>
-      <c r="L106" s="19">
+      <c r="L107" s="18">
         <v>16.899999999999999</v>
       </c>
-      <c r="M106" s="19">
+      <c r="M107" s="18">
         <v>1.5</v>
       </c>
-      <c r="N106" s="19">
+      <c r="N107" s="18">
         <v>0.67500000000000004</v>
       </c>
-      <c r="O106" s="19">
+      <c r="O107" s="18">
         <v>2.4E-2</v>
       </c>
-      <c r="P106" s="19">
+      <c r="P107" s="18">
         <v>340</v>
       </c>
-      <c r="Q106" s="19">
+      <c r="Q107" s="18">
         <v>3</v>
       </c>
-      <c r="R106" s="19">
+      <c r="R107" s="18">
         <v>52412.34</v>
       </c>
-      <c r="S106" s="19">
+      <c r="S107" s="18">
         <v>0.16</v>
       </c>
-      <c r="T106" s="19">
+      <c r="T107" s="18">
         <v>3.7</v>
       </c>
-      <c r="U106" s="19">
+      <c r="U107" s="18">
         <v>0.3</v>
       </c>
-      <c r="V106" s="21">
+      <c r="V107" s="20">
         <v>4.3E-3</v>
       </c>
-      <c r="W106" s="21">
+      <c r="W107" s="20">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="X106" s="19">
+      <c r="X107" s="18">
         <v>1.18</v>
       </c>
-      <c r="Y106" s="19">
+      <c r="Y107" s="18">
         <v>37</v>
       </c>
-      <c r="Z106" s="19" t="s">
+      <c r="Z107" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="AA106" s="19" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="107" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C107" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D107" s="10">
-        <v>5110</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F107" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="G107" s="10">
-        <v>21.360199999999999</v>
-      </c>
-      <c r="H107" s="10">
-        <v>1.9E-3</v>
-      </c>
-      <c r="I107" s="10">
-        <v>163.19999999999999</v>
-      </c>
-      <c r="J107" s="10">
-        <v>-38</v>
-      </c>
-      <c r="K107" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="L107" s="10">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="M107" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="N107" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="O107" s="10">
-        <v>0.03</v>
-      </c>
-      <c r="P107" s="10">
-        <v>195</v>
-      </c>
-      <c r="Q107" s="10">
-        <v>16</v>
-      </c>
-      <c r="R107" s="10">
-        <v>51197.2</v>
-      </c>
-      <c r="S107" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="T107" s="10">
-        <v>11.1</v>
-      </c>
-      <c r="U107" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="V107" s="11">
-        <v>0.11799999999999999</v>
-      </c>
-      <c r="W107" s="11">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="X107" s="10">
-        <v>3.07</v>
-      </c>
-      <c r="Y107" s="10">
-        <v>22</v>
-      </c>
-      <c r="Z107" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA107" s="10" t="s">
+      <c r="AA107" s="18" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3507,7 +3466,7 @@
         <v>73</v>
       </c>
       <c r="D108" s="10">
-        <v>736</v>
+        <v>5110</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>98</v>
@@ -3516,61 +3475,61 @@
         <v>98</v>
       </c>
       <c r="G108" s="10">
-        <v>24.004000000000001</v>
+        <v>21.360199999999999</v>
       </c>
       <c r="H108" s="10">
-        <v>5.0000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="I108" s="10">
-        <v>50.8</v>
+        <v>163.19999999999999</v>
       </c>
       <c r="J108" s="10">
-        <v>-50.5</v>
+        <v>-38</v>
       </c>
       <c r="K108" s="10">
-        <v>0.11</v>
+        <v>0.7</v>
       </c>
       <c r="L108" s="10">
-        <v>7.21</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="M108" s="10">
-        <v>0.16</v>
+        <v>0.9</v>
       </c>
       <c r="N108" s="10">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
       <c r="O108" s="10">
-        <v>1.9E-2</v>
+        <v>0.03</v>
       </c>
       <c r="P108" s="10">
-        <v>240</v>
+        <v>195</v>
       </c>
       <c r="Q108" s="10">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="R108" s="10">
-        <v>52039.8</v>
+        <v>51197.2</v>
       </c>
       <c r="S108" s="10">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="T108" s="10">
-        <v>2.33</v>
+        <v>11.1</v>
       </c>
       <c r="U108" s="10">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="V108" s="11">
-        <v>8.7000000000000001E-4</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="W108" s="11">
-        <v>6.0000000000000002E-5</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="X108" s="10">
-        <v>0.42</v>
+        <v>3.07</v>
       </c>
       <c r="Y108" s="10">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Z108" s="10" t="s">
         <v>96</v>
@@ -3579,95 +3538,92 @@
         <v>97</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B109" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D109">
-        <v>4999</v>
-      </c>
-      <c r="E109" t="s">
-        <v>98</v>
-      </c>
-      <c r="F109" t="s">
-        <v>98</v>
-      </c>
-      <c r="G109">
-        <v>24.366</v>
-      </c>
-      <c r="H109">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="I109">
-        <v>30.4</v>
-      </c>
-      <c r="J109">
-        <v>-41.6</v>
-      </c>
-      <c r="K109">
+    <row r="109" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C109" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D109" s="10">
+        <v>736</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F109" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G109" s="10">
+        <v>24.004000000000001</v>
+      </c>
+      <c r="H109" s="10">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I109" s="10">
+        <v>50.8</v>
+      </c>
+      <c r="J109" s="10">
+        <v>-50.5</v>
+      </c>
+      <c r="K109" s="10">
+        <v>0.11</v>
+      </c>
+      <c r="L109" s="10">
+        <v>7.21</v>
+      </c>
+      <c r="M109" s="10">
+        <v>0.16</v>
+      </c>
+      <c r="N109" s="10">
+        <v>0.21</v>
+      </c>
+      <c r="O109" s="10">
+        <v>1.9E-2</v>
+      </c>
+      <c r="P109" s="10">
+        <v>240</v>
+      </c>
+      <c r="Q109" s="10">
+        <v>6</v>
+      </c>
+      <c r="R109" s="10">
+        <v>52039.8</v>
+      </c>
+      <c r="S109" s="10">
         <v>0.4</v>
       </c>
-      <c r="L109">
-        <v>14.6</v>
-      </c>
-      <c r="M109">
-        <v>0.6</v>
-      </c>
-      <c r="N109">
-        <v>0.32</v>
-      </c>
-      <c r="O109">
-        <v>0.04</v>
-      </c>
-      <c r="P109">
-        <v>248</v>
-      </c>
-      <c r="Q109">
-        <v>5</v>
-      </c>
-      <c r="R109">
-        <v>50867.6</v>
-      </c>
-      <c r="S109">
-        <v>0.4</v>
-      </c>
-      <c r="T109">
-        <v>4.62</v>
-      </c>
-      <c r="U109">
-        <v>0.21</v>
-      </c>
-      <c r="V109" s="2">
-        <v>6.6E-3</v>
-      </c>
-      <c r="W109" s="2">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="X109">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="Y109">
-        <v>24</v>
-      </c>
-      <c r="Z109" t="s">
+      <c r="T109" s="10">
+        <v>2.33</v>
+      </c>
+      <c r="U109" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="V109" s="11">
+        <v>8.7000000000000001E-4</v>
+      </c>
+      <c r="W109" s="11">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="X109" s="10">
+        <v>0.42</v>
+      </c>
+      <c r="Y109" s="10">
+        <v>17</v>
+      </c>
+      <c r="Z109" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AA109" t="s">
+      <c r="AA109" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B110" s="15" t="s">
-        <v>112</v>
+    <row r="110" spans="1:27" ht="29" x14ac:dyDescent="0.35">
+      <c r="B110" s="24" t="s">
+        <v>125</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>104</v>
       </c>
       <c r="D110">
-        <v>4080</v>
+        <v>4999</v>
       </c>
       <c r="E110" t="s">
         <v>98</v>
@@ -3676,61 +3632,61 @@
         <v>98</v>
       </c>
       <c r="G110">
-        <v>32.197000000000003</v>
+        <v>24.366</v>
       </c>
       <c r="H110">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="I110">
-        <v>31.7</v>
+        <v>30.4</v>
       </c>
       <c r="J110">
-        <v>-42.45</v>
+        <v>-41.6</v>
       </c>
       <c r="K110">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="L110">
-        <v>20.7</v>
+        <v>14.6</v>
       </c>
       <c r="M110">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N110">
-        <v>6.9000000000000006E-2</v>
+        <v>0.32</v>
       </c>
       <c r="O110">
-        <v>1.4999999999999999E-2</v>
+        <v>0.04</v>
       </c>
       <c r="P110">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="Q110">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="R110">
-        <v>50884.6</v>
+        <v>50867.6</v>
       </c>
       <c r="S110">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="T110">
-        <v>9.16</v>
+        <v>4.62</v>
       </c>
       <c r="U110">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="V110" s="2">
-        <v>2.9600000000000001E-2</v>
+        <v>6.6E-3</v>
       </c>
       <c r="W110" s="2">
-        <v>1.4E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="X110">
-        <v>1.05</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="Y110">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z110" t="s">
         <v>96</v>
@@ -3740,14 +3696,14 @@
       </c>
     </row>
     <row r="111" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B111" s="25" t="s">
+      <c r="B111" s="14" t="s">
         <v>112</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>104</v>
       </c>
       <c r="D111">
-        <v>5040</v>
+        <v>4080</v>
       </c>
       <c r="E111" t="s">
         <v>98</v>
@@ -3756,61 +3712,61 @@
         <v>98</v>
       </c>
       <c r="G111">
-        <v>33.454999999999998</v>
+        <v>32.197000000000003</v>
       </c>
       <c r="H111">
-        <v>3.0000000000000001E-3</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="I111">
-        <v>104.3</v>
+        <v>31.7</v>
       </c>
       <c r="J111">
-        <v>-43.79</v>
+        <v>-42.45</v>
       </c>
       <c r="K111">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="L111">
-        <v>6.91</v>
+        <v>20.7</v>
       </c>
       <c r="M111">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="N111">
-        <v>0.28999999999999998</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="O111">
-        <v>0.03</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="P111">
-        <v>209</v>
+        <v>264</v>
       </c>
       <c r="Q111">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="R111">
-        <v>51356.4</v>
+        <v>50884.6</v>
       </c>
       <c r="S111">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="T111">
-        <v>3.05</v>
+        <v>9.16</v>
       </c>
       <c r="U111">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="V111" s="2">
-        <v>1.01E-3</v>
+        <v>2.9600000000000001E-2</v>
       </c>
       <c r="W111" s="2">
-        <v>1.1E-4</v>
+        <v>1.4E-3</v>
       </c>
       <c r="X111">
-        <v>0.45</v>
+        <v>1.05</v>
       </c>
       <c r="Y111">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Z111" t="s">
         <v>96</v>
@@ -3819,157 +3775,160 @@
         <v>97</v>
       </c>
     </row>
-    <row r="112" spans="1:27" s="19" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C112" s="20" t="s">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B112" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D112" s="19">
+      <c r="D112">
+        <v>5040</v>
+      </c>
+      <c r="E112" t="s">
+        <v>98</v>
+      </c>
+      <c r="F112" t="s">
+        <v>98</v>
+      </c>
+      <c r="G112">
+        <v>33.454999999999998</v>
+      </c>
+      <c r="H112">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I112">
+        <v>104.3</v>
+      </c>
+      <c r="J112">
+        <v>-43.79</v>
+      </c>
+      <c r="K112">
+        <v>0.16</v>
+      </c>
+      <c r="L112">
+        <v>6.91</v>
+      </c>
+      <c r="M112">
+        <v>0.24</v>
+      </c>
+      <c r="N112">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O112">
+        <v>0.03</v>
+      </c>
+      <c r="P112">
+        <v>209</v>
+      </c>
+      <c r="Q112">
+        <v>6</v>
+      </c>
+      <c r="R112">
+        <v>51356.4</v>
+      </c>
+      <c r="S112">
+        <v>0.5</v>
+      </c>
+      <c r="T112">
+        <v>3.05</v>
+      </c>
+      <c r="U112">
+        <v>0.11</v>
+      </c>
+      <c r="V112" s="2">
+        <v>1.01E-3</v>
+      </c>
+      <c r="W112" s="2">
+        <v>1.1E-4</v>
+      </c>
+      <c r="X112">
+        <v>0.45</v>
+      </c>
+      <c r="Y112">
+        <v>15</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA112" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="113" spans="3:27" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C113" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D113" s="18">
         <v>4673</v>
       </c>
-      <c r="E112" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="F112" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="G112" s="19">
+      <c r="E113" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F113" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="G113" s="18">
         <v>48.27</v>
       </c>
-      <c r="H112" s="19">
+      <c r="H113" s="18">
         <v>0.06</v>
       </c>
-      <c r="I112" s="19">
+      <c r="I113" s="18">
         <v>22.4</v>
       </c>
-      <c r="J112" s="19">
+      <c r="J113" s="18">
         <v>-41.35</v>
       </c>
-      <c r="K112" s="19">
+      <c r="K113" s="18">
         <v>0.12</v>
       </c>
-      <c r="L112" s="19">
+      <c r="L113" s="18">
         <v>8.4</v>
       </c>
-      <c r="M112" s="19">
+      <c r="M113" s="18">
         <v>0.3</v>
       </c>
-      <c r="N112" s="19">
+      <c r="N113" s="18">
         <v>0.37</v>
       </c>
-      <c r="O112" s="19">
+      <c r="O113" s="18">
         <v>0.03</v>
       </c>
-      <c r="P112" s="19">
+      <c r="P113" s="18">
         <v>351</v>
       </c>
-      <c r="Q112" s="19">
+      <c r="Q113" s="18">
         <v>4</v>
       </c>
-      <c r="R112" s="19">
+      <c r="R113" s="18">
         <v>50836.6</v>
       </c>
-      <c r="S112" s="19">
+      <c r="S113" s="18">
         <v>0.6</v>
       </c>
-      <c r="T112" s="19">
+      <c r="T113" s="18">
         <v>5.18</v>
       </c>
-      <c r="U112" s="19">
+      <c r="U113" s="18">
         <v>0.19</v>
       </c>
-      <c r="V112" s="21">
+      <c r="V113" s="20">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="W112" s="21">
+      <c r="W113" s="20">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="X112" s="19">
+      <c r="X113" s="18">
         <v>0.49</v>
       </c>
-      <c r="Y112" s="19">
+      <c r="Y113" s="18">
         <v>22</v>
       </c>
-      <c r="Z112" s="19" t="s">
+      <c r="Z113" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="AA112" s="19" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="113" spans="3:27" x14ac:dyDescent="0.2">
-      <c r="C113" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D113">
-        <v>5599</v>
-      </c>
-      <c r="E113" t="s">
-        <v>98</v>
-      </c>
-      <c r="F113" t="s">
-        <v>98</v>
-      </c>
-      <c r="G113">
-        <v>59.837000000000003</v>
-      </c>
-      <c r="H113">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="I113">
-        <v>32.5</v>
-      </c>
-      <c r="J113">
-        <v>-42.01</v>
-      </c>
-      <c r="K113">
-        <v>0.1</v>
-      </c>
-      <c r="L113">
-        <v>19.38</v>
-      </c>
-      <c r="M113">
-        <v>0.22</v>
-      </c>
-      <c r="N113">
-        <v>0.63300000000000001</v>
-      </c>
-      <c r="O113">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="P113">
-        <v>175.4</v>
-      </c>
-      <c r="Q113">
-        <v>0.6</v>
-      </c>
-      <c r="R113">
-        <v>51879.1</v>
-      </c>
-      <c r="S113">
-        <v>0.09</v>
-      </c>
-      <c r="T113">
-        <v>12.34</v>
-      </c>
-      <c r="U113">
-        <v>0.16</v>
-      </c>
-      <c r="V113" s="2">
-        <v>2.0899999999999998E-2</v>
-      </c>
-      <c r="W113" s="2">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="X113">
-        <v>0.39</v>
-      </c>
-      <c r="Y113">
-        <v>28</v>
-      </c>
-      <c r="Z113" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA113" t="s">
+      <c r="AA113" s="18" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3978,7 +3937,7 @@
         <v>104</v>
       </c>
       <c r="D114">
-        <v>4865</v>
+        <v>5599</v>
       </c>
       <c r="E114" t="s">
         <v>98</v>
@@ -3987,61 +3946,61 @@
         <v>98</v>
       </c>
       <c r="G114">
-        <v>66.311000000000007</v>
+        <v>59.837000000000003</v>
       </c>
       <c r="H114">
-        <v>1.2E-2</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="I114">
-        <v>19.2</v>
+        <v>32.5</v>
       </c>
       <c r="J114">
-        <v>-42.46</v>
+        <v>-42.01</v>
       </c>
       <c r="K114">
         <v>0.1</v>
       </c>
       <c r="L114">
-        <v>24.31</v>
+        <v>19.38</v>
       </c>
       <c r="M114">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="N114">
-        <v>0.20399999999999999</v>
+        <v>0.63300000000000001</v>
       </c>
       <c r="O114">
-        <v>7.0000000000000001E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P114">
-        <v>174.7</v>
+        <v>175.4</v>
       </c>
       <c r="Q114">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="R114">
-        <v>51076.6</v>
+        <v>51879.1</v>
       </c>
       <c r="S114">
-        <v>0.3</v>
+        <v>0.09</v>
       </c>
       <c r="T114">
-        <v>21.67</v>
+        <v>12.34</v>
       </c>
       <c r="U114">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="V114" s="2">
-        <v>9.2600000000000002E-2</v>
+        <v>2.0899999999999998E-2</v>
       </c>
       <c r="W114" s="2">
-        <v>1.4E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="X114">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="Y114">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z114" t="s">
         <v>96</v>
@@ -4055,7 +4014,7 @@
         <v>104</v>
       </c>
       <c r="D115">
-        <v>5048</v>
+        <v>4865</v>
       </c>
       <c r="E115" t="s">
         <v>98</v>
@@ -4064,61 +4023,61 @@
         <v>98</v>
       </c>
       <c r="G115">
-        <v>90.902000000000001</v>
+        <v>66.311000000000007</v>
       </c>
       <c r="H115">
-        <v>1.4E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="I115">
-        <v>97.9</v>
+        <v>19.2</v>
       </c>
       <c r="J115">
-        <v>-42.3</v>
+        <v>-42.46</v>
       </c>
       <c r="K115">
+        <v>0.1</v>
+      </c>
+      <c r="L115">
+        <v>24.31</v>
+      </c>
+      <c r="M115">
+        <v>0.12</v>
+      </c>
+      <c r="N115">
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="O115">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="P115">
+        <v>174.7</v>
+      </c>
+      <c r="Q115">
+        <v>1.4</v>
+      </c>
+      <c r="R115">
+        <v>51076.6</v>
+      </c>
+      <c r="S115">
         <v>0.3</v>
       </c>
-      <c r="L115">
-        <v>12.2</v>
-      </c>
-      <c r="M115">
-        <v>0.5</v>
-      </c>
-      <c r="N115">
-        <v>0.18</v>
-      </c>
-      <c r="O115">
-        <v>0.04</v>
-      </c>
-      <c r="P115">
-        <v>331</v>
-      </c>
-      <c r="Q115">
-        <v>11</v>
-      </c>
-      <c r="R115">
-        <v>49095</v>
-      </c>
-      <c r="S115">
-        <v>3</v>
-      </c>
       <c r="T115">
-        <v>15.1</v>
+        <v>21.67</v>
       </c>
       <c r="U115">
-        <v>0.6</v>
+        <v>0.11</v>
       </c>
       <c r="V115" s="2">
-        <v>1.6500000000000001E-2</v>
+        <v>9.2600000000000002E-2</v>
       </c>
       <c r="W115" s="2">
-        <v>2E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="X115">
-        <v>2.08</v>
+        <v>0.36</v>
       </c>
       <c r="Y115">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="Z115" t="s">
         <v>96</v>
@@ -4132,7 +4091,7 @@
         <v>104</v>
       </c>
       <c r="D116">
-        <v>5381</v>
+        <v>5048</v>
       </c>
       <c r="E116" t="s">
         <v>98</v>
@@ -4141,61 +4100,61 @@
         <v>98</v>
       </c>
       <c r="G116">
-        <v>98.7</v>
+        <v>90.902000000000001</v>
       </c>
       <c r="H116">
-        <v>0.3</v>
+        <v>1.4E-2</v>
       </c>
       <c r="I116">
-        <v>35.299999999999997</v>
+        <v>97.9</v>
       </c>
       <c r="J116">
-        <v>-42</v>
+        <v>-42.3</v>
       </c>
       <c r="K116">
         <v>0.3</v>
       </c>
       <c r="L116">
-        <v>5.0999999999999996</v>
+        <v>12.2</v>
       </c>
       <c r="M116">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="N116">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="O116">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="P116">
-        <v>249</v>
+        <v>331</v>
       </c>
       <c r="Q116">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R116">
-        <v>51008</v>
+        <v>49095</v>
       </c>
       <c r="S116">
         <v>3</v>
       </c>
       <c r="T116">
-        <v>6.6</v>
+        <v>15.1</v>
       </c>
       <c r="U116">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="V116" s="2">
-        <v>1.1900000000000001E-3</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="W116" s="2">
-        <v>2.3000000000000001E-4</v>
+        <v>2E-3</v>
       </c>
       <c r="X116">
-        <v>0.94</v>
+        <v>2.08</v>
       </c>
       <c r="Y116">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="Z116" t="s">
         <v>96</v>
@@ -4206,10 +4165,10 @@
     </row>
     <row r="117" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C117" s="1" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="D117">
-        <v>5927</v>
+        <v>5381</v>
       </c>
       <c r="E117" t="s">
         <v>98</v>
@@ -4218,61 +4177,61 @@
         <v>98</v>
       </c>
       <c r="G117">
-        <v>99.94</v>
+        <v>98.7</v>
       </c>
       <c r="H117">
-        <v>1.0999999999999999E-2</v>
+        <v>0.3</v>
       </c>
       <c r="I117">
-        <v>113.5</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="J117">
-        <v>-43.21</v>
+        <v>-42</v>
       </c>
       <c r="K117">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="L117">
-        <v>6.9</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M117">
         <v>0.3</v>
       </c>
       <c r="N117">
-        <v>0.6</v>
+        <v>0.31</v>
       </c>
       <c r="O117">
-        <v>2.3E-2</v>
+        <v>0.06</v>
       </c>
       <c r="P117">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="Q117">
+        <v>13</v>
+      </c>
+      <c r="R117">
+        <v>51008</v>
+      </c>
+      <c r="S117">
         <v>3</v>
       </c>
-      <c r="R117">
-        <v>48271.1</v>
-      </c>
-      <c r="S117">
-        <v>0.6</v>
-      </c>
       <c r="T117">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="U117">
         <v>0.4</v>
       </c>
       <c r="V117" s="2">
-        <v>1.7799999999999999E-3</v>
+        <v>1.1900000000000001E-3</v>
       </c>
       <c r="W117" s="2">
-        <v>2.5000000000000001E-4</v>
+        <v>2.3000000000000001E-4</v>
       </c>
       <c r="X117">
-        <v>0.62</v>
+        <v>0.94</v>
       </c>
       <c r="Y117">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Z117" t="s">
         <v>96</v>
@@ -4283,10 +4242,10 @@
     </row>
     <row r="118" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C118" s="1" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="D118">
-        <v>5887</v>
+        <v>5927</v>
       </c>
       <c r="E118" t="s">
         <v>98</v>
@@ -4295,61 +4254,61 @@
         <v>98</v>
       </c>
       <c r="G118">
-        <v>106.03400000000001</v>
+        <v>99.94</v>
       </c>
       <c r="H118">
-        <v>1.7999999999999999E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="I118">
-        <v>57.5</v>
+        <v>113.5</v>
       </c>
       <c r="J118">
-        <v>-41.9</v>
+        <v>-43.21</v>
       </c>
       <c r="K118">
+        <v>0.13</v>
+      </c>
+      <c r="L118">
+        <v>6.9</v>
+      </c>
+      <c r="M118">
         <v>0.3</v>
       </c>
-      <c r="L118">
-        <v>19.8</v>
-      </c>
-      <c r="M118">
-        <v>0.5</v>
-      </c>
       <c r="N118">
-        <v>0.17100000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="O118">
-        <v>1.7999999999999999E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="P118">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="Q118">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R118">
-        <v>55583.1</v>
+        <v>48271.1</v>
       </c>
       <c r="S118">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="T118">
-        <v>28.5</v>
+        <v>7.6</v>
       </c>
       <c r="U118">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="V118" s="2">
-        <v>8.2000000000000003E-2</v>
+        <v>1.7799999999999999E-3</v>
       </c>
       <c r="W118" s="2">
-        <v>6.0000000000000001E-3</v>
+        <v>2.5000000000000001E-4</v>
       </c>
       <c r="X118">
-        <v>1.0900000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="Y118">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z118" t="s">
         <v>96</v>
@@ -4363,7 +4322,7 @@
         <v>104</v>
       </c>
       <c r="D119">
-        <v>4386</v>
+        <v>5887</v>
       </c>
       <c r="E119" t="s">
         <v>98</v>
@@ -4372,61 +4331,61 @@
         <v>98</v>
       </c>
       <c r="G119">
-        <v>108.393</v>
+        <v>106.03400000000001</v>
       </c>
       <c r="H119">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="I119">
-        <v>11.7</v>
+        <v>57.5</v>
       </c>
       <c r="J119">
-        <v>-42.97</v>
+        <v>-41.9</v>
       </c>
       <c r="K119">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="L119">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="M119">
-        <v>1.1000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="N119">
-        <v>0.78500000000000003</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="O119">
-        <v>1.2999999999999999E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="P119">
-        <v>133.69999999999999</v>
+        <v>103</v>
       </c>
       <c r="Q119">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="R119">
-        <v>51125.56</v>
+        <v>55583.1</v>
       </c>
       <c r="S119">
-        <v>0.23</v>
+        <v>1.8</v>
       </c>
       <c r="T119">
-        <v>18.600000000000001</v>
+        <v>28.5</v>
       </c>
       <c r="U119">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="V119" s="2">
-        <v>2.1999999999999999E-2</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="W119" s="2">
-        <v>4.0000000000000001E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="X119">
-        <v>0.54</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="Y119">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Z119" t="s">
         <v>96</v>
@@ -4440,7 +4399,7 @@
         <v>104</v>
       </c>
       <c r="D120">
-        <v>4726</v>
+        <v>4386</v>
       </c>
       <c r="E120" t="s">
         <v>98</v>
@@ -4449,61 +4408,61 @@
         <v>98</v>
       </c>
       <c r="G120">
-        <v>110.81</v>
+        <v>108.393</v>
       </c>
       <c r="H120">
-        <v>0.16</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="I120">
-        <v>8</v>
+        <v>11.7</v>
       </c>
       <c r="J120">
-        <v>-42.13</v>
+        <v>-42.97</v>
       </c>
       <c r="K120">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="L120">
-        <v>9.4</v>
+        <v>20.2</v>
       </c>
       <c r="M120">
-        <v>0.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N120">
-        <v>0.44600000000000001</v>
+        <v>0.78500000000000003</v>
       </c>
       <c r="O120">
-        <v>1.6E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="P120">
-        <v>252.4</v>
+        <v>133.69999999999999</v>
       </c>
       <c r="Q120">
-        <v>2.2000000000000002</v>
+        <v>0.9</v>
       </c>
       <c r="R120">
-        <v>51017.3</v>
+        <v>51125.56</v>
       </c>
       <c r="S120">
-        <v>0.5</v>
+        <v>0.23</v>
       </c>
       <c r="T120">
-        <v>12.8</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="U120">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="V120" s="2">
-        <v>6.8999999999999999E-3</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="W120" s="2">
-        <v>5.0000000000000001E-4</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="X120">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
       <c r="Y120">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="Z120" t="s">
         <v>96</v>
@@ -4517,7 +4476,7 @@
         <v>104</v>
       </c>
       <c r="D121">
-        <v>5379</v>
+        <v>4726</v>
       </c>
       <c r="E121" t="s">
         <v>98</v>
@@ -4526,61 +4485,61 @@
         <v>98</v>
       </c>
       <c r="G121">
-        <v>120.21</v>
+        <v>110.81</v>
       </c>
       <c r="H121">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="I121">
-        <v>35.1</v>
+        <v>8</v>
       </c>
       <c r="J121">
-        <v>-42.8</v>
+        <v>-42.13</v>
       </c>
       <c r="K121">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L121">
-        <v>8.1</v>
+        <v>9.4</v>
       </c>
       <c r="M121">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="N121">
-        <v>0.24</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="O121">
-        <v>0.03</v>
+        <v>1.6E-2</v>
       </c>
       <c r="P121">
-        <v>206</v>
+        <v>252.4</v>
       </c>
       <c r="Q121">
-        <v>6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="R121">
-        <v>52715.7</v>
+        <v>51017.3</v>
       </c>
       <c r="S121">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="T121">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="U121">
         <v>0.3</v>
       </c>
       <c r="V121" s="2">
-        <v>6.1000000000000004E-3</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="W121" s="2">
-        <v>4.0000000000000002E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="X121">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="Y121">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z121" t="s">
         <v>96</v>
@@ -4594,7 +4553,7 @@
         <v>104</v>
       </c>
       <c r="D122">
-        <v>3171</v>
+        <v>5379</v>
       </c>
       <c r="E122" t="s">
         <v>98</v>
@@ -4603,61 +4562,61 @@
         <v>98</v>
       </c>
       <c r="G122">
-        <v>123.01</v>
+        <v>120.21</v>
       </c>
       <c r="H122">
+        <v>0.04</v>
+      </c>
+      <c r="I122">
+        <v>35.1</v>
+      </c>
+      <c r="J122">
+        <v>-42.8</v>
+      </c>
+      <c r="K122">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L122">
+        <v>8.1</v>
+      </c>
+      <c r="M122">
         <v>0.17</v>
       </c>
-      <c r="I122">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="J122">
-        <v>-42.56</v>
-      </c>
-      <c r="K122">
-        <v>0.13</v>
-      </c>
-      <c r="L122">
-        <v>8.4</v>
-      </c>
-      <c r="M122">
-        <v>0.14000000000000001</v>
-      </c>
       <c r="N122">
-        <v>0.129</v>
+        <v>0.24</v>
       </c>
       <c r="O122">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="P122">
-        <v>275</v>
+        <v>206</v>
       </c>
       <c r="Q122">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R122">
-        <v>50827</v>
+        <v>52715.7</v>
       </c>
       <c r="S122">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="T122">
-        <v>14.09</v>
+        <v>13</v>
       </c>
       <c r="U122">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="V122" s="2">
-        <v>7.4000000000000003E-3</v>
+        <v>6.1000000000000004E-3</v>
       </c>
       <c r="W122" s="2">
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="X122">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="Y122">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="Z122" t="s">
         <v>96</v>
@@ -4668,10 +4627,10 @@
     </row>
     <row r="123" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C123" s="1" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="D123">
-        <v>5121</v>
+        <v>3171</v>
       </c>
       <c r="E123" t="s">
         <v>98</v>
@@ -4680,61 +4639,61 @@
         <v>98</v>
       </c>
       <c r="G123">
-        <v>156</v>
+        <v>123.01</v>
       </c>
       <c r="H123">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="I123">
-        <v>7.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="J123">
-        <v>-41.37</v>
+        <v>-42.56</v>
       </c>
       <c r="K123">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="L123">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="M123">
-        <v>0.3</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="N123">
-        <v>0.16</v>
+        <v>0.129</v>
       </c>
       <c r="O123">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="P123">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="Q123">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R123">
-        <v>51217</v>
+        <v>50827</v>
       </c>
       <c r="S123">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T123">
-        <v>16.399999999999999</v>
+        <v>14.09</v>
       </c>
       <c r="U123">
-        <v>0.7</v>
+        <v>0.24</v>
       </c>
       <c r="V123" s="2">
-        <v>7.1999999999999998E-3</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="W123" s="2">
-        <v>8.9999999999999998E-4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="X123">
-        <v>0.73</v>
+        <v>0.51</v>
       </c>
       <c r="Y123">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Z123" t="s">
         <v>96</v>
@@ -4745,10 +4704,10 @@
     </row>
     <row r="124" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C124" s="1" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="D124">
-        <v>4585</v>
+        <v>5121</v>
       </c>
       <c r="E124" t="s">
         <v>98</v>
@@ -4757,61 +4716,61 @@
         <v>98</v>
       </c>
       <c r="G124">
-        <v>181.52</v>
+        <v>156</v>
       </c>
       <c r="H124">
+        <v>0.3</v>
+      </c>
+      <c r="I124">
+        <v>7.3</v>
+      </c>
+      <c r="J124">
+        <v>-41.37</v>
+      </c>
+      <c r="K124">
         <v>0.17</v>
       </c>
-      <c r="I124">
-        <v>11.4</v>
-      </c>
-      <c r="J124">
-        <v>-43.1</v>
-      </c>
-      <c r="K124">
+      <c r="L124">
+        <v>7.7</v>
+      </c>
+      <c r="M124">
         <v>0.3</v>
       </c>
-      <c r="L124">
-        <v>12.7</v>
-      </c>
-      <c r="M124">
-        <v>0.4</v>
-      </c>
       <c r="N124">
-        <v>0.37</v>
+        <v>0.16</v>
       </c>
       <c r="O124">
-        <v>2.3E-2</v>
+        <v>0.04</v>
       </c>
       <c r="P124">
-        <v>30</v>
+        <v>243</v>
       </c>
       <c r="Q124">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R124">
-        <v>52110.400000000001</v>
+        <v>51217</v>
       </c>
       <c r="S124">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="T124">
-        <v>29.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="U124">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="V124" s="2">
-        <v>3.1E-2</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="W124" s="2">
-        <v>3.0000000000000001E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="X124">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="Y124">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="Z124" t="s">
         <v>96</v>
@@ -4825,7 +4784,7 @@
         <v>104</v>
       </c>
       <c r="D125">
-        <v>5666</v>
+        <v>4585</v>
       </c>
       <c r="E125" t="s">
         <v>98</v>
@@ -4834,61 +4793,61 @@
         <v>98</v>
       </c>
       <c r="G125">
-        <v>211.22</v>
+        <v>181.52</v>
       </c>
       <c r="H125">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="I125">
-        <v>13.3</v>
+        <v>11.4</v>
       </c>
       <c r="J125">
-        <v>-41.5</v>
+        <v>-43.1</v>
       </c>
       <c r="K125">
         <v>0.3</v>
       </c>
       <c r="L125">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="M125">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="N125">
-        <v>0.71199999999999997</v>
+        <v>0.37</v>
       </c>
       <c r="O125">
-        <v>1.9E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="P125">
-        <v>224</v>
+        <v>30</v>
       </c>
       <c r="Q125">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R125">
-        <v>53321.7</v>
+        <v>52110.400000000001</v>
       </c>
       <c r="S125">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="T125">
-        <v>24.7</v>
+        <v>29.5</v>
       </c>
       <c r="U125">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="V125" s="2">
-        <v>1.34E-2</v>
+        <v>3.1E-2</v>
       </c>
       <c r="W125" s="2">
-        <v>2.2000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="X125">
-        <v>0.32</v>
+        <v>0.95</v>
       </c>
       <c r="Y125">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z125" t="s">
         <v>96</v>
@@ -4902,7 +4861,7 @@
         <v>104</v>
       </c>
       <c r="D126">
-        <v>5855</v>
+        <v>5666</v>
       </c>
       <c r="E126" t="s">
         <v>98</v>
@@ -4911,61 +4870,61 @@
         <v>98</v>
       </c>
       <c r="G126">
-        <v>211.24</v>
+        <v>211.22</v>
       </c>
       <c r="H126">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="I126">
-        <v>47</v>
+        <v>13.3</v>
       </c>
       <c r="J126">
-        <v>-42.35</v>
+        <v>-41.5</v>
       </c>
       <c r="K126">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L126">
-        <v>2.3199999999999998</v>
+        <v>12.1</v>
       </c>
       <c r="M126">
-        <v>0.18</v>
+        <v>0.6</v>
       </c>
       <c r="N126">
-        <v>0.28999999999999998</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="O126">
-        <v>7.0000000000000007E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="P126">
-        <v>157</v>
+        <v>224</v>
       </c>
       <c r="Q126">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R126">
-        <v>50203</v>
+        <v>53321.7</v>
       </c>
       <c r="S126">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="T126">
-        <v>6.5</v>
+        <v>24.7</v>
       </c>
       <c r="U126">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="V126" s="2">
-        <v>2.4000000000000001E-4</v>
+        <v>1.34E-2</v>
       </c>
       <c r="W126" s="2">
-        <v>6.0000000000000002E-5</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="X126">
-        <v>0.59</v>
+        <v>0.32</v>
       </c>
       <c r="Y126">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="Z126" t="s">
         <v>96</v>
@@ -4979,7 +4938,7 @@
         <v>104</v>
       </c>
       <c r="D127">
-        <v>5467</v>
+        <v>5855</v>
       </c>
       <c r="E127" t="s">
         <v>98</v>
@@ -4988,61 +4947,61 @@
         <v>98</v>
       </c>
       <c r="G127">
-        <v>224.1</v>
+        <v>211.24</v>
       </c>
       <c r="H127">
-        <v>0.3</v>
+        <v>0.19</v>
       </c>
       <c r="I127">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="J127">
-        <v>-42.48</v>
+        <v>-42.35</v>
       </c>
       <c r="K127">
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L127">
-        <v>6.27</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="M127">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="N127">
-        <v>0.15</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="O127">
-        <v>0.03</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="P127">
-        <v>25</v>
+        <v>157</v>
       </c>
       <c r="Q127">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R127">
-        <v>51153</v>
+        <v>50203</v>
       </c>
       <c r="S127">
         <v>6</v>
       </c>
       <c r="T127">
-        <v>19.100000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="U127">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="V127" s="2">
-        <v>5.4999999999999997E-3</v>
+        <v>2.4000000000000001E-4</v>
       </c>
       <c r="W127" s="2">
-        <v>5.0000000000000001E-4</v>
+        <v>6.0000000000000002E-5</v>
       </c>
       <c r="X127">
-        <v>0.56999999999999995</v>
+        <v>0.59</v>
       </c>
       <c r="Y127">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="Z127" t="s">
         <v>96</v>
@@ -5056,7 +5015,7 @@
         <v>104</v>
       </c>
       <c r="D128">
-        <v>6586</v>
+        <v>5467</v>
       </c>
       <c r="E128" t="s">
         <v>98</v>
@@ -5065,61 +5024,61 @@
         <v>98</v>
       </c>
       <c r="G128">
-        <v>239.1</v>
+        <v>224.1</v>
       </c>
       <c r="H128">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I128">
-        <v>5.0999999999999996</v>
+        <v>11</v>
       </c>
       <c r="J128">
-        <v>-43.24</v>
+        <v>-42.48</v>
       </c>
       <c r="K128">
-        <v>0.12</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="L128">
-        <v>15.58</v>
+        <v>6.27</v>
       </c>
       <c r="M128">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="N128">
-        <v>0.42199999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="O128">
-        <v>1.2999999999999999E-2</v>
+        <v>0.03</v>
       </c>
       <c r="P128">
-        <v>181.9</v>
+        <v>25</v>
       </c>
       <c r="Q128">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="R128">
-        <v>50562.2</v>
+        <v>51153</v>
       </c>
       <c r="S128">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T128">
-        <v>46.5</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="U128">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="V128" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="W128" s="2">
-        <v>3.0000000000000001E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="X128">
         <v>0.56999999999999995</v>
       </c>
       <c r="Y128">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="Z128" t="s">
         <v>96</v>
@@ -5133,7 +5092,7 @@
         <v>104</v>
       </c>
       <c r="D129">
-        <v>5332</v>
+        <v>6586</v>
       </c>
       <c r="E129" t="s">
         <v>98</v>
@@ -5142,61 +5101,61 @@
         <v>98</v>
       </c>
       <c r="G129">
-        <v>257.5</v>
+        <v>239.1</v>
       </c>
       <c r="H129">
         <v>0.4</v>
       </c>
       <c r="I129">
-        <v>12.7</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="J129">
-        <v>-42.31</v>
+        <v>-43.24</v>
       </c>
       <c r="K129">
-        <v>0.14000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="L129">
-        <v>4.3</v>
+        <v>15.58</v>
       </c>
       <c r="M129">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="N129">
-        <v>0.45</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="O129">
-        <v>0.05</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="P129">
-        <v>232</v>
+        <v>181.9</v>
       </c>
       <c r="Q129">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="R129">
-        <v>52560</v>
+        <v>50562.2</v>
       </c>
       <c r="S129">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T129">
-        <v>13.8</v>
+        <v>46.5</v>
       </c>
       <c r="U129">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="V129" s="2">
-        <v>1.6000000000000001E-3</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="W129" s="2">
-        <v>2.9999999999999997E-4</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="X129">
-        <v>0.52</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="Y129">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Z129" t="s">
         <v>96</v>
@@ -5210,70 +5169,70 @@
         <v>104</v>
       </c>
       <c r="D130">
-        <v>6325</v>
+        <v>5332</v>
       </c>
       <c r="E130" t="s">
         <v>98</v>
       </c>
       <c r="F130" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G130">
-        <v>259.3</v>
+        <v>257.5</v>
       </c>
       <c r="H130">
         <v>0.4</v>
       </c>
       <c r="I130">
-        <v>11.8</v>
+        <v>12.7</v>
       </c>
       <c r="J130">
-        <v>-42.1</v>
+        <v>-42.31</v>
       </c>
       <c r="K130">
-        <v>0.4</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="L130">
-        <v>13.3</v>
+        <v>4.3</v>
       </c>
       <c r="M130">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N130">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="O130">
         <v>0.05</v>
       </c>
       <c r="P130">
-        <v>25</v>
+        <v>232</v>
       </c>
       <c r="Q130">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R130">
-        <v>52995</v>
+        <v>52560</v>
       </c>
       <c r="S130">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T130">
-        <v>44.3</v>
+        <v>13.8</v>
       </c>
       <c r="U130">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="V130" s="2">
-        <v>5.0999999999999997E-2</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="W130" s="2">
-        <v>6.0000000000000001E-3</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="X130">
-        <v>0.98</v>
+        <v>0.52</v>
       </c>
       <c r="Y130">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="Z130" t="s">
         <v>96</v>
@@ -5287,70 +5246,70 @@
         <v>104</v>
       </c>
       <c r="D131">
-        <v>5095</v>
+        <v>6325</v>
       </c>
       <c r="E131" t="s">
         <v>98</v>
       </c>
       <c r="F131" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G131">
-        <v>263.92</v>
+        <v>259.3</v>
       </c>
       <c r="H131">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="I131">
-        <v>12.9</v>
+        <v>11.8</v>
       </c>
       <c r="J131">
-        <v>-42.54</v>
+        <v>-42.1</v>
       </c>
       <c r="K131">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="L131">
-        <v>20.399999999999999</v>
+        <v>13.3</v>
       </c>
       <c r="M131">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="N131">
-        <v>0.67300000000000004</v>
+        <v>0.36</v>
       </c>
       <c r="O131">
-        <v>1.9E-2</v>
+        <v>0.05</v>
       </c>
       <c r="P131">
-        <v>230.8</v>
+        <v>25</v>
       </c>
       <c r="Q131">
+        <v>6</v>
+      </c>
+      <c r="R131">
+        <v>52995</v>
+      </c>
+      <c r="S131">
+        <v>6</v>
+      </c>
+      <c r="T131">
+        <v>44.3</v>
+      </c>
+      <c r="U131">
         <v>1.8</v>
       </c>
-      <c r="R131">
-        <v>51475.3</v>
-      </c>
-      <c r="S131">
-        <v>0.6</v>
-      </c>
-      <c r="T131">
-        <v>54.7</v>
-      </c>
-      <c r="U131">
-        <v>2.5</v>
-      </c>
       <c r="V131" s="2">
-        <v>9.2999999999999999E-2</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="W131" s="2">
-        <v>1.0999999999999999E-2</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="X131">
-        <v>0.59</v>
+        <v>0.98</v>
       </c>
       <c r="Y131">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="Z131" t="s">
         <v>96</v>
@@ -5364,70 +5323,70 @@
         <v>104</v>
       </c>
       <c r="D132">
-        <v>5015</v>
+        <v>5095</v>
       </c>
       <c r="E132" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F132" t="s">
         <v>98</v>
       </c>
       <c r="G132">
-        <v>312.5</v>
+        <v>263.92</v>
       </c>
       <c r="H132">
-        <v>0.9</v>
-      </c>
-      <c r="I132" t="s">
-        <v>107</v>
+        <v>0.18</v>
+      </c>
+      <c r="I132">
+        <v>12.9</v>
       </c>
       <c r="J132">
-        <v>-46.5</v>
+        <v>-42.54</v>
       </c>
       <c r="K132">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="L132">
-        <v>11.4</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M132">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="N132">
-        <v>0.1</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="O132">
-        <v>0.03</v>
+        <v>1.9E-2</v>
       </c>
       <c r="P132">
-        <v>74</v>
+        <v>230.8</v>
       </c>
       <c r="Q132">
-        <v>21</v>
+        <v>1.8</v>
       </c>
       <c r="R132">
-        <v>51599</v>
+        <v>51475.3</v>
       </c>
       <c r="S132">
-        <v>19</v>
+        <v>0.6</v>
       </c>
       <c r="T132">
-        <v>48.6</v>
+        <v>54.7</v>
       </c>
       <c r="U132">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="V132" s="2">
-        <v>4.7E-2</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="W132" s="2">
-        <v>4.0000000000000001E-3</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="X132">
-        <v>1</v>
+        <v>0.59</v>
       </c>
       <c r="Y132">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="Z132" t="s">
         <v>96</v>
@@ -5441,70 +5400,70 @@
         <v>104</v>
       </c>
       <c r="D133">
-        <v>5242</v>
+        <v>5015</v>
       </c>
       <c r="E133" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F133" t="s">
         <v>98</v>
       </c>
       <c r="G133">
-        <v>339.5</v>
+        <v>312.5</v>
       </c>
       <c r="H133">
-        <v>1.3</v>
-      </c>
-      <c r="I133">
-        <v>3.4</v>
+        <v>0.9</v>
+      </c>
+      <c r="I133" t="s">
+        <v>107</v>
       </c>
       <c r="J133">
-        <v>-42.22</v>
+        <v>-46.5</v>
       </c>
       <c r="K133">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="L133">
-        <v>7.26</v>
+        <v>11.4</v>
       </c>
       <c r="M133">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="N133">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="O133">
         <v>0.03</v>
       </c>
       <c r="P133">
-        <v>195</v>
+        <v>74</v>
       </c>
       <c r="Q133">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="R133">
-        <v>51144</v>
+        <v>51599</v>
       </c>
       <c r="S133">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="T133">
-        <v>32.299999999999997</v>
+        <v>48.6</v>
       </c>
       <c r="U133">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="V133" s="2">
-        <v>1.17E-2</v>
+        <v>4.7E-2</v>
       </c>
       <c r="W133" s="2">
-        <v>1E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="X133">
-        <v>0.41</v>
+        <v>1</v>
       </c>
       <c r="Y133">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="Z133" t="s">
         <v>96</v>
@@ -5518,7 +5477,7 @@
         <v>104</v>
       </c>
       <c r="D134">
-        <v>4565</v>
+        <v>5242</v>
       </c>
       <c r="E134" t="s">
         <v>98</v>
@@ -5527,61 +5486,61 @@
         <v>98</v>
       </c>
       <c r="G134">
-        <v>344.01</v>
+        <v>339.5</v>
       </c>
       <c r="H134">
-        <v>0.05</v>
+        <v>1.3</v>
       </c>
       <c r="I134">
-        <v>19.8</v>
+        <v>3.4</v>
       </c>
       <c r="J134">
-        <v>-42.18</v>
+        <v>-42.22</v>
       </c>
       <c r="K134">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="L134">
-        <v>8.36</v>
+        <v>7.26</v>
       </c>
       <c r="M134">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="N134">
-        <v>0.64100000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="O134">
-        <v>1.2999999999999999E-2</v>
+        <v>0.03</v>
       </c>
       <c r="P134">
-        <v>240.8</v>
+        <v>195</v>
       </c>
       <c r="Q134">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="R134">
-        <v>47601.9</v>
+        <v>51144</v>
       </c>
       <c r="S134">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="T134">
-        <v>30.4</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="U134">
         <v>0.9</v>
       </c>
       <c r="V134" s="2">
-        <v>9.4000000000000004E-3</v>
+        <v>1.17E-2</v>
       </c>
       <c r="W134" s="2">
-        <v>8.0000000000000004E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="X134">
-        <v>0.71</v>
+        <v>0.41</v>
       </c>
       <c r="Y134">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="Z134" t="s">
         <v>96</v>
@@ -5595,70 +5554,70 @@
         <v>104</v>
       </c>
       <c r="D135">
-        <v>5268</v>
+        <v>4565</v>
       </c>
       <c r="E135" t="s">
         <v>98</v>
       </c>
       <c r="F135" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G135">
-        <v>420.6</v>
+        <v>344.01</v>
       </c>
       <c r="H135">
-        <v>1.8</v>
+        <v>0.05</v>
       </c>
       <c r="I135">
-        <v>7.7</v>
+        <v>19.8</v>
       </c>
       <c r="J135">
-        <v>-42.78</v>
+        <v>-42.18</v>
       </c>
       <c r="K135">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="L135">
-        <v>1.7</v>
+        <v>8.36</v>
       </c>
       <c r="M135">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="N135">
-        <v>0.44</v>
+        <v>0.64100000000000001</v>
       </c>
       <c r="O135">
-        <v>0.08</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="P135">
-        <v>343</v>
+        <v>240.8</v>
       </c>
       <c r="Q135">
-        <v>21</v>
+        <v>2.5</v>
       </c>
       <c r="R135">
-        <v>52950</v>
+        <v>47601.9</v>
       </c>
       <c r="S135">
-        <v>30</v>
+        <v>0.9</v>
       </c>
       <c r="T135">
-        <v>8.9</v>
+        <v>30.4</v>
       </c>
       <c r="U135">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="V135" s="2">
-        <v>1.6000000000000001E-4</v>
+        <v>9.4000000000000004E-3</v>
       </c>
       <c r="W135" s="2">
-        <v>1.1E-4</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="X135">
-        <v>0.34</v>
+        <v>0.71</v>
       </c>
       <c r="Y135">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="Z135" t="s">
         <v>96</v>
@@ -5669,73 +5628,73 @@
     </row>
     <row r="136" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C136" s="1" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="D136">
-        <v>6786</v>
+        <v>5268</v>
       </c>
       <c r="E136" t="s">
         <v>98</v>
       </c>
       <c r="F136" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G136">
-        <v>435.4</v>
+        <v>420.6</v>
       </c>
       <c r="H136">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="I136">
-        <v>3.7</v>
+        <v>7.7</v>
       </c>
       <c r="J136">
-        <v>-59.39</v>
+        <v>-42.78</v>
       </c>
       <c r="K136">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="L136">
-        <v>11.19</v>
+        <v>1.7</v>
       </c>
       <c r="M136">
-        <v>0.19</v>
+        <v>0.4</v>
       </c>
       <c r="N136">
-        <v>0.49099999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="O136">
-        <v>1.2999999999999999E-2</v>
+        <v>0.08</v>
       </c>
       <c r="P136">
-        <v>36.700000000000003</v>
+        <v>343</v>
       </c>
       <c r="Q136">
-        <v>1.8</v>
+        <v>21</v>
       </c>
       <c r="R136">
-        <v>51935.199999999997</v>
+        <v>52950</v>
       </c>
       <c r="S136">
-        <v>1.4</v>
+        <v>30</v>
       </c>
       <c r="T136">
-        <v>58.4</v>
+        <v>8.9</v>
       </c>
       <c r="U136">
-        <v>1.1000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="V136" s="2">
-        <v>4.1799999999999997E-2</v>
+        <v>1.6000000000000001E-4</v>
       </c>
       <c r="W136" s="2">
-        <v>2.2000000000000001E-3</v>
+        <v>1.1E-4</v>
       </c>
       <c r="X136">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="Y136">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z136" t="s">
         <v>96</v>
@@ -5746,10 +5705,10 @@
     </row>
     <row r="137" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C137" s="1" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="D137">
-        <v>4369</v>
+        <v>6786</v>
       </c>
       <c r="E137" t="s">
         <v>98</v>
@@ -5758,61 +5717,61 @@
         <v>98</v>
       </c>
       <c r="G137">
-        <v>441</v>
+        <v>435.4</v>
       </c>
       <c r="H137">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I137">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J137">
-        <v>-41.91</v>
+        <v>-59.39</v>
       </c>
       <c r="K137">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="L137">
-        <v>6.42</v>
+        <v>11.19</v>
       </c>
       <c r="M137">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="N137">
-        <v>0.38</v>
+        <v>0.49099999999999999</v>
       </c>
       <c r="O137">
-        <v>0.03</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="P137">
-        <v>53</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="Q137">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="R137">
-        <v>50625</v>
+        <v>51935.199999999997</v>
       </c>
       <c r="S137">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="T137">
-        <v>36</v>
+        <v>58.4</v>
       </c>
       <c r="U137">
-        <v>1.4</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="V137" s="2">
-        <v>9.4999999999999998E-3</v>
+        <v>4.1799999999999997E-2</v>
       </c>
       <c r="W137" s="2">
-        <v>1E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="X137">
-        <v>0.66</v>
+        <v>0.39</v>
       </c>
       <c r="Y137">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z137" t="s">
         <v>96</v>
@@ -5826,7 +5785,7 @@
         <v>104</v>
       </c>
       <c r="D138">
-        <v>4581</v>
+        <v>4369</v>
       </c>
       <c r="E138" t="s">
         <v>98</v>
@@ -5835,61 +5794,61 @@
         <v>98</v>
       </c>
       <c r="G138">
-        <v>546.70000000000005</v>
+        <v>441</v>
       </c>
       <c r="H138">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="I138">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J138">
-        <v>-41.9</v>
+        <v>-41.91</v>
       </c>
       <c r="K138">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="L138">
-        <v>8.4</v>
+        <v>6.42</v>
       </c>
       <c r="M138">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="N138">
-        <v>0.26900000000000002</v>
+        <v>0.38</v>
       </c>
       <c r="O138">
-        <v>1.4999999999999999E-2</v>
+        <v>0.03</v>
       </c>
       <c r="P138">
-        <v>217</v>
+        <v>53</v>
       </c>
       <c r="Q138">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R138">
-        <v>51222</v>
+        <v>50625</v>
       </c>
       <c r="S138">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T138">
-        <v>60.8</v>
+        <v>36</v>
       </c>
       <c r="U138">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="V138" s="2">
-        <v>0.03</v>
+        <v>9.4999999999999998E-3</v>
       </c>
       <c r="W138" s="2">
         <v>1E-3</v>
       </c>
       <c r="X138">
-        <v>0.27</v>
+        <v>0.66</v>
       </c>
       <c r="Y138">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Z138" t="s">
         <v>96</v>
@@ -5900,10 +5859,10 @@
     </row>
     <row r="139" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C139" s="1" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="D139">
-        <v>4456</v>
+        <v>4581</v>
       </c>
       <c r="E139" t="s">
         <v>98</v>
@@ -5912,58 +5871,58 @@
         <v>98</v>
       </c>
       <c r="G139">
-        <v>565</v>
+        <v>546.70000000000005</v>
       </c>
       <c r="H139">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="I139">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J139">
-        <v>-51.32</v>
+        <v>-41.9</v>
       </c>
       <c r="K139">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="L139">
         <v>8.4</v>
       </c>
       <c r="M139">
-        <v>0.3</v>
+        <v>0.09</v>
       </c>
       <c r="N139">
-        <v>0.2</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="O139">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P139">
+        <v>217</v>
+      </c>
+      <c r="Q139">
+        <v>3</v>
+      </c>
+      <c r="R139">
+        <v>51222</v>
+      </c>
+      <c r="S139">
+        <v>3</v>
+      </c>
+      <c r="T139">
+        <v>60.8</v>
+      </c>
+      <c r="U139">
+        <v>0.7</v>
+      </c>
+      <c r="V139" s="2">
         <v>0.03</v>
       </c>
-      <c r="P139">
-        <v>207</v>
-      </c>
-      <c r="Q139">
-        <v>10</v>
-      </c>
-      <c r="R139">
-        <v>52117</v>
-      </c>
-      <c r="S139">
-        <v>15</v>
-      </c>
-      <c r="T139">
-        <v>63.8</v>
-      </c>
-      <c r="U139">
-        <v>2.1</v>
-      </c>
-      <c r="V139" s="2">
-        <v>3.2000000000000001E-2</v>
-      </c>
       <c r="W139" s="2">
-        <v>3.0000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="X139">
-        <v>0.75</v>
+        <v>0.27</v>
       </c>
       <c r="Y139">
         <v>18</v>
@@ -5977,10 +5936,10 @@
     </row>
     <row r="140" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C140" s="1" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="D140">
-        <v>4589</v>
+        <v>4456</v>
       </c>
       <c r="E140" t="s">
         <v>98</v>
@@ -5989,61 +5948,61 @@
         <v>98</v>
       </c>
       <c r="G140">
-        <v>615.20000000000005</v>
+        <v>565</v>
       </c>
       <c r="H140">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="I140">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J140">
-        <v>-43.2</v>
+        <v>-51.32</v>
       </c>
       <c r="K140">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="L140">
-        <v>4.62</v>
+        <v>8.4</v>
       </c>
       <c r="M140">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="N140">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="O140">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="P140">
-        <v>128</v>
+        <v>207</v>
       </c>
       <c r="Q140">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R140">
-        <v>52125</v>
+        <v>52117</v>
       </c>
       <c r="S140">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T140">
-        <v>38.299999999999997</v>
+        <v>63.8</v>
       </c>
       <c r="U140">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="V140" s="2">
-        <v>5.8999999999999999E-3</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="W140" s="2">
-        <v>6.9999999999999999E-4</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="X140">
-        <v>0.54</v>
+        <v>0.75</v>
       </c>
       <c r="Y140">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Z140" t="s">
         <v>96</v>
@@ -6057,7 +6016,7 @@
         <v>104</v>
       </c>
       <c r="D141">
-        <v>5350</v>
+        <v>4589</v>
       </c>
       <c r="E141" t="s">
         <v>98</v>
@@ -6066,61 +6025,61 @@
         <v>98</v>
       </c>
       <c r="G141">
-        <v>690</v>
+        <v>615.20000000000005</v>
       </c>
       <c r="H141">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="I141">
-        <v>10.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="J141">
-        <v>-41.58</v>
+        <v>-43.2</v>
       </c>
       <c r="K141">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="L141">
-        <v>2.5099999999999998</v>
+        <v>4.62</v>
       </c>
       <c r="M141">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="N141">
-        <v>7.0000000000000007E-2</v>
+        <v>0.21</v>
       </c>
       <c r="O141">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="P141">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="Q141">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="R141">
-        <v>51210</v>
+        <v>52125</v>
       </c>
       <c r="S141">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="T141">
-        <v>23.8</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="U141">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="V141" s="2">
-        <v>1.1199999999999999E-3</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="W141" s="2">
-        <v>1.8000000000000001E-4</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="X141">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="Y141">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="Z141" t="s">
         <v>96</v>
@@ -6131,10 +6090,10 @@
     </row>
     <row r="142" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C142" s="1" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="D142">
-        <v>667</v>
+        <v>5350</v>
       </c>
       <c r="E142" t="s">
         <v>98</v>
@@ -6143,61 +6102,61 @@
         <v>98</v>
       </c>
       <c r="G142">
-        <v>720</v>
+        <v>690</v>
       </c>
       <c r="H142">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I142">
-        <v>2.2999999999999998</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="J142">
-        <v>-38.61</v>
+        <v>-41.58</v>
       </c>
       <c r="K142">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="L142">
-        <v>2.29</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="M142">
         <v>0.13</v>
       </c>
       <c r="N142">
-        <v>0.22</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O142">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="P142">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="Q142">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="R142">
-        <v>52210</v>
+        <v>51210</v>
       </c>
       <c r="S142">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="T142">
-        <v>22.1</v>
+        <v>23.8</v>
       </c>
       <c r="U142">
         <v>1.3</v>
       </c>
       <c r="V142" s="2">
-        <v>8.3000000000000001E-4</v>
+        <v>1.1199999999999999E-3</v>
       </c>
       <c r="W142" s="2">
-        <v>1.3999999999999999E-4</v>
+        <v>1.8000000000000001E-4</v>
       </c>
       <c r="X142">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="Y142">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Z142" t="s">
         <v>96</v>
@@ -6208,10 +6167,10 @@
     </row>
     <row r="143" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C143" s="1" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="D143">
-        <v>451</v>
+        <v>667</v>
       </c>
       <c r="E143" t="s">
         <v>98</v>
@@ -6220,61 +6179,61 @@
         <v>98</v>
       </c>
       <c r="G143">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="H143">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I143">
-        <v>5.5</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J143">
-        <v>-41.04</v>
+        <v>-38.61</v>
       </c>
       <c r="K143">
         <v>0.1</v>
       </c>
       <c r="L143">
-        <v>4.3499999999999996</v>
+        <v>2.29</v>
       </c>
       <c r="M143">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="N143">
-        <v>0.34</v>
+        <v>0.22</v>
       </c>
       <c r="O143">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="P143">
-        <v>235</v>
+        <v>16</v>
       </c>
       <c r="Q143">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="R143">
-        <v>51010</v>
+        <v>52210</v>
       </c>
       <c r="S143">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="T143">
-        <v>40.6</v>
+        <v>22.1</v>
       </c>
       <c r="U143">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="V143" s="2">
-        <v>5.1000000000000004E-3</v>
+        <v>8.3000000000000001E-4</v>
       </c>
       <c r="W143" s="2">
-        <v>5.9999999999999995E-4</v>
+        <v>1.3999999999999999E-4</v>
       </c>
       <c r="X143">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="Y143">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z143" t="s">
         <v>96</v>
@@ -6288,7 +6247,7 @@
         <v>104</v>
       </c>
       <c r="D144">
-        <v>5373</v>
+        <v>451</v>
       </c>
       <c r="E144" t="s">
         <v>98</v>
@@ -6297,61 +6256,61 @@
         <v>98</v>
       </c>
       <c r="G144">
-        <v>878</v>
+        <v>722</v>
       </c>
       <c r="H144">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I144">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="J144">
-        <v>-43.4</v>
+        <v>-41.04</v>
       </c>
       <c r="K144">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="L144">
-        <v>4.5999999999999996</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="M144">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="N144">
-        <v>0.14000000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="O144">
         <v>0.03</v>
       </c>
       <c r="P144">
-        <v>180</v>
+        <v>235</v>
       </c>
       <c r="Q144">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="R144">
-        <v>51730</v>
+        <v>51010</v>
       </c>
       <c r="S144">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="T144">
-        <v>55</v>
+        <v>40.6</v>
       </c>
       <c r="U144">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="V144" s="2">
-        <v>8.6E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="W144" s="2">
-        <v>8.9999999999999998E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="X144">
-        <v>0.46</v>
+        <v>0.37</v>
       </c>
       <c r="Y144">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Z144" t="s">
         <v>96</v>
@@ -6365,70 +6324,70 @@
         <v>104</v>
       </c>
       <c r="D145">
-        <v>3732</v>
+        <v>5373</v>
       </c>
       <c r="E145" t="s">
         <v>98</v>
       </c>
       <c r="F145" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G145">
-        <v>893</v>
+        <v>878</v>
       </c>
       <c r="H145">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I145">
-        <v>4.4000000000000004</v>
+        <v>3.5</v>
       </c>
       <c r="J145">
-        <v>-42.6</v>
+        <v>-43.4</v>
       </c>
       <c r="K145">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="L145">
-        <v>4.0999999999999996</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="M145">
-        <v>1</v>
+        <v>0.16</v>
       </c>
       <c r="N145">
-        <v>0.74</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="O145">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="P145">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="Q145">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="R145">
-        <v>52181</v>
+        <v>51730</v>
       </c>
       <c r="S145">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T145">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="U145">
-        <v>10</v>
+        <v>1.9</v>
       </c>
       <c r="V145" s="2">
-        <v>2E-3</v>
+        <v>8.6E-3</v>
       </c>
       <c r="W145" s="2">
-        <v>1.6000000000000001E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="X145">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="Y145">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Z145" t="s">
         <v>96</v>
@@ -6442,70 +6401,70 @@
         <v>104</v>
       </c>
       <c r="D146">
-        <v>4333</v>
+        <v>3732</v>
       </c>
       <c r="E146" t="s">
         <v>98</v>
       </c>
       <c r="F146" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G146">
-        <v>1001</v>
+        <v>893</v>
       </c>
       <c r="H146">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I146">
-        <v>3.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J146">
-        <v>-42.7</v>
+        <v>-42.6</v>
       </c>
       <c r="K146">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="L146">
-        <v>4.9000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M146">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N146">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="O146">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="P146">
-        <v>207</v>
+        <v>46</v>
       </c>
       <c r="Q146">
+        <v>8</v>
+      </c>
+      <c r="R146">
+        <v>52181</v>
+      </c>
+      <c r="S146">
         <v>10</v>
       </c>
-      <c r="R146">
-        <v>50825</v>
-      </c>
-      <c r="S146">
-        <v>20</v>
-      </c>
       <c r="T146">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="U146">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V146" s="2">
-        <v>7.7000000000000002E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="W146" s="2">
-        <v>2.2000000000000001E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="X146">
-        <v>1.37</v>
+        <v>0.48</v>
       </c>
       <c r="Y146">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="Z146" t="s">
         <v>96</v>
@@ -6519,7 +6478,7 @@
         <v>104</v>
       </c>
       <c r="D147">
-        <v>4970</v>
+        <v>4333</v>
       </c>
       <c r="E147" t="s">
         <v>98</v>
@@ -6528,61 +6487,61 @@
         <v>98</v>
       </c>
       <c r="G147">
-        <v>1002.6</v>
+        <v>1001</v>
       </c>
       <c r="H147">
-        <v>2.4</v>
+        <v>18</v>
       </c>
       <c r="I147">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J147">
-        <v>-41.78</v>
+        <v>-42.7</v>
       </c>
       <c r="K147">
+        <v>0.3</v>
+      </c>
+      <c r="L147">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="M147">
+        <v>0.4</v>
+      </c>
+      <c r="N147">
+        <v>0.5</v>
+      </c>
+      <c r="O147">
         <v>0.06</v>
       </c>
-      <c r="L147">
-        <v>7.74</v>
-      </c>
-      <c r="M147">
-        <v>0.09</v>
-      </c>
-      <c r="N147">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="O147">
-        <v>1.2999999999999999E-2</v>
-      </c>
       <c r="P147">
-        <v>333</v>
+        <v>207</v>
       </c>
       <c r="Q147">
+        <v>10</v>
+      </c>
+      <c r="R147">
+        <v>50825</v>
+      </c>
+      <c r="S147">
+        <v>20</v>
+      </c>
+      <c r="T147">
+        <v>58</v>
+      </c>
+      <c r="U147">
         <v>6</v>
       </c>
-      <c r="R147">
-        <v>51256</v>
-      </c>
-      <c r="S147">
-        <v>17</v>
-      </c>
-      <c r="T147">
-        <v>106.3</v>
-      </c>
-      <c r="U147">
-        <v>1.2</v>
-      </c>
       <c r="V147" s="2">
-        <v>4.7600000000000003E-2</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="W147" s="2">
-        <v>1.6999999999999999E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="X147">
-        <v>0.28999999999999998</v>
+        <v>1.37</v>
       </c>
       <c r="Y147">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="Z147" t="s">
         <v>96</v>
@@ -6596,7 +6555,7 @@
         <v>104</v>
       </c>
       <c r="D148">
-        <v>4734</v>
+        <v>4970</v>
       </c>
       <c r="E148" t="s">
         <v>98</v>
@@ -6605,61 +6564,61 @@
         <v>98</v>
       </c>
       <c r="G148">
-        <v>1029</v>
+        <v>1002.6</v>
       </c>
       <c r="H148">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="I148">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J148">
-        <v>-43.45</v>
+        <v>-41.78</v>
       </c>
       <c r="K148">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="L148">
-        <v>8.6999999999999993</v>
+        <v>7.74</v>
       </c>
       <c r="M148">
-        <v>0.3</v>
+        <v>0.09</v>
       </c>
       <c r="N148">
-        <v>0.312</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="O148">
-        <v>2.4E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="P148">
-        <v>143</v>
+        <v>333</v>
       </c>
       <c r="Q148">
         <v>6</v>
       </c>
       <c r="R148">
-        <v>51730</v>
+        <v>51256</v>
       </c>
       <c r="S148">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T148">
-        <v>117</v>
+        <v>106.3</v>
       </c>
       <c r="U148">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="V148" s="2">
-        <v>0.06</v>
+        <v>4.7600000000000003E-2</v>
       </c>
       <c r="W148" s="2">
-        <v>5.0000000000000001E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="X148">
-        <v>0.83</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Y148">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z148" t="s">
         <v>96</v>
@@ -6673,7 +6632,7 @@
         <v>104</v>
       </c>
       <c r="D149">
-        <v>2679</v>
+        <v>4734</v>
       </c>
       <c r="E149" t="s">
         <v>98</v>
@@ -6682,61 +6641,61 @@
         <v>98</v>
       </c>
       <c r="G149">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="H149">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I149">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J149">
-        <v>-42.3</v>
+        <v>-43.45</v>
       </c>
       <c r="K149">
+        <v>0.17</v>
+      </c>
+      <c r="L149">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="M149">
         <v>0.3</v>
       </c>
-      <c r="L149">
-        <v>6.2</v>
-      </c>
-      <c r="M149">
-        <v>0.4</v>
-      </c>
       <c r="N149">
-        <v>7.0000000000000007E-2</v>
+        <v>0.312</v>
       </c>
       <c r="O149">
-        <v>0.05</v>
+        <v>2.4E-2</v>
       </c>
       <c r="P149">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="Q149">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="R149">
-        <v>52500</v>
+        <v>51730</v>
       </c>
       <c r="S149">
-        <v>130</v>
+        <v>15</v>
       </c>
       <c r="T149">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="U149">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V149" s="2">
-        <v>2.5000000000000001E-2</v>
+        <v>0.06</v>
       </c>
       <c r="W149" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="X149">
-        <v>1.22</v>
+        <v>0.83</v>
       </c>
       <c r="Y149">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Z149" t="s">
         <v>96</v>
@@ -6750,7 +6709,7 @@
         <v>104</v>
       </c>
       <c r="D150">
-        <v>4348</v>
+        <v>2679</v>
       </c>
       <c r="E150" t="s">
         <v>98</v>
@@ -6759,61 +6718,61 @@
         <v>98</v>
       </c>
       <c r="G150">
-        <v>1168</v>
+        <v>1033</v>
       </c>
       <c r="H150">
         <v>8</v>
       </c>
       <c r="I150">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J150">
-        <v>-40.700000000000003</v>
+        <v>-42.3</v>
       </c>
       <c r="K150">
         <v>0.3</v>
       </c>
       <c r="L150">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="M150">
         <v>0.4</v>
       </c>
       <c r="N150">
-        <v>0.09</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O150">
         <v>0.05</v>
       </c>
       <c r="P150">
-        <v>220</v>
+        <v>50</v>
       </c>
       <c r="Q150">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="R150">
-        <v>51750</v>
+        <v>52500</v>
       </c>
       <c r="S150">
         <v>130</v>
       </c>
       <c r="T150">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="U150">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V150" s="2">
-        <v>3.5999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="W150" s="2">
-        <v>7.0000000000000001E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="X150">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="Y150">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Z150" t="s">
         <v>96</v>
@@ -6827,7 +6786,7 @@
         <v>104</v>
       </c>
       <c r="D151">
-        <v>4147</v>
+        <v>4348</v>
       </c>
       <c r="E151" t="s">
         <v>98</v>
@@ -6836,61 +6795,61 @@
         <v>98</v>
       </c>
       <c r="G151">
-        <v>1194</v>
+        <v>1168</v>
       </c>
       <c r="H151">
+        <v>8</v>
+      </c>
+      <c r="I151">
+        <v>3.2</v>
+      </c>
+      <c r="J151">
+        <v>-40.700000000000003</v>
+      </c>
+      <c r="K151">
+        <v>0.3</v>
+      </c>
+      <c r="L151">
+        <v>6.7</v>
+      </c>
+      <c r="M151">
+        <v>0.4</v>
+      </c>
+      <c r="N151">
+        <v>0.09</v>
+      </c>
+      <c r="O151">
+        <v>0.05</v>
+      </c>
+      <c r="P151">
+        <v>220</v>
+      </c>
+      <c r="Q151">
+        <v>40</v>
+      </c>
+      <c r="R151">
+        <v>51750</v>
+      </c>
+      <c r="S151">
+        <v>130</v>
+      </c>
+      <c r="T151">
+        <v>107</v>
+      </c>
+      <c r="U151">
         <v>7</v>
       </c>
-      <c r="I151">
-        <v>3.1</v>
-      </c>
-      <c r="J151">
-        <v>-42.3</v>
-      </c>
-      <c r="K151">
-        <v>0.09</v>
-      </c>
-      <c r="L151">
-        <v>3.62</v>
-      </c>
-      <c r="M151">
-        <v>0.13</v>
-      </c>
-      <c r="N151">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="O151">
-        <v>0.04</v>
-      </c>
-      <c r="P151">
-        <v>321</v>
-      </c>
-      <c r="Q151">
-        <v>14</v>
-      </c>
-      <c r="R151">
-        <v>52120</v>
-      </c>
-      <c r="S151">
-        <v>50</v>
-      </c>
-      <c r="T151">
-        <v>58.9</v>
-      </c>
-      <c r="U151">
-        <v>2.1</v>
-      </c>
       <c r="V151" s="2">
-        <v>5.7000000000000002E-3</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W151" s="2">
-        <v>5.9999999999999995E-4</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="X151">
-        <v>0.32</v>
+        <v>1.34</v>
       </c>
       <c r="Y151">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="Z151" t="s">
         <v>96</v>
@@ -6904,70 +6863,70 @@
         <v>104</v>
       </c>
       <c r="D152">
-        <v>4688</v>
+        <v>4147</v>
       </c>
       <c r="E152" t="s">
         <v>98</v>
       </c>
       <c r="F152" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G152">
-        <v>1222.3</v>
+        <v>1194</v>
       </c>
       <c r="H152">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I152">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J152">
-        <v>-42.59</v>
+        <v>-42.3</v>
       </c>
       <c r="K152">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="L152">
-        <v>9.6</v>
+        <v>3.62</v>
       </c>
       <c r="M152">
-        <v>1.7</v>
+        <v>0.13</v>
       </c>
       <c r="N152">
-        <v>0.7</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="O152">
         <v>0.04</v>
       </c>
       <c r="P152">
-        <v>163</v>
+        <v>321</v>
       </c>
       <c r="Q152">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="R152">
-        <v>52238</v>
+        <v>52120</v>
       </c>
       <c r="S152">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T152">
-        <v>114</v>
+        <v>58.9</v>
       </c>
       <c r="U152">
-        <v>21</v>
+        <v>2.1</v>
       </c>
       <c r="V152" s="2">
-        <v>0.04</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="W152" s="2">
-        <v>2.1000000000000001E-2</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="X152">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="Y152">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Z152" t="s">
         <v>96</v>
@@ -6981,70 +6940,70 @@
         <v>104</v>
       </c>
       <c r="D153">
-        <v>4843</v>
+        <v>4688</v>
       </c>
       <c r="E153" t="s">
         <v>98</v>
       </c>
       <c r="F153" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G153">
-        <v>1240</v>
+        <v>1222.3</v>
       </c>
       <c r="H153">
+        <v>1</v>
+      </c>
+      <c r="I153">
         <v>3</v>
       </c>
-      <c r="I153">
-        <v>9.1</v>
-      </c>
       <c r="J153">
-        <v>-42.08</v>
+        <v>-42.59</v>
       </c>
       <c r="K153">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="L153">
-        <v>5.32</v>
+        <v>9.6</v>
       </c>
       <c r="M153">
-        <v>0.16</v>
+        <v>1.7</v>
       </c>
       <c r="N153">
-        <v>0.21</v>
+        <v>0.7</v>
       </c>
       <c r="O153">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="P153">
-        <v>256</v>
+        <v>163</v>
       </c>
       <c r="Q153">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R153">
-        <v>49310</v>
+        <v>52238</v>
       </c>
       <c r="S153">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T153">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="U153">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="V153" s="2">
-        <v>1.8100000000000002E-2</v>
+        <v>0.04</v>
       </c>
       <c r="W153" s="2">
-        <v>1.6999999999999999E-3</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="X153">
-        <v>0.57999999999999996</v>
+        <v>0.3</v>
       </c>
       <c r="Y153">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Z153" t="s">
         <v>96</v>
@@ -7058,7 +7017,7 @@
         <v>104</v>
       </c>
       <c r="D154">
-        <v>4524</v>
+        <v>4843</v>
       </c>
       <c r="E154" t="s">
         <v>98</v>
@@ -7067,46 +7026,46 @@
         <v>98</v>
       </c>
       <c r="G154">
-        <v>1267</v>
+        <v>1240</v>
       </c>
       <c r="H154">
         <v>3</v>
       </c>
       <c r="I154">
-        <v>7.6</v>
+        <v>9.1</v>
       </c>
       <c r="J154">
-        <v>-42.97</v>
+        <v>-42.08</v>
       </c>
       <c r="K154">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="L154">
-        <v>5.19</v>
+        <v>5.32</v>
       </c>
       <c r="M154">
         <v>0.16</v>
       </c>
       <c r="N154">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="O154">
         <v>0.03</v>
       </c>
       <c r="P154">
-        <v>34</v>
+        <v>256</v>
       </c>
       <c r="Q154">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="R154">
-        <v>49020</v>
+        <v>49310</v>
       </c>
       <c r="S154">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="T154">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="U154">
         <v>3</v>
@@ -7115,13 +7074,13 @@
         <v>1.8100000000000002E-2</v>
       </c>
       <c r="W154" s="2">
-        <v>1.6000000000000001E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="X154">
-        <v>0.76</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="Y154">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="Z154" t="s">
         <v>96</v>
@@ -7135,7 +7094,7 @@
         <v>104</v>
       </c>
       <c r="D155">
-        <v>4595</v>
+        <v>4524</v>
       </c>
       <c r="E155" t="s">
         <v>98</v>
@@ -7144,61 +7103,61 @@
         <v>98</v>
       </c>
       <c r="G155">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="H155">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I155">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="J155">
-        <v>-42.4</v>
+        <v>-42.97</v>
       </c>
       <c r="K155">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="L155">
-        <v>6.3</v>
+        <v>5.19</v>
       </c>
       <c r="M155">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="N155">
-        <v>0.25</v>
+        <v>0.09</v>
       </c>
       <c r="O155">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="P155">
-        <v>163</v>
+        <v>34</v>
       </c>
       <c r="Q155">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="R155">
-        <v>51720</v>
+        <v>49020</v>
       </c>
       <c r="S155">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="T155">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="U155">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V155" s="2">
-        <v>2.9000000000000001E-2</v>
+        <v>1.8100000000000002E-2</v>
       </c>
       <c r="W155" s="2">
-        <v>4.0000000000000001E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="X155">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="Y155">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="Z155" t="s">
         <v>96</v>
@@ -7212,7 +7171,7 @@
         <v>104</v>
       </c>
       <c r="D156">
-        <v>5434</v>
+        <v>4595</v>
       </c>
       <c r="E156" t="s">
         <v>98</v>
@@ -7221,7 +7180,7 @@
         <v>98</v>
       </c>
       <c r="G156">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H156">
         <v>9</v>
@@ -7230,52 +7189,52 @@
         <v>2.4</v>
       </c>
       <c r="J156">
-        <v>-41.14</v>
+        <v>-42.4</v>
       </c>
       <c r="K156">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="L156">
-        <v>7.8</v>
+        <v>6.3</v>
       </c>
       <c r="M156">
         <v>0.3</v>
       </c>
       <c r="N156">
-        <v>0.55100000000000005</v>
+        <v>0.25</v>
       </c>
       <c r="O156">
-        <v>1.7999999999999999E-2</v>
+        <v>0.04</v>
       </c>
       <c r="P156">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="Q156">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R156">
-        <v>52449</v>
+        <v>51720</v>
       </c>
       <c r="S156">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="T156">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="U156">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V156" s="2">
-        <v>3.5999999999999997E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="W156" s="2">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="X156">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="Y156">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="Z156" t="s">
         <v>96</v>
@@ -7289,7 +7248,7 @@
         <v>104</v>
       </c>
       <c r="D157">
-        <v>4390</v>
+        <v>5434</v>
       </c>
       <c r="E157" t="s">
         <v>98</v>
@@ -7298,61 +7257,61 @@
         <v>98</v>
       </c>
       <c r="G157">
-        <v>1313</v>
+        <v>1277</v>
       </c>
       <c r="H157">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I157">
+        <v>2.4</v>
+      </c>
+      <c r="J157">
+        <v>-41.14</v>
+      </c>
+      <c r="K157">
+        <v>0.11</v>
+      </c>
+      <c r="L157">
+        <v>7.8</v>
+      </c>
+      <c r="M157">
+        <v>0.3</v>
+      </c>
+      <c r="N157">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="O157">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="P157">
+        <v>192</v>
+      </c>
+      <c r="Q157">
         <v>3</v>
       </c>
-      <c r="J157">
-        <v>-42.4</v>
-      </c>
-      <c r="K157">
-        <v>0.23</v>
-      </c>
-      <c r="L157">
-        <v>5.5</v>
-      </c>
-      <c r="M157">
-        <v>0.9</v>
-      </c>
-      <c r="N157">
-        <v>0.37</v>
-      </c>
-      <c r="O157">
-        <v>0.08</v>
-      </c>
-      <c r="P157">
-        <v>143</v>
-      </c>
-      <c r="Q157">
-        <v>8</v>
-      </c>
       <c r="R157">
-        <v>51203</v>
+        <v>52449</v>
       </c>
       <c r="S157">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="T157">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="U157">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="V157" s="2">
-        <v>1.7999999999999999E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W157" s="2">
-        <v>8.9999999999999993E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="X157">
-        <v>0.6</v>
+        <v>0.43</v>
       </c>
       <c r="Y157">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Z157" t="s">
         <v>96</v>
@@ -7366,7 +7325,7 @@
         <v>104</v>
       </c>
       <c r="D158">
-        <v>4560</v>
+        <v>4390</v>
       </c>
       <c r="E158" t="s">
         <v>98</v>
@@ -7375,61 +7334,61 @@
         <v>98</v>
       </c>
       <c r="G158">
-        <v>1365</v>
+        <v>1313</v>
       </c>
       <c r="H158">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I158">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J158">
-        <v>-41.93</v>
+        <v>-42.4</v>
       </c>
       <c r="K158">
-        <v>7.0000000000000007E-2</v>
+        <v>0.23</v>
       </c>
       <c r="L158">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="M158">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="N158">
-        <v>0.63</v>
+        <v>0.37</v>
       </c>
       <c r="O158">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="P158">
-        <v>322</v>
+        <v>143</v>
       </c>
       <c r="Q158">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R158">
-        <v>53413</v>
+        <v>51203</v>
       </c>
       <c r="S158">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="T158">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="U158">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="V158" s="2">
-        <v>2.5000000000000001E-3</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="W158" s="2">
-        <v>1.1999999999999999E-3</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="X158">
-        <v>0.24</v>
+        <v>0.6</v>
       </c>
       <c r="Y158">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="Z158" t="s">
         <v>96</v>
@@ -7443,7 +7402,7 @@
         <v>104</v>
       </c>
       <c r="D159">
-        <v>5671</v>
+        <v>4560</v>
       </c>
       <c r="E159" t="s">
         <v>98</v>
@@ -7452,61 +7411,61 @@
         <v>98</v>
       </c>
       <c r="G159">
-        <v>1423</v>
+        <v>1365</v>
       </c>
       <c r="H159">
+        <v>5</v>
+      </c>
+      <c r="I159">
+        <v>2.9</v>
+      </c>
+      <c r="J159">
+        <v>-41.93</v>
+      </c>
+      <c r="K159">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L159">
+        <v>3.3</v>
+      </c>
+      <c r="M159">
+        <v>0.5</v>
+      </c>
+      <c r="N159">
+        <v>0.63</v>
+      </c>
+      <c r="O159">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="P159">
+        <v>322</v>
+      </c>
+      <c r="Q159">
+        <v>6</v>
+      </c>
+      <c r="R159">
+        <v>53413</v>
+      </c>
+      <c r="S159">
         <v>7</v>
       </c>
-      <c r="I159">
-        <v>2.1</v>
-      </c>
-      <c r="J159">
-        <v>-41.49</v>
-      </c>
-      <c r="K159">
-        <v>0.08</v>
-      </c>
-      <c r="L159">
-        <v>5.74</v>
-      </c>
-      <c r="M159">
-        <v>0.1</v>
-      </c>
-      <c r="N159">
-        <v>0.28599999999999998</v>
-      </c>
-      <c r="O159">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="P159">
-        <v>123</v>
-      </c>
-      <c r="Q159">
-        <v>4</v>
-      </c>
-      <c r="R159">
-        <v>51044</v>
-      </c>
-      <c r="S159">
-        <v>12</v>
-      </c>
       <c r="T159">
-        <v>107.6</v>
+        <v>49</v>
       </c>
       <c r="U159">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V159" s="2">
-        <v>2.4500000000000001E-2</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="W159" s="2">
-        <v>1.2999999999999999E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="X159">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="Y159">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="Z159" t="s">
         <v>96</v>
@@ -7517,10 +7476,10 @@
     </row>
     <row r="160" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C160" s="1" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="D160">
-        <v>5848</v>
+        <v>5671</v>
       </c>
       <c r="E160" t="s">
         <v>98</v>
@@ -7529,61 +7488,61 @@
         <v>98</v>
       </c>
       <c r="G160">
-        <v>1720</v>
+        <v>1423</v>
       </c>
       <c r="H160">
+        <v>7</v>
+      </c>
+      <c r="I160">
+        <v>2.1</v>
+      </c>
+      <c r="J160">
+        <v>-41.49</v>
+      </c>
+      <c r="K160">
+        <v>0.08</v>
+      </c>
+      <c r="L160">
+        <v>5.74</v>
+      </c>
+      <c r="M160">
+        <v>0.1</v>
+      </c>
+      <c r="N160">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="O160">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="P160">
+        <v>123</v>
+      </c>
+      <c r="Q160">
+        <v>4</v>
+      </c>
+      <c r="R160">
+        <v>51044</v>
+      </c>
+      <c r="S160">
+        <v>12</v>
+      </c>
+      <c r="T160">
+        <v>107.6</v>
+      </c>
+      <c r="U160">
+        <v>2</v>
+      </c>
+      <c r="V160" s="2">
+        <v>2.4500000000000001E-2</v>
+      </c>
+      <c r="W160" s="2">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="X160">
+        <v>0.35</v>
+      </c>
+      <c r="Y160">
         <v>30</v>
-      </c>
-      <c r="I160">
-        <v>2</v>
-      </c>
-      <c r="J160">
-        <v>-33.5</v>
-      </c>
-      <c r="K160">
-        <v>0.3</v>
-      </c>
-      <c r="L160">
-        <v>7.4</v>
-      </c>
-      <c r="M160">
-        <v>0.7</v>
-      </c>
-      <c r="N160">
-        <v>0.45</v>
-      </c>
-      <c r="O160">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="P160">
-        <v>26</v>
-      </c>
-      <c r="Q160">
-        <v>7</v>
-      </c>
-      <c r="R160">
-        <v>51090</v>
-      </c>
-      <c r="S160">
-        <v>24</v>
-      </c>
-      <c r="T160">
-        <v>156</v>
-      </c>
-      <c r="U160">
-        <v>15</v>
-      </c>
-      <c r="V160" s="2">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="W160" s="2">
-        <v>1.4E-2</v>
-      </c>
-      <c r="X160">
-        <v>1.48</v>
-      </c>
-      <c r="Y160">
-        <v>29</v>
       </c>
       <c r="Z160" t="s">
         <v>96</v>
@@ -7594,10 +7553,10 @@
     </row>
     <row r="161" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C161" s="1" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="D161">
-        <v>5325</v>
+        <v>5848</v>
       </c>
       <c r="E161" t="s">
         <v>98</v>
@@ -7606,61 +7565,61 @@
         <v>98</v>
       </c>
       <c r="G161">
-        <v>1772</v>
+        <v>1720</v>
       </c>
       <c r="H161">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="I161">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J161">
-        <v>-42.91</v>
+        <v>-33.5</v>
       </c>
       <c r="K161">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="L161">
-        <v>8.6999999999999993</v>
+        <v>7.4</v>
       </c>
       <c r="M161">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="N161">
-        <v>0.77</v>
+        <v>0.45</v>
       </c>
       <c r="O161">
-        <v>0.03</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="P161">
-        <v>239.3</v>
+        <v>26</v>
       </c>
       <c r="Q161">
-        <v>2.2999999999999998</v>
+        <v>7</v>
       </c>
       <c r="R161">
-        <v>53588</v>
+        <v>51090</v>
       </c>
       <c r="S161">
         <v>24</v>
       </c>
       <c r="T161">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="U161">
         <v>15</v>
       </c>
       <c r="V161" s="2">
-        <v>3.1E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="W161" s="2">
-        <v>8.9999999999999993E-3</v>
+        <v>1.4E-2</v>
       </c>
       <c r="X161">
-        <v>0.66</v>
+        <v>1.48</v>
       </c>
       <c r="Y161">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Z161" t="s">
         <v>96</v>
@@ -7674,7 +7633,7 @@
         <v>104</v>
       </c>
       <c r="D162">
-        <v>3871</v>
+        <v>5325</v>
       </c>
       <c r="E162" t="s">
         <v>98</v>
@@ -7683,61 +7642,61 @@
         <v>98</v>
       </c>
       <c r="G162">
-        <v>1960</v>
+        <v>1772</v>
       </c>
       <c r="H162">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="I162">
         <v>1.9</v>
       </c>
       <c r="J162">
-        <v>-42.87</v>
+        <v>-42.91</v>
       </c>
       <c r="K162">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="L162">
-        <v>2.91</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="M162">
-        <v>0.23</v>
+        <v>0.8</v>
       </c>
       <c r="N162">
-        <v>0.54</v>
+        <v>0.77</v>
       </c>
       <c r="O162">
-        <v>7.0000000000000007E-2</v>
+        <v>0.03</v>
       </c>
       <c r="P162">
-        <v>10</v>
+        <v>239.3</v>
       </c>
       <c r="Q162">
-        <v>12</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="R162">
-        <v>52630</v>
+        <v>53588</v>
       </c>
       <c r="S162">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="T162">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="U162">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="V162" s="2">
-        <v>3.0000000000000001E-3</v>
+        <v>3.1E-2</v>
       </c>
       <c r="W162" s="2">
-        <v>6.9999999999999999E-4</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="X162">
-        <v>0.84</v>
+        <v>0.66</v>
       </c>
       <c r="Y162">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="Z162" t="s">
         <v>96</v>
@@ -7751,7 +7710,7 @@
         <v>104</v>
       </c>
       <c r="D163">
-        <v>1888</v>
+        <v>3871</v>
       </c>
       <c r="E163" t="s">
         <v>98</v>
@@ -7760,61 +7719,61 @@
         <v>98</v>
       </c>
       <c r="G163">
-        <v>2240</v>
+        <v>1960</v>
       </c>
       <c r="H163">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I163">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J163">
-        <v>-41.44</v>
+        <v>-42.87</v>
       </c>
       <c r="K163">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="L163">
-        <v>6.4</v>
+        <v>2.91</v>
       </c>
       <c r="M163">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="N163">
-        <v>0.21</v>
+        <v>0.54</v>
       </c>
       <c r="O163">
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="P163">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q163">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R163">
-        <v>52510</v>
+        <v>52630</v>
       </c>
       <c r="S163">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T163">
-        <v>192</v>
+        <v>66</v>
       </c>
       <c r="U163">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="V163" s="2">
-        <v>5.7000000000000002E-2</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="W163" s="2">
-        <v>0.01</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="X163">
-        <v>1.1100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="Y163">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="Z163" t="s">
         <v>96</v>
@@ -7828,7 +7787,7 @@
         <v>104</v>
       </c>
       <c r="D164">
-        <v>5309</v>
+        <v>1888</v>
       </c>
       <c r="E164" t="s">
         <v>98</v>
@@ -7837,61 +7796,61 @@
         <v>98</v>
       </c>
       <c r="G164">
-        <v>2670</v>
+        <v>2240</v>
       </c>
       <c r="H164">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I164">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J164">
-        <v>-42.93</v>
+        <v>-41.44</v>
       </c>
       <c r="K164">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="L164">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="M164">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N164">
-        <v>0.32</v>
+        <v>0.21</v>
       </c>
       <c r="O164">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="P164">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="Q164">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="R164">
-        <v>51650</v>
+        <v>52510</v>
       </c>
       <c r="S164">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="T164">
-        <v>112</v>
+        <v>192</v>
       </c>
       <c r="U164">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V164" s="2">
-        <v>7.7000000000000002E-3</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="W164" s="2">
-        <v>1.8E-3</v>
+        <v>0.01</v>
       </c>
       <c r="X164">
-        <v>0.91</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="Y164">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="Z164" t="s">
         <v>96</v>
@@ -7905,7 +7864,7 @@
         <v>104</v>
       </c>
       <c r="D165">
-        <v>5700</v>
+        <v>5309</v>
       </c>
       <c r="E165" t="s">
         <v>98</v>
@@ -7914,61 +7873,61 @@
         <v>98</v>
       </c>
       <c r="G165">
-        <v>2800</v>
+        <v>2670</v>
       </c>
       <c r="H165">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="I165">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J165">
-        <v>-41.61</v>
+        <v>-42.93</v>
       </c>
       <c r="K165">
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
       <c r="L165">
-        <v>4.68</v>
+        <v>3.2</v>
       </c>
       <c r="M165">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="N165">
-        <v>0.15</v>
+        <v>0.32</v>
       </c>
       <c r="O165">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="P165">
-        <v>345</v>
+        <v>131</v>
       </c>
       <c r="Q165">
+        <v>18</v>
+      </c>
+      <c r="R165">
+        <v>51650</v>
+      </c>
+      <c r="S165">
+        <v>120</v>
+      </c>
+      <c r="T165">
+        <v>112</v>
+      </c>
+      <c r="U165">
         <v>10</v>
       </c>
-      <c r="R165">
-        <v>52420</v>
-      </c>
-      <c r="S165">
-        <v>80</v>
-      </c>
-      <c r="T165">
-        <v>178</v>
-      </c>
-      <c r="U165">
-        <v>5</v>
-      </c>
       <c r="V165" s="2">
-        <v>2.8799999999999999E-2</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="W165" s="2">
-        <v>2.5000000000000001E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="X165">
-        <v>0.44</v>
+        <v>0.91</v>
       </c>
       <c r="Y165">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="Z165" t="s">
         <v>96</v>
@@ -7982,7 +7941,7 @@
         <v>104</v>
       </c>
       <c r="D166">
-        <v>5356</v>
+        <v>5700</v>
       </c>
       <c r="E166" t="s">
         <v>98</v>
@@ -7991,61 +7950,61 @@
         <v>98</v>
       </c>
       <c r="G166">
-        <v>2827</v>
+        <v>2800</v>
       </c>
       <c r="H166">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I166">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J166">
-        <v>-43.04</v>
+        <v>-41.61</v>
       </c>
       <c r="K166">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="L166">
-        <v>5.21</v>
+        <v>4.68</v>
       </c>
       <c r="M166">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="N166">
-        <v>0.31</v>
+        <v>0.15</v>
       </c>
       <c r="O166">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="P166">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="Q166">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R166">
-        <v>50930</v>
+        <v>52420</v>
       </c>
       <c r="S166">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="T166">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="U166">
         <v>5</v>
       </c>
       <c r="V166" s="2">
-        <v>3.5999999999999997E-2</v>
+        <v>2.8799999999999999E-2</v>
       </c>
       <c r="W166" s="2">
-        <v>3.0000000000000001E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="X166">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="Y166">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="Z166" t="s">
         <v>96</v>
@@ -8059,7 +8018,7 @@
         <v>104</v>
       </c>
       <c r="D167">
-        <v>4540</v>
+        <v>5356</v>
       </c>
       <c r="E167" t="s">
         <v>98</v>
@@ -8068,61 +8027,61 @@
         <v>98</v>
       </c>
       <c r="G167">
-        <v>3030</v>
+        <v>2827</v>
       </c>
       <c r="H167">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="I167">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J167">
-        <v>-40.4</v>
+        <v>-43.04</v>
       </c>
       <c r="K167">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="L167">
+        <v>5.21</v>
+      </c>
+      <c r="M167">
+        <v>0.12</v>
+      </c>
+      <c r="N167">
+        <v>0.31</v>
+      </c>
+      <c r="O167">
+        <v>0.02</v>
+      </c>
+      <c r="P167">
+        <v>312</v>
+      </c>
+      <c r="Q167">
+        <v>6</v>
+      </c>
+      <c r="R167">
+        <v>50930</v>
+      </c>
+      <c r="S167">
+        <v>30</v>
+      </c>
+      <c r="T167">
+        <v>192</v>
+      </c>
+      <c r="U167">
         <v>5</v>
       </c>
-      <c r="M167">
+      <c r="V167" s="2">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="W167" s="2">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="X167">
         <v>0.4</v>
       </c>
-      <c r="N167">
-        <v>0.36</v>
-      </c>
-      <c r="O167">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="P167">
-        <v>114</v>
-      </c>
-      <c r="Q167">
-        <v>10</v>
-      </c>
-      <c r="R167">
-        <v>53140</v>
-      </c>
-      <c r="S167">
-        <v>100</v>
-      </c>
-      <c r="T167">
-        <v>196</v>
-      </c>
-      <c r="U167">
-        <v>15</v>
-      </c>
-      <c r="V167" s="2">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="W167" s="2">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="X167">
-        <v>0.65</v>
-      </c>
       <c r="Y167">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Z167" t="s">
         <v>96</v>
@@ -8136,7 +8095,7 @@
         <v>104</v>
       </c>
       <c r="D168">
-        <v>8406</v>
+        <v>4540</v>
       </c>
       <c r="E168" t="s">
         <v>98</v>
@@ -8145,61 +8104,61 @@
         <v>98</v>
       </c>
       <c r="G168">
-        <v>3080</v>
+        <v>3030</v>
       </c>
       <c r="H168">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I168">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J168">
-        <v>-42.02</v>
+        <v>-40.4</v>
       </c>
       <c r="K168">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="L168">
-        <v>2.2400000000000002</v>
+        <v>5</v>
       </c>
       <c r="M168">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="N168">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="O168">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="P168">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="Q168">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="R168">
-        <v>53210</v>
+        <v>53140</v>
       </c>
       <c r="S168">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="T168">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="U168">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="V168" s="2">
-        <v>2.8E-3</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="W168" s="2">
-        <v>8.9999999999999998E-4</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="X168">
-        <v>0.56000000000000005</v>
+        <v>0.65</v>
       </c>
       <c r="Y168">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="Z168" t="s">
         <v>96</v>
@@ -8213,7 +8172,7 @@
         <v>104</v>
       </c>
       <c r="D169">
-        <v>5065</v>
+        <v>8406</v>
       </c>
       <c r="E169" t="s">
         <v>98</v>
@@ -8222,61 +8181,61 @@
         <v>98</v>
       </c>
       <c r="G169">
-        <v>4010</v>
+        <v>3080</v>
       </c>
       <c r="H169">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I169">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J169">
-        <v>-43.25</v>
+        <v>-42.02</v>
       </c>
       <c r="K169">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="L169">
-        <v>4.0999999999999996</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="M169">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="N169">
-        <v>0.15</v>
+        <v>0.38</v>
       </c>
       <c r="O169">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="P169">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="Q169">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="R169">
-        <v>51000</v>
+        <v>53210</v>
       </c>
       <c r="S169">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="T169">
-        <v>224</v>
+        <v>88</v>
       </c>
       <c r="U169">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V169" s="2">
-        <v>2.8000000000000001E-2</v>
+        <v>2.8E-3</v>
       </c>
       <c r="W169" s="2">
-        <v>5.0000000000000001E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="X169">
-        <v>0.56999999999999995</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="Y169">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="Z169" t="s">
         <v>96</v>
@@ -8290,7 +8249,7 @@
         <v>104</v>
       </c>
       <c r="D170">
-        <v>5438</v>
+        <v>5065</v>
       </c>
       <c r="E170" t="s">
         <v>98</v>
@@ -8299,61 +8258,61 @@
         <v>98</v>
       </c>
       <c r="G170">
-        <v>4320</v>
+        <v>4010</v>
       </c>
       <c r="H170">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="I170">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J170">
-        <v>-42.2</v>
+        <v>-43.25</v>
       </c>
       <c r="K170">
-        <v>0.5</v>
+        <v>0.16</v>
       </c>
       <c r="L170">
-        <v>9.5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M170">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="N170">
-        <v>0.86</v>
+        <v>0.15</v>
       </c>
       <c r="O170">
-        <v>7.0000000000000007E-2</v>
+        <v>0.05</v>
       </c>
       <c r="P170">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="Q170">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="R170">
-        <v>49560</v>
+        <v>51000</v>
       </c>
       <c r="S170">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="T170">
-        <v>290</v>
+        <v>224</v>
       </c>
       <c r="U170">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="V170" s="2">
-        <v>0.05</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="W170" s="2">
-        <v>0.03</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="X170">
-        <v>1.44</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="Y170">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Z170" t="s">
         <v>96</v>
@@ -8367,7 +8326,7 @@
         <v>104</v>
       </c>
       <c r="D171">
-        <v>4392</v>
+        <v>5438</v>
       </c>
       <c r="E171" t="s">
         <v>98</v>
@@ -8376,61 +8335,61 @@
         <v>98</v>
       </c>
       <c r="G171">
-        <v>4640</v>
+        <v>4320</v>
       </c>
       <c r="H171">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="I171">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J171">
-        <v>-42.13</v>
+        <v>-42.2</v>
       </c>
       <c r="K171">
+        <v>0.5</v>
+      </c>
+      <c r="L171">
+        <v>9.5</v>
+      </c>
+      <c r="M171">
+        <v>1.6</v>
+      </c>
+      <c r="N171">
+        <v>0.86</v>
+      </c>
+      <c r="O171">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L171">
-        <v>5.0599999999999996</v>
-      </c>
-      <c r="M171">
-        <v>0.09</v>
-      </c>
-      <c r="N171">
-        <v>0.51100000000000001</v>
-      </c>
-      <c r="O171">
-        <v>1.4999999999999999E-2</v>
-      </c>
       <c r="P171">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q171">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R171">
-        <v>55530</v>
+        <v>49560</v>
       </c>
       <c r="S171">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="T171">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="U171">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="V171" s="2">
-        <v>3.9E-2</v>
+        <v>0.05</v>
       </c>
       <c r="W171" s="2">
-        <v>3.0000000000000001E-3</v>
+        <v>0.03</v>
       </c>
       <c r="X171">
-        <v>0.3</v>
+        <v>1.44</v>
       </c>
       <c r="Y171">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="Z171" t="s">
         <v>96</v>
@@ -8439,9 +8398,86 @@
         <v>97</v>
       </c>
     </row>
+    <row r="172" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="C172" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D172">
+        <v>4392</v>
+      </c>
+      <c r="E172" t="s">
+        <v>98</v>
+      </c>
+      <c r="F172" t="s">
+        <v>98</v>
+      </c>
+      <c r="G172">
+        <v>4640</v>
+      </c>
+      <c r="H172">
+        <v>150</v>
+      </c>
+      <c r="I172">
+        <v>0.9</v>
+      </c>
+      <c r="J172">
+        <v>-42.13</v>
+      </c>
+      <c r="K172">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L172">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="M172">
+        <v>0.09</v>
+      </c>
+      <c r="N172">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="O172">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P172">
+        <v>194</v>
+      </c>
+      <c r="Q172">
+        <v>3</v>
+      </c>
+      <c r="R172">
+        <v>55530</v>
+      </c>
+      <c r="S172">
+        <v>160</v>
+      </c>
+      <c r="T172">
+        <v>277</v>
+      </c>
+      <c r="U172">
+        <v>6</v>
+      </c>
+      <c r="V172" s="2">
+        <v>3.9E-2</v>
+      </c>
+      <c r="W172" s="2">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="X172">
+        <v>0.3</v>
+      </c>
+      <c r="Y172">
+        <v>34</v>
+      </c>
+      <c r="Z172" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA172" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C89:AA171">
-    <sortCondition ref="G89:G171"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C90:AA172">
+    <sortCondition ref="G90:G172"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Geller_et_al_2009_WIYN_single_lined_orbits.xlsx
+++ b/data/Geller_et_al_2009_WIYN_single_lined_orbits.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10411"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kpenev/projects/git/CircularizationDissipationConstraints/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E090225-8288-5A46-AEC1-CF1F46CC1FFD}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6393DE1-283D-9E4D-B699-BEF321ADA1C4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10880" yWindow="2820" windowWidth="40320" windowHeight="25980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Geller_et_al_2009_WIYN_single_l" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="128">
   <si>
     <t>#</t>
   </si>
@@ -410,7 +421,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -570,6 +581,14 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF00F4FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -975,7 +994,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -997,11 +1016,14 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1799,7 +1821,7 @@
       <c r="C83" s="1"/>
     </row>
     <row r="84" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A84" s="23" t="s">
+      <c r="A84" s="24" t="s">
         <v>116</v>
       </c>
       <c r="B84" t="s">
@@ -1808,7 +1830,7 @@
       <c r="C84" s="1"/>
     </row>
     <row r="85" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A85" s="18" t="s">
+      <c r="A85" s="21" t="s">
         <v>123</v>
       </c>
       <c r="B85" t="s">
@@ -1817,7 +1839,7 @@
       <c r="C85" s="1"/>
     </row>
     <row r="86" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A86" s="25" t="s">
+      <c r="A86" s="26" t="s">
         <v>126</v>
       </c>
       <c r="B86" t="s">
@@ -2155,7 +2177,7 @@
       <c r="A92" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B92" s="24" t="s">
         <v>112</v>
       </c>
       <c r="C92" s="1" t="s">
@@ -2235,6 +2257,12 @@
       </c>
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A93" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="C93" s="1" t="s">
         <v>104</v>
       </c>
@@ -2312,10 +2340,10 @@
       </c>
     </row>
     <row r="94" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="5" t="s">
+      <c r="A94" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="27" t="s">
         <v>112</v>
       </c>
       <c r="C94" s="8" t="s">
@@ -2395,10 +2423,10 @@
       </c>
     </row>
     <row r="95" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A95" s="16" t="s">
+      <c r="A95" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="B95" s="24" t="s">
         <v>112</v>
       </c>
       <c r="C95" s="1" t="s">
@@ -2481,7 +2509,7 @@
       <c r="A96" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B96" s="5" t="s">
+      <c r="B96" s="24" t="s">
         <v>112</v>
       </c>
       <c r="C96" s="1" t="s">
@@ -2561,10 +2589,10 @@
       </c>
     </row>
     <row r="97" spans="1:27" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="16" t="s">
+      <c r="A97" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B97" s="23" t="s">
+      <c r="B97" s="24" t="s">
         <v>112</v>
       </c>
       <c r="C97" s="1" t="s">
@@ -2644,10 +2672,10 @@
       </c>
     </row>
     <row r="98" spans="1:27" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="21" t="s">
+      <c r="A98" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="B98" s="22" t="s">
+      <c r="B98" s="28" t="s">
         <v>112</v>
       </c>
       <c r="C98" s="19" t="s">
@@ -2727,10 +2755,10 @@
       </c>
     </row>
     <row r="99" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A99" s="16" t="s">
+      <c r="A99" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="24" t="s">
         <v>112</v>
       </c>
       <c r="C99" s="1" t="s">
@@ -2810,10 +2838,10 @@
       </c>
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A100" s="16" t="s">
+      <c r="A100" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="B100" s="24" t="s">
         <v>112</v>
       </c>
       <c r="C100" s="1" t="s">
@@ -2979,7 +3007,7 @@
       <c r="A102" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="24" t="s">
         <v>112</v>
       </c>
       <c r="C102" s="1" t="s">
@@ -3305,7 +3333,7 @@
       </c>
     </row>
     <row r="106" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B106" s="5" t="s">
+      <c r="B106" s="24" t="s">
         <v>112</v>
       </c>
       <c r="C106" s="1" t="s">
@@ -3384,80 +3412,80 @@
         <v>97</v>
       </c>
     </row>
-    <row r="107" spans="1:27" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C107" s="19" t="s">
+    <row r="107" spans="1:27" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C107" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D107" s="18">
+      <c r="D107" s="21">
         <v>4710</v>
       </c>
-      <c r="E107" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="F107" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="G107" s="18">
+      <c r="E107" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="F107" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="G107" s="21">
         <v>21.340699999999998</v>
       </c>
-      <c r="H107" s="18">
+      <c r="H107" s="21">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="I107" s="18">
+      <c r="I107" s="21">
         <v>203.7</v>
       </c>
-      <c r="J107" s="18">
+      <c r="J107" s="21">
         <v>-45.7</v>
       </c>
-      <c r="K107" s="18">
+      <c r="K107" s="21">
         <v>0.3</v>
       </c>
-      <c r="L107" s="18">
+      <c r="L107" s="21">
         <v>16.899999999999999</v>
       </c>
-      <c r="M107" s="18">
+      <c r="M107" s="21">
         <v>1.5</v>
       </c>
-      <c r="N107" s="18">
+      <c r="N107" s="21">
         <v>0.67500000000000004</v>
       </c>
-      <c r="O107" s="18">
+      <c r="O107" s="21">
         <v>2.4E-2</v>
       </c>
-      <c r="P107" s="18">
+      <c r="P107" s="21">
         <v>340</v>
       </c>
-      <c r="Q107" s="18">
+      <c r="Q107" s="21">
         <v>3</v>
       </c>
-      <c r="R107" s="18">
+      <c r="R107" s="21">
         <v>52412.34</v>
       </c>
-      <c r="S107" s="18">
+      <c r="S107" s="21">
         <v>0.16</v>
       </c>
-      <c r="T107" s="18">
+      <c r="T107" s="21">
         <v>3.7</v>
       </c>
-      <c r="U107" s="18">
+      <c r="U107" s="21">
         <v>0.3</v>
       </c>
-      <c r="V107" s="20">
+      <c r="V107" s="23">
         <v>4.3E-3</v>
       </c>
-      <c r="W107" s="20">
+      <c r="W107" s="23">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="X107" s="18">
+      <c r="X107" s="21">
         <v>1.18</v>
       </c>
-      <c r="Y107" s="18">
+      <c r="Y107" s="21">
         <v>37</v>
       </c>
-      <c r="Z107" s="18" t="s">
+      <c r="Z107" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="AA107" s="18" t="s">
+      <c r="AA107" s="21" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3616,7 +3644,7 @@
       </c>
     </row>
     <row r="110" spans="1:27" ht="29" x14ac:dyDescent="0.35">
-      <c r="B110" s="24" t="s">
+      <c r="B110" s="25" t="s">
         <v>125</v>
       </c>
       <c r="C110" s="1" t="s">
@@ -3855,80 +3883,80 @@
         <v>97</v>
       </c>
     </row>
-    <row r="113" spans="3:27" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C113" s="19" t="s">
+    <row r="113" spans="3:27" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C113" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D113" s="18">
+      <c r="D113" s="21">
         <v>4673</v>
       </c>
-      <c r="E113" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="F113" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="G113" s="18">
+      <c r="E113" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="F113" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="G113" s="21">
         <v>48.27</v>
       </c>
-      <c r="H113" s="18">
+      <c r="H113" s="21">
         <v>0.06</v>
       </c>
-      <c r="I113" s="18">
+      <c r="I113" s="21">
         <v>22.4</v>
       </c>
-      <c r="J113" s="18">
+      <c r="J113" s="21">
         <v>-41.35</v>
       </c>
-      <c r="K113" s="18">
+      <c r="K113" s="21">
         <v>0.12</v>
       </c>
-      <c r="L113" s="18">
+      <c r="L113" s="21">
         <v>8.4</v>
       </c>
-      <c r="M113" s="18">
+      <c r="M113" s="21">
         <v>0.3</v>
       </c>
-      <c r="N113" s="18">
+      <c r="N113" s="21">
         <v>0.37</v>
       </c>
-      <c r="O113" s="18">
+      <c r="O113" s="21">
         <v>0.03</v>
       </c>
-      <c r="P113" s="18">
+      <c r="P113" s="21">
         <v>351</v>
       </c>
-      <c r="Q113" s="18">
+      <c r="Q113" s="21">
         <v>4</v>
       </c>
-      <c r="R113" s="18">
+      <c r="R113" s="21">
         <v>50836.6</v>
       </c>
-      <c r="S113" s="18">
+      <c r="S113" s="21">
         <v>0.6</v>
       </c>
-      <c r="T113" s="18">
+      <c r="T113" s="21">
         <v>5.18</v>
       </c>
-      <c r="U113" s="18">
+      <c r="U113" s="21">
         <v>0.19</v>
       </c>
-      <c r="V113" s="20">
+      <c r="V113" s="23">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="W113" s="20">
+      <c r="W113" s="23">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="X113" s="18">
+      <c r="X113" s="21">
         <v>0.49</v>
       </c>
-      <c r="Y113" s="18">
+      <c r="Y113" s="21">
         <v>22</v>
       </c>
-      <c r="Z113" s="18" t="s">
+      <c r="Z113" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="AA113" s="18" t="s">
+      <c r="AA113" s="21" t="s">
         <v>97</v>
       </c>
     </row>

--- a/data/Geller_et_al_2009_WIYN_single_lined_orbits.xlsx
+++ b/data/Geller_et_al_2009_WIYN_single_lined_orbits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kpenev/projects/git/CircularizationDissipationConstraints/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6393DE1-283D-9E4D-B699-BEF321ADA1C4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21921BA-D6F0-F94E-98E2-FC18C7E7CBB9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10880" yWindow="2820" windowWidth="40320" windowHeight="25980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2091,7 +2091,7 @@
       </c>
     </row>
     <row r="91" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="5" t="s">
         <v>113</v>
       </c>
       <c r="B91" s="7" t="s">
@@ -2174,7 +2174,7 @@
       </c>
     </row>
     <row r="92" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A92" s="5" t="s">
+      <c r="A92" s="24" t="s">
         <v>113</v>
       </c>
       <c r="B92" s="24" t="s">
@@ -2340,7 +2340,7 @@
       </c>
     </row>
     <row r="94" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="12" t="s">
+      <c r="A94" s="27" t="s">
         <v>113</v>
       </c>
       <c r="B94" s="27" t="s">
@@ -2838,7 +2838,7 @@
       </c>
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A100" s="5" t="s">
+      <c r="A100" s="24" t="s">
         <v>113</v>
       </c>
       <c r="B100" s="24" t="s">
@@ -2921,7 +2921,7 @@
       </c>
     </row>
     <row r="101" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="5" t="s">
+      <c r="A101" s="27" t="s">
         <v>113</v>
       </c>
       <c r="B101" s="12" t="s">
@@ -3173,7 +3173,7 @@
       <c r="A104" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="24" t="s">
         <v>112</v>
       </c>
       <c r="C104" s="1" t="s">
@@ -3724,7 +3724,7 @@
       </c>
     </row>
     <row r="111" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B111" s="14" t="s">
+      <c r="B111" s="24" t="s">
         <v>112</v>
       </c>
       <c r="C111" s="1" t="s">

--- a/data/Geller_et_al_2009_WIYN_single_lined_orbits.xlsx
+++ b/data/Geller_et_al_2009_WIYN_single_lined_orbits.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kpenev/projects/git/CircularizationDissipationConstraints/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21921BA-D6F0-F94E-98E2-FC18C7E7CBB9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1DA070-F668-1B46-883E-CA921A991C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10880" yWindow="2820" windowWidth="40320" windowHeight="25980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="500" windowWidth="33600" windowHeight="20540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Geller_et_al_2009_WIYN_single_l" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="126">
   <si>
     <t>#</t>
   </si>
@@ -363,21 +363,12 @@
     <t>Units</t>
   </si>
   <si>
-    <t>Q=const</t>
-  </si>
-  <si>
     <t>Q=pwrlaw</t>
   </si>
   <si>
-    <t>ganymede</t>
-  </si>
-  <si>
     <t>stampede</t>
   </si>
   <si>
-    <t>kartof</t>
-  </si>
-  <si>
     <t>Color codes</t>
   </si>
   <si>
@@ -408,13 +399,16 @@
     <t>Sufficient samples accumulated on the given cluster</t>
   </si>
   <si>
-    <t>CRASHED</t>
-  </si>
-  <si>
     <t>bold purple</t>
   </si>
   <si>
     <t>Stellar mass distributions go out of range too often</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>M but PPM/PRV small</t>
   </si>
 </sst>
 </file>
@@ -585,14 +579,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF00F4FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <color rgb="FF00C8D2"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -616,8 +602,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="39">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -817,19 +809,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00F4FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -994,7 +974,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1002,28 +982,27 @@
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16"/>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="11" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="11" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1073,8 +1052,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF00C8D2"/>
       <color rgb="FF00F4FF"/>
-      <color rgb="FF00C8D2"/>
       <color rgb="FF009EFF"/>
       <color rgb="FFFF7D41"/>
       <color rgb="FF009099"/>
@@ -1395,6 +1374,7 @@
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:3" x14ac:dyDescent="0.2">
@@ -1788,71 +1768,71 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" s="15" t="s">
+      <c r="A80" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C80" s="1"/>
+    </row>
+    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A81" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B81" t="s">
+        <v>114</v>
+      </c>
+      <c r="C81" s="1"/>
+    </row>
+    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A82" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B82" t="s">
         <v>115</v>
-      </c>
-      <c r="C80" s="1"/>
-    </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A81" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="B81" t="s">
-        <v>117</v>
-      </c>
-      <c r="C81" s="1"/>
-    </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A82" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B82" t="s">
-        <v>118</v>
       </c>
       <c r="C82" s="1"/>
     </row>
     <row r="83" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B83" t="s">
         <v>116</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" s="1"/>
+    </row>
+    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A84" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B84" t="s">
+        <v>121</v>
+      </c>
+      <c r="C84" s="1"/>
+    </row>
+    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A85" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B85" t="s">
         <v>119</v>
       </c>
-      <c r="C83" s="1"/>
-    </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A84" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="B84" t="s">
-        <v>124</v>
-      </c>
-      <c r="C84" s="1"/>
-    </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A85" s="21" t="s">
+      <c r="C85" s="1"/>
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A86" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B86" t="s">
         <v>123</v>
       </c>
-      <c r="B85" t="s">
-        <v>122</v>
-      </c>
-      <c r="C85" s="1"/>
-    </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A86" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="B86" t="s">
-        <v>127</v>
-      </c>
       <c r="C86" s="1"/>
     </row>
     <row r="87" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A87" s="17" t="s">
-        <v>121</v>
+      <c r="A87" s="14" t="s">
+        <v>118</v>
       </c>
       <c r="B87" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C87" s="1"/>
     </row>
@@ -1890,7 +1870,7 @@
       <c r="M88" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="N88" s="3" t="s">
+      <c r="N88" s="20" t="s">
         <v>98</v>
       </c>
       <c r="O88" s="3" t="s">
@@ -1932,10 +1912,10 @@
     </row>
     <row r="89" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>73</v>
@@ -1970,7 +1950,7 @@
       <c r="M89" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="N89" s="3" t="s">
+      <c r="N89" s="20" t="s">
         <v>84</v>
       </c>
       <c r="O89" s="3" t="s">
@@ -2014,6 +1994,9 @@
       </c>
     </row>
     <row r="90" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A90" s="13" t="s">
+        <v>111</v>
+      </c>
       <c r="C90" s="1" t="s">
         <v>104</v>
       </c>
@@ -2047,7 +2030,7 @@
       <c r="M90">
         <v>0.3</v>
       </c>
-      <c r="N90">
+      <c r="N90" s="5">
         <v>0.05</v>
       </c>
       <c r="O90">
@@ -2090,96 +2073,90 @@
         <v>97</v>
       </c>
     </row>
-    <row r="91" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C91" s="8" t="s">
+    <row r="91" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="6"/>
+      <c r="B91" s="8"/>
+      <c r="C91" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D91" s="9">
+      <c r="D91" s="8">
         <v>5362</v>
       </c>
-      <c r="E91" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F91" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="G91" s="10">
+      <c r="E91" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G91" s="9">
         <v>6.1894400000000003</v>
       </c>
-      <c r="H91" s="10">
+      <c r="H91" s="9">
         <v>1.9000000000000001E-4</v>
       </c>
-      <c r="I91" s="10">
+      <c r="I91" s="9">
         <v>178.9</v>
       </c>
-      <c r="J91" s="10">
+      <c r="J91" s="9">
         <v>-28.2</v>
       </c>
-      <c r="K91" s="10">
+      <c r="K91" s="9">
         <v>0.3</v>
       </c>
-      <c r="L91" s="10">
+      <c r="L91" s="9">
         <v>49</v>
       </c>
-      <c r="M91" s="10">
+      <c r="M91" s="9">
         <v>0.5</v>
       </c>
-      <c r="N91" s="10">
+      <c r="N91" s="21">
         <v>2.7E-2</v>
       </c>
-      <c r="O91" s="10">
+      <c r="O91" s="9">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="P91" s="10">
+      <c r="P91" s="9">
         <v>183</v>
       </c>
-      <c r="Q91" s="10">
+      <c r="Q91" s="9">
         <v>20</v>
       </c>
-      <c r="R91" s="10">
+      <c r="R91" s="9">
         <v>51035.3</v>
       </c>
-      <c r="S91" s="10">
+      <c r="S91" s="9">
         <v>0.4</v>
       </c>
-      <c r="T91" s="10">
+      <c r="T91" s="9">
         <v>4.17</v>
       </c>
-      <c r="U91" s="10">
+      <c r="U91" s="9">
         <v>0.04</v>
       </c>
-      <c r="V91" s="11">
+      <c r="V91" s="10">
         <v>7.5200000000000003E-2</v>
       </c>
-      <c r="W91" s="11">
+      <c r="W91" s="10">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="X91" s="10">
+      <c r="X91" s="9">
         <v>1.51</v>
       </c>
-      <c r="Y91" s="10">
+      <c r="Y91" s="9">
         <v>29</v>
       </c>
-      <c r="Z91" s="10" t="s">
+      <c r="Z91" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="AA91" s="10" t="s">
+      <c r="AA91" s="9" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A92" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B92" s="24" t="s">
-        <v>112</v>
-      </c>
+      <c r="A92" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B92" s="6"/>
       <c r="C92" s="1" t="s">
         <v>104</v>
       </c>
@@ -2213,7 +2190,7 @@
       <c r="M92">
         <v>0.4</v>
       </c>
-      <c r="N92">
+      <c r="N92" s="5">
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="O92">
@@ -2257,12 +2234,10 @@
       </c>
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A93" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>112</v>
-      </c>
+      <c r="A93" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B93" s="6"/>
       <c r="C93" s="1" t="s">
         <v>104</v>
       </c>
@@ -2296,7 +2271,7 @@
       <c r="M93">
         <v>0.7</v>
       </c>
-      <c r="N93">
+      <c r="N93" s="5">
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="O93">
@@ -2339,96 +2314,90 @@
         <v>97</v>
       </c>
     </row>
-    <row r="94" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="B94" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="C94" s="8" t="s">
+    <row r="94" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="8"/>
+      <c r="B94" s="8"/>
+      <c r="C94" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D94" s="9">
+      <c r="D94" s="8">
         <v>5733</v>
       </c>
-      <c r="E94" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F94" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="G94" s="10">
+      <c r="E94" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G94" s="9">
         <v>8.7040000000000006</v>
       </c>
-      <c r="H94" s="10">
+      <c r="H94" s="9">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="I94" s="10">
+      <c r="I94" s="9">
         <v>356.8</v>
       </c>
-      <c r="J94" s="10">
+      <c r="J94" s="9">
         <v>-33</v>
       </c>
-      <c r="K94" s="10">
+      <c r="K94" s="9">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L94" s="10">
+      <c r="L94" s="9">
         <v>60</v>
       </c>
-      <c r="M94" s="10">
+      <c r="M94" s="9">
         <v>5</v>
       </c>
-      <c r="N94" s="10">
+      <c r="N94" s="21">
         <v>0.5</v>
       </c>
-      <c r="O94" s="10">
+      <c r="O94" s="9">
         <v>0.05</v>
       </c>
-      <c r="P94" s="10">
+      <c r="P94" s="9">
         <v>120</v>
       </c>
-      <c r="Q94" s="10">
+      <c r="Q94" s="9">
         <v>7</v>
       </c>
-      <c r="R94" s="10">
+      <c r="R94" s="9">
         <v>51606.69</v>
       </c>
-      <c r="S94" s="10">
+      <c r="S94" s="9">
         <v>0.1</v>
       </c>
-      <c r="T94" s="10">
+      <c r="T94" s="9">
         <v>6.2</v>
       </c>
-      <c r="U94" s="10">
+      <c r="U94" s="9">
         <v>0.6</v>
       </c>
-      <c r="V94" s="11">
+      <c r="V94" s="10">
         <v>0.13</v>
       </c>
-      <c r="W94" s="11">
+      <c r="W94" s="10">
         <v>0.03</v>
       </c>
-      <c r="X94" s="10">
+      <c r="X94" s="9">
         <v>5.49</v>
       </c>
-      <c r="Y94" s="10">
+      <c r="Y94" s="9">
         <v>11</v>
       </c>
-      <c r="Z94" s="10" t="s">
+      <c r="Z94" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="AA94" s="10" t="s">
+      <c r="AA94" s="9" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="95" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B95" s="24" t="s">
-        <v>112</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B95" s="6"/>
       <c r="C95" s="1" t="s">
         <v>104</v>
       </c>
@@ -2462,7 +2431,7 @@
       <c r="M95">
         <v>0.4</v>
       </c>
-      <c r="N95">
+      <c r="N95" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="O95">
@@ -2506,12 +2475,10 @@
       </c>
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A96" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B96" s="24" t="s">
-        <v>112</v>
-      </c>
+      <c r="A96" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B96" s="6"/>
       <c r="C96" s="1" t="s">
         <v>104</v>
       </c>
@@ -2545,7 +2512,7 @@
       <c r="M96">
         <v>0.22</v>
       </c>
-      <c r="N96">
+      <c r="N96" s="5">
         <v>0.05</v>
       </c>
       <c r="O96">
@@ -2590,11 +2557,9 @@
     </row>
     <row r="97" spans="1:27" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B97" s="24" t="s">
-        <v>112</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B97" s="6"/>
       <c r="C97" s="1" t="s">
         <v>104</v>
       </c>
@@ -2628,7 +2593,7 @@
       <c r="M97">
         <v>0.1</v>
       </c>
-      <c r="N97">
+      <c r="N97" s="5">
         <v>0.09</v>
       </c>
       <c r="O97">
@@ -2671,96 +2636,91 @@
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:27" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="B98" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="C98" s="19" t="s">
+    <row r="98" spans="1:27" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C98" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="D98" s="18">
+      <c r="D98" s="23">
         <v>4904</v>
       </c>
-      <c r="E98" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="F98" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="G98" s="18">
+      <c r="E98" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="F98" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="G98" s="23">
         <v>10.185</v>
       </c>
-      <c r="H98" s="18">
+      <c r="H98" s="23">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I98" s="18">
+      <c r="I98" s="23">
         <v>100.5</v>
       </c>
-      <c r="J98" s="18">
+      <c r="J98" s="23">
         <v>-42.7</v>
       </c>
-      <c r="K98" s="18">
+      <c r="K98" s="23">
         <v>0.3</v>
       </c>
-      <c r="L98" s="18">
+      <c r="L98" s="23">
         <v>11.2</v>
       </c>
-      <c r="M98" s="18">
+      <c r="M98" s="23">
         <v>0.5</v>
       </c>
-      <c r="N98" s="18">
+      <c r="N98" s="25">
         <v>0.37</v>
       </c>
-      <c r="O98" s="18">
+      <c r="O98" s="23">
         <v>0.04</v>
       </c>
-      <c r="P98" s="18">
+      <c r="P98" s="23">
         <v>253</v>
       </c>
-      <c r="Q98" s="18">
+      <c r="Q98" s="23">
         <v>7</v>
       </c>
-      <c r="R98" s="18">
+      <c r="R98" s="23">
         <v>50894.6</v>
       </c>
-      <c r="S98" s="18">
+      <c r="S98" s="23">
         <v>0.16</v>
       </c>
-      <c r="T98" s="18">
+      <c r="T98" s="23">
         <v>1.45</v>
       </c>
-      <c r="U98" s="18">
+      <c r="U98" s="23">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="V98" s="20">
+      <c r="V98" s="26">
         <v>1.1800000000000001E-3</v>
       </c>
-      <c r="W98" s="20">
+      <c r="W98" s="26">
         <v>1.6000000000000001E-4</v>
       </c>
-      <c r="X98" s="18">
+      <c r="X98" s="23">
         <v>1.26</v>
       </c>
-      <c r="Y98" s="18">
+      <c r="Y98" s="23">
         <v>28</v>
       </c>
-      <c r="Z98" s="18" t="s">
+      <c r="Z98" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="AA98" s="18" t="s">
+      <c r="AA98" s="23" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B99" s="24" t="s">
-        <v>112</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B99" s="6"/>
       <c r="C99" s="1" t="s">
         <v>104</v>
       </c>
@@ -2794,7 +2754,7 @@
       <c r="M99">
         <v>0.3</v>
       </c>
-      <c r="N99">
+      <c r="N99" s="5">
         <v>1.2E-2</v>
       </c>
       <c r="O99">
@@ -2838,12 +2798,10 @@
       </c>
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A100" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B100" s="24" t="s">
-        <v>112</v>
-      </c>
+      <c r="A100" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B100" s="6"/>
       <c r="C100" s="1" t="s">
         <v>104</v>
       </c>
@@ -2877,7 +2835,7 @@
       <c r="M100">
         <v>0.2</v>
       </c>
-      <c r="N100">
+      <c r="N100" s="5">
         <v>0.02</v>
       </c>
       <c r="O100">
@@ -2920,96 +2878,90 @@
         <v>97</v>
       </c>
     </row>
-    <row r="101" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="B101" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C101" s="8" t="s">
+    <row r="101" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="8"/>
+      <c r="B101" s="8"/>
+      <c r="C101" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D101" s="9">
+      <c r="D101" s="8">
         <v>8775</v>
       </c>
-      <c r="E101" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F101" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="G101" s="10">
+      <c r="E101" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G101" s="9">
         <v>14.57</v>
       </c>
-      <c r="H101" s="10">
+      <c r="H101" s="9">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I101" s="10">
+      <c r="I101" s="9">
         <v>50.8</v>
       </c>
-      <c r="J101" s="10">
+      <c r="J101" s="9">
         <v>-23.18</v>
       </c>
-      <c r="K101" s="10">
+      <c r="K101" s="9">
         <v>0.22</v>
       </c>
-      <c r="L101" s="10">
+      <c r="L101" s="9">
         <v>8.8000000000000007</v>
       </c>
-      <c r="M101" s="10">
+      <c r="M101" s="9">
         <v>0.3</v>
       </c>
-      <c r="N101" s="10">
+      <c r="N101" s="21">
         <v>0.2</v>
       </c>
-      <c r="O101" s="10">
+      <c r="O101" s="9">
         <v>0.04</v>
       </c>
-      <c r="P101" s="10">
+      <c r="P101" s="9">
         <v>74</v>
       </c>
-      <c r="Q101" s="10">
+      <c r="Q101" s="9">
         <v>9</v>
       </c>
-      <c r="R101" s="10">
+      <c r="R101" s="9">
         <v>50890.400000000001</v>
       </c>
-      <c r="S101" s="10">
+      <c r="S101" s="9">
         <v>0.3</v>
       </c>
-      <c r="T101" s="10">
+      <c r="T101" s="9">
         <v>1.72</v>
       </c>
-      <c r="U101" s="10">
+      <c r="U101" s="9">
         <v>0.06</v>
       </c>
-      <c r="V101" s="11">
+      <c r="V101" s="10">
         <v>9.6000000000000002E-4</v>
       </c>
-      <c r="W101" s="11">
+      <c r="W101" s="10">
         <v>1E-4</v>
       </c>
-      <c r="X101" s="10">
+      <c r="X101" s="9">
         <v>0.9</v>
       </c>
-      <c r="Y101" s="10">
+      <c r="Y101" s="9">
         <v>19</v>
       </c>
-      <c r="Z101" s="10" t="s">
+      <c r="Z101" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="AA101" s="10" t="s">
+      <c r="AA101" s="9" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="102" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B102" s="24" t="s">
-        <v>112</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B102" s="6"/>
       <c r="C102" s="1" t="s">
         <v>104</v>
       </c>
@@ -3043,7 +2995,7 @@
       <c r="M102">
         <v>0.19</v>
       </c>
-      <c r="N102">
+      <c r="N102" s="5">
         <v>1.2E-2</v>
       </c>
       <c r="O102">
@@ -3088,11 +3040,9 @@
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>112</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B103" s="6"/>
       <c r="C103" s="1" t="s">
         <v>104</v>
       </c>
@@ -3126,7 +3076,7 @@
       <c r="M103">
         <v>0.2</v>
       </c>
-      <c r="N103">
+      <c r="N103" s="5">
         <v>0.01</v>
       </c>
       <c r="O103">
@@ -3171,11 +3121,9 @@
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B104" s="24" t="s">
-        <v>112</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B104" s="6"/>
       <c r="C104" s="1" t="s">
         <v>104</v>
       </c>
@@ -3209,7 +3157,7 @@
       <c r="M104">
         <v>0.23</v>
       </c>
-      <c r="N104">
+      <c r="N104" s="5">
         <v>2.3E-2</v>
       </c>
       <c r="O104">
@@ -3253,9 +3201,10 @@
       </c>
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B105" s="5" t="s">
-        <v>112</v>
-      </c>
+      <c r="A105" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" s="6"/>
       <c r="C105" s="1" t="s">
         <v>104</v>
       </c>
@@ -3289,7 +3238,7 @@
       <c r="M105">
         <v>0.7</v>
       </c>
-      <c r="N105">
+      <c r="N105" s="5">
         <v>0.28499999999999998</v>
       </c>
       <c r="O105">
@@ -3332,321 +3281,330 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B106" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="C106" s="1" t="s">
+    <row r="106" spans="1:27" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C106" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="15">
         <v>880</v>
       </c>
-      <c r="E106" t="s">
-        <v>98</v>
-      </c>
-      <c r="F106" t="s">
-        <v>98</v>
-      </c>
-      <c r="G106">
+      <c r="E106" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="F106" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="G106" s="15">
         <v>20.292000000000002</v>
       </c>
-      <c r="H106">
+      <c r="H106" s="15">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="I106">
+      <c r="I106" s="15">
         <v>42.1</v>
       </c>
-      <c r="J106">
+      <c r="J106" s="15">
         <v>-41.71</v>
       </c>
-      <c r="K106">
+      <c r="K106" s="15">
         <v>0.24</v>
       </c>
-      <c r="L106">
+      <c r="L106" s="15">
         <v>15.4</v>
       </c>
-      <c r="M106">
+      <c r="M106" s="15">
         <v>0.3</v>
       </c>
-      <c r="N106">
+      <c r="N106" s="15">
         <v>0.21299999999999999</v>
       </c>
-      <c r="O106">
+      <c r="O106" s="15">
         <v>1.6E-2</v>
       </c>
-      <c r="P106">
+      <c r="P106" s="15">
         <v>238</v>
       </c>
-      <c r="Q106">
+      <c r="Q106" s="15">
         <v>4</v>
       </c>
-      <c r="R106">
+      <c r="R106" s="15">
         <v>50715.29</v>
       </c>
-      <c r="S106">
+      <c r="S106" s="15">
         <v>0.21</v>
       </c>
-      <c r="T106">
+      <c r="T106" s="15">
         <v>4.21</v>
       </c>
-      <c r="U106">
+      <c r="U106" s="15">
         <v>0.08</v>
       </c>
-      <c r="V106" s="2">
+      <c r="V106" s="15">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="W106" s="2">
+      <c r="W106" s="15">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="X106">
+      <c r="X106" s="15">
         <v>0.77</v>
       </c>
-      <c r="Y106">
+      <c r="Y106" s="15">
         <v>31</v>
       </c>
-      <c r="Z106" t="s">
+      <c r="Z106" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="AA106" t="s">
+      <c r="AA106" s="15" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="107" spans="1:27" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C107" s="22" t="s">
+    <row r="107" spans="1:27" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C107" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="D107" s="21">
+      <c r="D107" s="23">
         <v>4710</v>
       </c>
-      <c r="E107" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="F107" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="G107" s="21">
+      <c r="E107" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="F107" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="G107" s="23">
         <v>21.340699999999998</v>
       </c>
-      <c r="H107" s="21">
+      <c r="H107" s="23">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="I107" s="21">
+      <c r="I107" s="23">
         <v>203.7</v>
       </c>
-      <c r="J107" s="21">
+      <c r="J107" s="23">
         <v>-45.7</v>
       </c>
-      <c r="K107" s="21">
+      <c r="K107" s="23">
         <v>0.3</v>
       </c>
-      <c r="L107" s="21">
+      <c r="L107" s="23">
         <v>16.899999999999999</v>
       </c>
-      <c r="M107" s="21">
+      <c r="M107" s="23">
         <v>1.5</v>
       </c>
-      <c r="N107" s="21">
+      <c r="N107" s="25">
         <v>0.67500000000000004</v>
       </c>
-      <c r="O107" s="21">
+      <c r="O107" s="23">
         <v>2.4E-2</v>
       </c>
-      <c r="P107" s="21">
+      <c r="P107" s="23">
         <v>340</v>
       </c>
-      <c r="Q107" s="21">
+      <c r="Q107" s="23">
         <v>3</v>
       </c>
-      <c r="R107" s="21">
+      <c r="R107" s="23">
         <v>52412.34</v>
       </c>
-      <c r="S107" s="21">
+      <c r="S107" s="23">
         <v>0.16</v>
       </c>
-      <c r="T107" s="21">
+      <c r="T107" s="23">
         <v>3.7</v>
       </c>
-      <c r="U107" s="21">
+      <c r="U107" s="23">
         <v>0.3</v>
       </c>
-      <c r="V107" s="23">
+      <c r="V107" s="26">
         <v>4.3E-3</v>
       </c>
-      <c r="W107" s="23">
+      <c r="W107" s="26">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="X107" s="21">
+      <c r="X107" s="23">
         <v>1.18</v>
       </c>
-      <c r="Y107" s="21">
+      <c r="Y107" s="23">
         <v>37</v>
       </c>
-      <c r="Z107" s="21" t="s">
+      <c r="Z107" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="AA107" s="21" t="s">
+      <c r="AA107" s="23" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="108" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C108" s="8" t="s">
+    <row r="108" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="8"/>
+      <c r="C108" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D108" s="10">
+      <c r="D108" s="9">
         <v>5110</v>
       </c>
-      <c r="E108" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F108" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="G108" s="10">
+      <c r="E108" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F108" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G108" s="9">
         <v>21.360199999999999</v>
       </c>
-      <c r="H108" s="10">
+      <c r="H108" s="9">
         <v>1.9E-3</v>
       </c>
-      <c r="I108" s="10">
+      <c r="I108" s="9">
         <v>163.19999999999999</v>
       </c>
-      <c r="J108" s="10">
+      <c r="J108" s="9">
         <v>-38</v>
       </c>
-      <c r="K108" s="10">
+      <c r="K108" s="9">
         <v>0.7</v>
       </c>
-      <c r="L108" s="10">
+      <c r="L108" s="9">
         <v>37.799999999999997</v>
       </c>
-      <c r="M108" s="10">
+      <c r="M108" s="9">
         <v>0.9</v>
       </c>
-      <c r="N108" s="10">
+      <c r="N108" s="21">
         <v>0.1</v>
       </c>
-      <c r="O108" s="10">
+      <c r="O108" s="9">
         <v>0.03</v>
       </c>
-      <c r="P108" s="10">
+      <c r="P108" s="9">
         <v>195</v>
       </c>
-      <c r="Q108" s="10">
+      <c r="Q108" s="9">
         <v>16</v>
       </c>
-      <c r="R108" s="10">
+      <c r="R108" s="9">
         <v>51197.2</v>
       </c>
-      <c r="S108" s="10">
+      <c r="S108" s="9">
         <v>0.9</v>
       </c>
-      <c r="T108" s="10">
+      <c r="T108" s="9">
         <v>11.1</v>
       </c>
-      <c r="U108" s="10">
+      <c r="U108" s="9">
         <v>0.3</v>
       </c>
-      <c r="V108" s="11">
+      <c r="V108" s="10">
         <v>0.11799999999999999</v>
       </c>
-      <c r="W108" s="11">
+      <c r="W108" s="10">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="X108" s="10">
+      <c r="X108" s="9">
         <v>3.07</v>
       </c>
-      <c r="Y108" s="10">
+      <c r="Y108" s="9">
         <v>22</v>
       </c>
-      <c r="Z108" s="10" t="s">
+      <c r="Z108" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="AA108" s="10" t="s">
+      <c r="AA108" s="9" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="109" spans="1:27" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C109" s="8" t="s">
+    <row r="109" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="8"/>
+      <c r="C109" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D109" s="10">
+      <c r="D109" s="9">
         <v>736</v>
       </c>
-      <c r="E109" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F109" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="G109" s="10">
+      <c r="E109" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F109" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G109" s="9">
         <v>24.004000000000001</v>
       </c>
-      <c r="H109" s="10">
+      <c r="H109" s="9">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="I109" s="10">
+      <c r="I109" s="9">
         <v>50.8</v>
       </c>
-      <c r="J109" s="10">
+      <c r="J109" s="9">
         <v>-50.5</v>
       </c>
-      <c r="K109" s="10">
+      <c r="K109" s="9">
         <v>0.11</v>
       </c>
-      <c r="L109" s="10">
+      <c r="L109" s="9">
         <v>7.21</v>
       </c>
-      <c r="M109" s="10">
+      <c r="M109" s="9">
         <v>0.16</v>
       </c>
-      <c r="N109" s="10">
+      <c r="N109" s="21">
         <v>0.21</v>
       </c>
-      <c r="O109" s="10">
+      <c r="O109" s="9">
         <v>1.9E-2</v>
       </c>
-      <c r="P109" s="10">
+      <c r="P109" s="9">
         <v>240</v>
       </c>
-      <c r="Q109" s="10">
+      <c r="Q109" s="9">
         <v>6</v>
       </c>
-      <c r="R109" s="10">
+      <c r="R109" s="9">
         <v>52039.8</v>
       </c>
-      <c r="S109" s="10">
+      <c r="S109" s="9">
         <v>0.4</v>
       </c>
-      <c r="T109" s="10">
+      <c r="T109" s="9">
         <v>2.33</v>
       </c>
-      <c r="U109" s="10">
+      <c r="U109" s="9">
         <v>0.05</v>
       </c>
-      <c r="V109" s="11">
+      <c r="V109" s="10">
         <v>8.7000000000000001E-4</v>
       </c>
-      <c r="W109" s="11">
+      <c r="W109" s="10">
         <v>6.0000000000000002E-5</v>
       </c>
-      <c r="X109" s="10">
+      <c r="X109" s="9">
         <v>0.42</v>
       </c>
-      <c r="Y109" s="10">
+      <c r="Y109" s="9">
         <v>17</v>
       </c>
-      <c r="Z109" s="10" t="s">
+      <c r="Z109" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="AA109" s="10" t="s">
+      <c r="AA109" s="9" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="110" spans="1:27" ht="29" x14ac:dyDescent="0.35">
-      <c r="B110" s="25" t="s">
-        <v>125</v>
-      </c>
+      <c r="A110" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B110" s="19"/>
       <c r="C110" s="1" t="s">
         <v>104</v>
       </c>
@@ -3680,7 +3638,7 @@
       <c r="M110">
         <v>0.6</v>
       </c>
-      <c r="N110">
+      <c r="N110" s="5">
         <v>0.32</v>
       </c>
       <c r="O110">
@@ -3724,9 +3682,10 @@
       </c>
     </row>
     <row r="111" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B111" s="24" t="s">
-        <v>112</v>
-      </c>
+      <c r="A111" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B111" s="6"/>
       <c r="C111" s="1" t="s">
         <v>104</v>
       </c>
@@ -3760,7 +3719,7 @@
       <c r="M111">
         <v>0.3</v>
       </c>
-      <c r="N111">
+      <c r="N111" s="5">
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="O111">
@@ -3804,9 +3763,10 @@
       </c>
     </row>
     <row r="112" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B112" s="14" t="s">
-        <v>112</v>
-      </c>
+      <c r="A112" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B112" s="18"/>
       <c r="C112" s="1" t="s">
         <v>104</v>
       </c>
@@ -3840,7 +3800,7 @@
       <c r="M112">
         <v>0.24</v>
       </c>
-      <c r="N112">
+      <c r="N112" s="5">
         <v>0.28999999999999998</v>
       </c>
       <c r="O112">
@@ -3883,84 +3843,90 @@
         <v>97</v>
       </c>
     </row>
-    <row r="113" spans="3:27" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C113" s="22" t="s">
+    <row r="113" spans="1:27" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C113" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="D113" s="21">
+      <c r="D113" s="23">
         <v>4673</v>
       </c>
-      <c r="E113" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="F113" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="G113" s="21">
+      <c r="E113" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="F113" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="G113" s="23">
         <v>48.27</v>
       </c>
-      <c r="H113" s="21">
+      <c r="H113" s="23">
         <v>0.06</v>
       </c>
-      <c r="I113" s="21">
+      <c r="I113" s="23">
         <v>22.4</v>
       </c>
-      <c r="J113" s="21">
+      <c r="J113" s="23">
         <v>-41.35</v>
       </c>
-      <c r="K113" s="21">
+      <c r="K113" s="23">
         <v>0.12</v>
       </c>
-      <c r="L113" s="21">
+      <c r="L113" s="23">
         <v>8.4</v>
       </c>
-      <c r="M113" s="21">
+      <c r="M113" s="23">
         <v>0.3</v>
       </c>
-      <c r="N113" s="21">
+      <c r="N113" s="25">
         <v>0.37</v>
       </c>
-      <c r="O113" s="21">
+      <c r="O113" s="23">
         <v>0.03</v>
       </c>
-      <c r="P113" s="21">
+      <c r="P113" s="23">
         <v>351</v>
       </c>
-      <c r="Q113" s="21">
+      <c r="Q113" s="23">
         <v>4</v>
       </c>
-      <c r="R113" s="21">
+      <c r="R113" s="23">
         <v>50836.6</v>
       </c>
-      <c r="S113" s="21">
+      <c r="S113" s="23">
         <v>0.6</v>
       </c>
-      <c r="T113" s="21">
+      <c r="T113" s="23">
         <v>5.18</v>
       </c>
-      <c r="U113" s="21">
+      <c r="U113" s="23">
         <v>0.19</v>
       </c>
-      <c r="V113" s="23">
+      <c r="V113" s="26">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="W113" s="23">
+      <c r="W113" s="26">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="X113" s="21">
+      <c r="X113" s="23">
         <v>0.49</v>
       </c>
-      <c r="Y113" s="21">
+      <c r="Y113" s="23">
         <v>22</v>
       </c>
-      <c r="Z113" s="21" t="s">
+      <c r="Z113" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="AA113" s="21" t="s">
+      <c r="AA113" s="23" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="114" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A114" s="11" t="s">
+        <v>111</v>
+      </c>
       <c r="C114" s="1" t="s">
         <v>104</v>
       </c>
@@ -3994,7 +3960,7 @@
       <c r="M114">
         <v>0.22</v>
       </c>
-      <c r="N114">
+      <c r="N114" s="5">
         <v>0.63300000000000001</v>
       </c>
       <c r="O114">
@@ -4037,7 +4003,10 @@
         <v>97</v>
       </c>
     </row>
-    <row r="115" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A115" s="11" t="s">
+        <v>111</v>
+      </c>
       <c r="C115" s="1" t="s">
         <v>104</v>
       </c>
@@ -4071,7 +4040,7 @@
       <c r="M115">
         <v>0.12</v>
       </c>
-      <c r="N115">
+      <c r="N115" s="5">
         <v>0.20399999999999999</v>
       </c>
       <c r="O115">
@@ -4114,7 +4083,10 @@
         <v>97</v>
       </c>
     </row>
-    <row r="116" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A116" s="11" t="s">
+        <v>111</v>
+      </c>
       <c r="C116" s="1" t="s">
         <v>104</v>
       </c>
@@ -4148,7 +4120,7 @@
       <c r="M116">
         <v>0.5</v>
       </c>
-      <c r="N116">
+      <c r="N116" s="5">
         <v>0.18</v>
       </c>
       <c r="O116">
@@ -4191,7 +4163,10 @@
         <v>97</v>
       </c>
     </row>
-    <row r="117" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A117" s="11" t="s">
+        <v>111</v>
+      </c>
       <c r="C117" s="1" t="s">
         <v>104</v>
       </c>
@@ -4225,7 +4200,7 @@
       <c r="M117">
         <v>0.3</v>
       </c>
-      <c r="N117">
+      <c r="N117" s="5">
         <v>0.31</v>
       </c>
       <c r="O117">
@@ -4268,84 +4243,87 @@
         <v>97</v>
       </c>
     </row>
-    <row r="118" spans="3:27" x14ac:dyDescent="0.2">
-      <c r="C118" s="1" t="s">
+    <row r="118" spans="1:27" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C118" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="9">
         <v>5927</v>
       </c>
-      <c r="E118" t="s">
-        <v>98</v>
-      </c>
-      <c r="F118" t="s">
-        <v>98</v>
-      </c>
-      <c r="G118">
+      <c r="E118" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F118" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G118" s="9">
         <v>99.94</v>
       </c>
-      <c r="H118">
+      <c r="H118" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="I118">
+      <c r="I118" s="9">
         <v>113.5</v>
       </c>
-      <c r="J118">
+      <c r="J118" s="9">
         <v>-43.21</v>
       </c>
-      <c r="K118">
+      <c r="K118" s="9">
         <v>0.13</v>
       </c>
-      <c r="L118">
+      <c r="L118" s="9">
         <v>6.9</v>
       </c>
-      <c r="M118">
+      <c r="M118" s="9">
         <v>0.3</v>
       </c>
-      <c r="N118">
+      <c r="N118" s="21">
         <v>0.6</v>
       </c>
-      <c r="O118">
+      <c r="O118" s="9">
         <v>2.3E-2</v>
       </c>
-      <c r="P118">
+      <c r="P118" s="9">
         <v>165</v>
       </c>
-      <c r="Q118">
+      <c r="Q118" s="9">
         <v>3</v>
       </c>
-      <c r="R118">
+      <c r="R118" s="9">
         <v>48271.1</v>
       </c>
-      <c r="S118">
+      <c r="S118" s="9">
         <v>0.6</v>
       </c>
-      <c r="T118">
+      <c r="T118" s="9">
         <v>7.6</v>
       </c>
-      <c r="U118">
+      <c r="U118" s="9">
         <v>0.4</v>
       </c>
-      <c r="V118" s="2">
+      <c r="V118" s="10">
         <v>1.7799999999999999E-3</v>
       </c>
-      <c r="W118" s="2">
+      <c r="W118" s="10">
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="X118">
+      <c r="X118" s="9">
         <v>0.62</v>
       </c>
-      <c r="Y118">
+      <c r="Y118" s="9">
         <v>23</v>
       </c>
-      <c r="Z118" t="s">
+      <c r="Z118" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="AA118" t="s">
+      <c r="AA118" s="9" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="119" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C119" s="1" t="s">
         <v>104</v>
       </c>
@@ -4379,7 +4357,7 @@
       <c r="M119">
         <v>0.5</v>
       </c>
-      <c r="N119">
+      <c r="N119" s="5">
         <v>0.17100000000000001</v>
       </c>
       <c r="O119">
@@ -4422,7 +4400,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="120" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C120" s="1" t="s">
         <v>104</v>
       </c>
@@ -4456,7 +4434,7 @@
       <c r="M120">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N120">
+      <c r="N120" s="5">
         <v>0.78500000000000003</v>
       </c>
       <c r="O120">
@@ -4499,7 +4477,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="121" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C121" s="1" t="s">
         <v>104</v>
       </c>
@@ -4533,7 +4511,7 @@
       <c r="M121">
         <v>0.2</v>
       </c>
-      <c r="N121">
+      <c r="N121" s="5">
         <v>0.44600000000000001</v>
       </c>
       <c r="O121">
@@ -4576,7 +4554,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="122" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C122" s="1" t="s">
         <v>104</v>
       </c>
@@ -4610,7 +4588,7 @@
       <c r="M122">
         <v>0.17</v>
       </c>
-      <c r="N122">
+      <c r="N122" s="5">
         <v>0.24</v>
       </c>
       <c r="O122">
@@ -4653,7 +4631,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="123" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C123" s="1" t="s">
         <v>104</v>
       </c>
@@ -4687,7 +4665,7 @@
       <c r="M123">
         <v>0.14000000000000001</v>
       </c>
-      <c r="N123">
+      <c r="N123" s="5">
         <v>0.129</v>
       </c>
       <c r="O123">
@@ -4730,7 +4708,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="124" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C124" s="1" t="s">
         <v>73</v>
       </c>
@@ -4764,7 +4742,7 @@
       <c r="M124">
         <v>0.3</v>
       </c>
-      <c r="N124">
+      <c r="N124" s="5">
         <v>0.16</v>
       </c>
       <c r="O124">
@@ -4807,7 +4785,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="125" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C125" s="1" t="s">
         <v>104</v>
       </c>
@@ -4841,7 +4819,7 @@
       <c r="M125">
         <v>0.4</v>
       </c>
-      <c r="N125">
+      <c r="N125" s="5">
         <v>0.37</v>
       </c>
       <c r="O125">
@@ -4884,7 +4862,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="126" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C126" s="1" t="s">
         <v>104</v>
       </c>
@@ -4918,7 +4896,7 @@
       <c r="M126">
         <v>0.6</v>
       </c>
-      <c r="N126">
+      <c r="N126" s="5">
         <v>0.71199999999999997</v>
       </c>
       <c r="O126">
@@ -4961,7 +4939,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="127" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C127" s="1" t="s">
         <v>104</v>
       </c>
@@ -4995,7 +4973,7 @@
       <c r="M127">
         <v>0.18</v>
       </c>
-      <c r="N127">
+      <c r="N127" s="5">
         <v>0.28999999999999998</v>
       </c>
       <c r="O127">
@@ -5038,7 +5016,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="128" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C128" s="1" t="s">
         <v>104</v>
       </c>
@@ -5072,7 +5050,7 @@
       <c r="M128">
         <v>0.19</v>
       </c>
-      <c r="N128">
+      <c r="N128" s="5">
         <v>0.15</v>
       </c>
       <c r="O128">
@@ -5149,7 +5127,7 @@
       <c r="M129">
         <v>0.22</v>
       </c>
-      <c r="N129">
+      <c r="N129" s="5">
         <v>0.42199999999999999</v>
       </c>
       <c r="O129">
@@ -5226,7 +5204,7 @@
       <c r="M130">
         <v>0.3</v>
       </c>
-      <c r="N130">
+      <c r="N130" s="5">
         <v>0.45</v>
       </c>
       <c r="O130">
@@ -5303,7 +5281,7 @@
       <c r="M131">
         <v>0.5</v>
       </c>
-      <c r="N131">
+      <c r="N131" s="5">
         <v>0.36</v>
       </c>
       <c r="O131">
@@ -5380,7 +5358,7 @@
       <c r="M132">
         <v>0.8</v>
       </c>
-      <c r="N132">
+      <c r="N132" s="5">
         <v>0.67300000000000004</v>
       </c>
       <c r="O132">
@@ -5457,7 +5435,7 @@
       <c r="M133">
         <v>0.4</v>
       </c>
-      <c r="N133">
+      <c r="N133" s="5">
         <v>0.1</v>
       </c>
       <c r="O133">
@@ -5534,7 +5512,7 @@
       <c r="M134">
         <v>0.2</v>
       </c>
-      <c r="N134">
+      <c r="N134" s="5">
         <v>0.3</v>
       </c>
       <c r="O134">
@@ -5611,7 +5589,7 @@
       <c r="M135">
         <v>0.23</v>
       </c>
-      <c r="N135">
+      <c r="N135" s="5">
         <v>0.64100000000000001</v>
       </c>
       <c r="O135">
@@ -5688,7 +5666,7 @@
       <c r="M136">
         <v>0.4</v>
       </c>
-      <c r="N136">
+      <c r="N136" s="5">
         <v>0.44</v>
       </c>
       <c r="O136">
@@ -5765,7 +5743,7 @@
       <c r="M137">
         <v>0.19</v>
       </c>
-      <c r="N137">
+      <c r="N137" s="5">
         <v>0.49099999999999999</v>
       </c>
       <c r="O137">
@@ -5842,7 +5820,7 @@
       <c r="M138">
         <v>0.22</v>
       </c>
-      <c r="N138">
+      <c r="N138" s="5">
         <v>0.38</v>
       </c>
       <c r="O138">
@@ -5919,7 +5897,7 @@
       <c r="M139">
         <v>0.09</v>
       </c>
-      <c r="N139">
+      <c r="N139" s="5">
         <v>0.26900000000000002</v>
       </c>
       <c r="O139">
@@ -5996,7 +5974,7 @@
       <c r="M140">
         <v>0.3</v>
       </c>
-      <c r="N140">
+      <c r="N140" s="5">
         <v>0.2</v>
       </c>
       <c r="O140">
@@ -6073,7 +6051,7 @@
       <c r="M141">
         <v>0.17</v>
       </c>
-      <c r="N141">
+      <c r="N141" s="5">
         <v>0.21</v>
       </c>
       <c r="O141">
@@ -6150,7 +6128,7 @@
       <c r="M142">
         <v>0.13</v>
       </c>
-      <c r="N142">
+      <c r="N142" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O142">
@@ -6227,7 +6205,7 @@
       <c r="M143">
         <v>0.13</v>
       </c>
-      <c r="N143">
+      <c r="N143" s="5">
         <v>0.22</v>
       </c>
       <c r="O143">
@@ -6304,7 +6282,7 @@
       <c r="M144">
         <v>0.17</v>
       </c>
-      <c r="N144">
+      <c r="N144" s="5">
         <v>0.34</v>
       </c>
       <c r="O144">
@@ -6381,7 +6359,7 @@
       <c r="M145">
         <v>0.16</v>
       </c>
-      <c r="N145">
+      <c r="N145" s="5">
         <v>0.14000000000000001</v>
       </c>
       <c r="O145">
@@ -6458,7 +6436,7 @@
       <c r="M146">
         <v>1</v>
       </c>
-      <c r="N146">
+      <c r="N146" s="5">
         <v>0.74</v>
       </c>
       <c r="O146">
@@ -6535,7 +6513,7 @@
       <c r="M147">
         <v>0.4</v>
       </c>
-      <c r="N147">
+      <c r="N147" s="5">
         <v>0.5</v>
       </c>
       <c r="O147">
@@ -6612,7 +6590,7 @@
       <c r="M148">
         <v>0.09</v>
       </c>
-      <c r="N148">
+      <c r="N148" s="5">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="O148">
@@ -6689,7 +6667,7 @@
       <c r="M149">
         <v>0.3</v>
       </c>
-      <c r="N149">
+      <c r="N149" s="5">
         <v>0.312</v>
       </c>
       <c r="O149">
@@ -6766,7 +6744,7 @@
       <c r="M150">
         <v>0.4</v>
       </c>
-      <c r="N150">
+      <c r="N150" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O150">
@@ -6843,7 +6821,7 @@
       <c r="M151">
         <v>0.4</v>
       </c>
-      <c r="N151">
+      <c r="N151" s="5">
         <v>0.09</v>
       </c>
       <c r="O151">
@@ -6920,7 +6898,7 @@
       <c r="M152">
         <v>0.13</v>
       </c>
-      <c r="N152">
+      <c r="N152" s="5">
         <v>0.14000000000000001</v>
       </c>
       <c r="O152">
@@ -6997,7 +6975,7 @@
       <c r="M153">
         <v>1.7</v>
       </c>
-      <c r="N153">
+      <c r="N153" s="5">
         <v>0.7</v>
       </c>
       <c r="O153">
@@ -7074,7 +7052,7 @@
       <c r="M154">
         <v>0.16</v>
       </c>
-      <c r="N154">
+      <c r="N154" s="5">
         <v>0.21</v>
       </c>
       <c r="O154">
@@ -7151,7 +7129,7 @@
       <c r="M155">
         <v>0.16</v>
       </c>
-      <c r="N155">
+      <c r="N155" s="5">
         <v>0.09</v>
       </c>
       <c r="O155">
@@ -7228,7 +7206,7 @@
       <c r="M156">
         <v>0.3</v>
       </c>
-      <c r="N156">
+      <c r="N156" s="5">
         <v>0.25</v>
       </c>
       <c r="O156">
@@ -7305,7 +7283,7 @@
       <c r="M157">
         <v>0.3</v>
       </c>
-      <c r="N157">
+      <c r="N157" s="5">
         <v>0.55100000000000005</v>
       </c>
       <c r="O157">
@@ -7382,7 +7360,7 @@
       <c r="M158">
         <v>0.9</v>
       </c>
-      <c r="N158">
+      <c r="N158" s="5">
         <v>0.37</v>
       </c>
       <c r="O158">
@@ -7459,7 +7437,7 @@
       <c r="M159">
         <v>0.5</v>
       </c>
-      <c r="N159">
+      <c r="N159" s="5">
         <v>0.63</v>
       </c>
       <c r="O159">
@@ -7536,7 +7514,7 @@
       <c r="M160">
         <v>0.1</v>
       </c>
-      <c r="N160">
+      <c r="N160" s="5">
         <v>0.28599999999999998</v>
       </c>
       <c r="O160">
@@ -7613,7 +7591,7 @@
       <c r="M161">
         <v>0.7</v>
       </c>
-      <c r="N161">
+      <c r="N161" s="5">
         <v>0.45</v>
       </c>
       <c r="O161">
@@ -7690,7 +7668,7 @@
       <c r="M162">
         <v>0.8</v>
       </c>
-      <c r="N162">
+      <c r="N162" s="5">
         <v>0.77</v>
       </c>
       <c r="O162">
@@ -7767,7 +7745,7 @@
       <c r="M163">
         <v>0.23</v>
       </c>
-      <c r="N163">
+      <c r="N163" s="5">
         <v>0.54</v>
       </c>
       <c r="O163">
@@ -7844,7 +7822,7 @@
       <c r="M164">
         <v>0.4</v>
       </c>
-      <c r="N164">
+      <c r="N164" s="5">
         <v>0.21</v>
       </c>
       <c r="O164">
@@ -7921,7 +7899,7 @@
       <c r="M165">
         <v>0.3</v>
       </c>
-      <c r="N165">
+      <c r="N165" s="5">
         <v>0.32</v>
       </c>
       <c r="O165">
@@ -7998,7 +7976,7 @@
       <c r="M166">
         <v>0.13</v>
       </c>
-      <c r="N166">
+      <c r="N166" s="5">
         <v>0.15</v>
       </c>
       <c r="O166">
@@ -8075,7 +8053,7 @@
       <c r="M167">
         <v>0.12</v>
       </c>
-      <c r="N167">
+      <c r="N167" s="5">
         <v>0.31</v>
       </c>
       <c r="O167">
@@ -8152,7 +8130,7 @@
       <c r="M168">
         <v>0.4</v>
       </c>
-      <c r="N168">
+      <c r="N168" s="5">
         <v>0.36</v>
       </c>
       <c r="O168">
@@ -8229,7 +8207,7 @@
       <c r="M169">
         <v>0.24</v>
       </c>
-      <c r="N169">
+      <c r="N169" s="5">
         <v>0.38</v>
       </c>
       <c r="O169">
@@ -8306,7 +8284,7 @@
       <c r="M170">
         <v>0.3</v>
       </c>
-      <c r="N170">
+      <c r="N170" s="5">
         <v>0.15</v>
       </c>
       <c r="O170">
@@ -8383,7 +8361,7 @@
       <c r="M171">
         <v>1.6</v>
       </c>
-      <c r="N171">
+      <c r="N171" s="5">
         <v>0.86</v>
       </c>
       <c r="O171">
@@ -8460,7 +8438,7 @@
       <c r="M172">
         <v>0.09</v>
       </c>
-      <c r="N172">
+      <c r="N172" s="5">
         <v>0.51100000000000001</v>
       </c>
       <c r="O172">
